--- a/Timber Course Alignment Audit.xlsx
+++ b/Timber Course Alignment Audit.xlsx
@@ -2,10 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview &amp; Legend" sheetId="1" r:id="R1cebe59d556c4468"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Syllabus Alignment Matrix" sheetId="2" r:id="R50da3668dbbb462d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Evidence" sheetId="3" r:id="Re0b894b138c847d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Register" sheetId="4" r:id="R778aad103cc146e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview &amp; Legend" sheetId="1" r:id="Rcf448a0dd26a4801"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Syllabus Alignment Matrix" sheetId="2" r:id="R3afeb0cd735b4976"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Evidence" sheetId="3" r:id="R9fa18db5c74d4843"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Register" sheetId="4" r:id="R7ccf8046f0a046cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Register" sheetId="5" r:id="R3ce27269267245d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current Syllabus Summary" sheetId="6" r:id="Rd46bc5f6794a45e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current Program Content Map" sheetId="7" r:id="Ra98e059dbceb4fbc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="25">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -63,8 +66,109 @@
       <x:color rgb="FF5E6B65"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="18"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF20332B"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF154734"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF52645D"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF0E3B2B"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF52645D"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF20332B"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF52645D"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF9C2B24"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF52645D"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF52645D"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF52645D"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF9C2B24"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF20332B"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF0E3B2B"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF20332B"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF0E3B2B"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="34">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -111,8 +215,128 @@
         <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF154734"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF8A552B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE6F0EB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F5F4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF8F3EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFA65E2E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF154734"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE6F0EB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFCE8E6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F5F4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF4CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE6F0EB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F5F4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE6F0EB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE6F0EB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F5F4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE6F0EB"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="11">
+  <x:borders count="30">
     <x:border/>
     <x:border>
       <x:right style="thin">
@@ -218,11 +442,211 @@
         <x:color rgb="FF6D8A7E"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF154734"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF154734"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD7D8D2"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF154734"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD7D8D2"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7D8D2"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7D8D2"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD7D8D2"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7D8D2"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFC9D4CE"/>
+      </x:left>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="135">
+  <x:cellXfs count="547">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -585,6 +1009,1094 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="15" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="15" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="15" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="15" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="21" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="21" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="21" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="21" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="21" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="21" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="22" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="22" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="23" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="23" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="23" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="23" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="23" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="23" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="23" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="21" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="21" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="21" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="21" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="21" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="21" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="21" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="21" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="21" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="21" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="21" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="23" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="23" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="23" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="23" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="23" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="23" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="21" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="21" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="21" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="24" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="24" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="22" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="22" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="23" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="23" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="23" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="23" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="23" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="23" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="23" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="23" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="23" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="23" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="23" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="23" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="22" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="22" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="22" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="22" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="25" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="25" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="26" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="26" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="27" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="27" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="25" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="25" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="25" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="25" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="25" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="25" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="29" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="30" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="30" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="31" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="31" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="30" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="30" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="30" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="30" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="30" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="32" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="32" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="32" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="32" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="30" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="32" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="33" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="33" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -788,14 +2300,14 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="47" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="54" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="4" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -850,477 +2362,298 @@
         <x:v>Timber Course Alignment Audit</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="27" customHeight="1">
-      <x:c r="A3" s="7" t="str">
-        <x:v>Completed webpage evidence map for the seven-stage Year 9-10 Timber pathway, reviewed 1 August 2026. I/P/E describes the strength of the published learning and evidence opportunity; it does not assert that an individual student achieved the outcome.</x:v>
-      </x:c>
-      <x:c r="B3" s="7" t="str">
-        <x:v>Completed webpage evidence map for the seven-stage Year 9-10 Timber pathway, reviewed 1 August 2026. I/P/E describes the strength of the published learning and evidence opportunity; it does not assert that an individual student achieved the outcome.</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="str">
-        <x:v>Completed webpage evidence map for the seven-stage Year 9-10 Timber pathway, reviewed 1 August 2026. I/P/E describes the strength of the published learning and evidence opportunity; it does not assert that an individual student achieved the outcome.</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="str">
-        <x:v>Completed webpage evidence map for the seven-stage Year 9-10 Timber pathway, reviewed 1 August 2026. I/P/E describes the strength of the published learning and evidence opportunity; it does not assert that an individual student achieved the outcome.</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="str">
-        <x:v>Completed webpage evidence map for the seven-stage Year 9-10 Timber pathway, reviewed 1 August 2026. I/P/E describes the strength of the published learning and evidence opportunity; it does not assert that an individual student achieved the outcome.</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="str">
-        <x:v>Completed webpage evidence map for the seven-stage Year 9-10 Timber pathway, reviewed 1 August 2026. I/P/E describes the strength of the published learning and evidence opportunity; it does not assert that an individual student achieved the outcome.</x:v>
-      </x:c>
-      <x:c r="G3" s="7" t="str">
-        <x:v>Completed webpage evidence map for the seven-stage Year 9-10 Timber pathway, reviewed 1 August 2026. I/P/E describes the strength of the published learning and evidence opportunity; it does not assert that an individual student achieved the outcome.</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="str">
-        <x:v>Completed webpage evidence map for the seven-stage Year 9-10 Timber pathway, reviewed 1 August 2026. I/P/E describes the strength of the published learning and evidence opportunity; it does not assert that an individual student achieved the outcome.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="27" customHeight="1">
-      <x:c r="A4" s="7" t="str">
-        <x:v>Completed webpage evidence map for the seven-stage Year 9-10 Timber pathway, reviewed 1 August 2026. I/P/E describes the strength of the published learning and evidence opportunity; it does not assert that an individual student achieved the outcome.</x:v>
-      </x:c>
-      <x:c r="B4" s="7" t="str">
-        <x:v>Completed webpage evidence map for the seven-stage Year 9-10 Timber pathway, reviewed 1 August 2026. I/P/E describes the strength of the published learning and evidence opportunity; it does not assert that an individual student achieved the outcome.</x:v>
-      </x:c>
-      <x:c r="C4" s="7" t="str">
-        <x:v>Completed webpage evidence map for the seven-stage Year 9-10 Timber pathway, reviewed 1 August 2026. I/P/E describes the strength of the published learning and evidence opportunity; it does not assert that an individual student achieved the outcome.</x:v>
-      </x:c>
-      <x:c r="D4" s="7" t="str">
-        <x:v>Completed webpage evidence map for the seven-stage Year 9-10 Timber pathway, reviewed 1 August 2026. I/P/E describes the strength of the published learning and evidence opportunity; it does not assert that an individual student achieved the outcome.</x:v>
-      </x:c>
-      <x:c r="E4" s="7" t="str">
-        <x:v>Completed webpage evidence map for the seven-stage Year 9-10 Timber pathway, reviewed 1 August 2026. I/P/E describes the strength of the published learning and evidence opportunity; it does not assert that an individual student achieved the outcome.</x:v>
-      </x:c>
-      <x:c r="F4" s="7" t="str">
-        <x:v>Completed webpage evidence map for the seven-stage Year 9-10 Timber pathway, reviewed 1 August 2026. I/P/E describes the strength of the published learning and evidence opportunity; it does not assert that an individual student achieved the outcome.</x:v>
-      </x:c>
-      <x:c r="G4" s="7" t="str">
-        <x:v>Completed webpage evidence map for the seven-stage Year 9-10 Timber pathway, reviewed 1 August 2026. I/P/E describes the strength of the published learning and evidence opportunity; it does not assert that an individual student achieved the outcome.</x:v>
-      </x:c>
-      <x:c r="H4" s="7" t="str">
-        <x:v>Completed webpage evidence map for the seven-stage Year 9-10 Timber pathway, reviewed 1 August 2026. I/P/E describes the strength of the published learning and evidence opportunity; it does not assert that an individual student achieved the outcome.</x:v>
-      </x:c>
+    <x:row r="3" ht="28" customHeight="1">
+      <x:c r="A3" s="225" t="str">
+        <x:v>Current-program first view for the two-year Year 9–10 Timber evidence pathway. I/P/E records the audited strength of the learning/evidence opportunity; it does not assert individual student achievement or departmental approval.</x:v>
+      </x:c>
+      <x:c r="B3" s="225"/>
+      <x:c r="C3" s="225"/>
+      <x:c r="D3" s="225"/>
+      <x:c r="E3" s="225"/>
+      <x:c r="F3" s="225"/>
+      <x:c r="G3" s="225"/>
+      <x:c r="H3" s="225"/>
+    </x:row>
+    <x:row r="4" ht="28" customHeight="1">
+      <x:c r="A4" s="225"/>
+      <x:c r="B4" s="225"/>
+      <x:c r="C4" s="225"/>
+      <x:c r="D4" s="225"/>
+      <x:c r="E4" s="225"/>
+      <x:c r="F4" s="225"/>
+      <x:c r="G4" s="225"/>
+      <x:c r="H4" s="225"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="10" t="str">
-        <x:v>Code</x:v>
-      </x:c>
-      <x:c r="B6" s="10" t="str">
+      <x:c r="A6" s="228" t="str">
+        <x:v>Code / status</x:v>
+      </x:c>
+      <x:c r="B6" s="228" t="str">
         <x:v>Meaning</x:v>
       </x:c>
-      <x:c r="C6" s="10" t="str">
-        <x:v>How to use it</x:v>
-      </x:c>
-      <x:c r="E6" s="50" t="str">
-        <x:v>Suggested audit workflow</x:v>
-      </x:c>
-      <x:c r="F6" s="50" t="str">
-        <x:v>Suggested audit workflow</x:v>
-      </x:c>
-      <x:c r="G6" s="50" t="str">
-        <x:v>Suggested audit workflow</x:v>
-      </x:c>
-      <x:c r="H6" s="50" t="str">
-        <x:v>Suggested audit workflow</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="46" customHeight="1">
-      <x:c r="A7" s="47" t="str">
-        <x:v>(blank)</x:v>
-      </x:c>
-      <x:c r="B7" s="30" t="str">
-        <x:v>No code entered</x:v>
-      </x:c>
-      <x:c r="C7" s="31" t="str">
-        <x:v>Read the adjacent reference: blank may mean not yet reviewed, no supported mapping, or not applicable to the supplied program.</x:v>
-      </x:c>
-      <x:c r="E7" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-      <x:c r="F7" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-      <x:c r="G7" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-      <x:c r="H7" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="46" customHeight="1">
-      <x:c r="A8" s="48" t="str">
+      <x:c r="C6" s="228" t="str">
+        <x:v>How to read it</x:v>
+      </x:c>
+      <x:c r="E6" s="269" t="str">
+        <x:v>Reading order</x:v>
+      </x:c>
+      <x:c r="F6" s="269"/>
+      <x:c r="G6" s="269"/>
+      <x:c r="H6" s="269"/>
+    </x:row>
+    <x:row r="7" ht="52" customHeight="1">
+      <x:c r="A7" s="265" t="str">
         <x:v>I</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="str">
+      <x:c r="B7" s="248" t="str">
         <x:v>Introduced</x:v>
       </x:c>
-      <x:c r="C8" s="34" t="str">
-        <x:v>The concept, skill or outcome is first explicitly taught or modelled.</x:v>
-      </x:c>
-      <x:c r="E8" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-      <x:c r="F8" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-      <x:c r="G8" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-      <x:c r="H8" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="46" customHeight="1">
-      <x:c r="A9" s="48" t="str">
+      <x:c r="C7" s="249" t="str">
+        <x:v>The concept, skill or outcome is explicitly taught or modelled.</x:v>
+      </x:c>
+      <x:c r="E7" s="273" t="str">
+        <x:v>1. Start with Current Syllabus Summary for IND51–IND510 pathway status and progression.
+2. Use Syllabus Alignment Matrix for original project-level I/P/E evidence and explicit Gap/Not applicable states.
+3. Use Current Program Content Map for 77 unique exact program statements, their project/week placements and named evidence.
+4. Use Project Evidence for site/folio/plan locations.
+5. Use Gap Register for genuine current issues and formal-program scope decisions.</x:v>
+      </x:c>
+      <x:c r="F7" s="273"/>
+      <x:c r="G7" s="273"/>
+      <x:c r="H7" s="273"/>
+    </x:row>
+    <x:row r="8" ht="52" customHeight="1">
+      <x:c r="A8" s="266" t="str">
         <x:v>P</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="str">
+      <x:c r="B8" s="251" t="str">
         <x:v>Practised and developed</x:v>
       </x:c>
-      <x:c r="C9" s="34" t="str">
-        <x:v>Students revisit and strengthen the learning through guided or increasingly independent work.</x:v>
-      </x:c>
-      <x:c r="E9" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-      <x:c r="F9" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-      <x:c r="G9" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-      <x:c r="H9" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="46" customHeight="1">
-      <x:c r="A10" s="49" t="str">
+      <x:c r="C8" s="252" t="str">
+        <x:v>Students revisit and strengthen the learning; this is the original I/P/E evidence-strength code, not the pathway status 'Partially covered'.</x:v>
+      </x:c>
+      <x:c r="E8" s="273"/>
+      <x:c r="F8" s="273"/>
+      <x:c r="G8" s="273"/>
+      <x:c r="H8" s="273"/>
+    </x:row>
+    <x:row r="9" ht="52" customHeight="1">
+      <x:c r="A9" s="266" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="B10" s="36" t="str">
+      <x:c r="B9" s="251" t="str">
         <x:v>Evidenced / assessed</x:v>
       </x:c>
-      <x:c r="C10" s="37" t="str">
+      <x:c r="C9" s="252" t="str">
         <x:v>A named activity, folio item, product or assessment provides inspectable evidence.</x:v>
       </x:c>
-      <x:c r="E10" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-      <x:c r="F10" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-      <x:c r="G10" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-      <x:c r="H10" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="E11" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-      <x:c r="F11" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-      <x:c r="G11" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-      <x:c r="H11" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="E12" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-      <x:c r="F12" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-      <x:c r="G12" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-      <x:c r="H12" s="54" t="str">
-        <x:v>1. Read the code and its source basis.
-2. Use the I/P/E cell to judge the strength of the published learning opportunity.
-3. Read the adjacent reference for the exact module, activity or gap.
-4. Use Project Evidence for plan, activity, assessment and navigation findings.
-5. Re-audit after any webpage or program revision.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="9" t="str">
+      <x:c r="E9" s="273"/>
+      <x:c r="F9" s="273"/>
+      <x:c r="G9" s="273"/>
+      <x:c r="H9" s="273"/>
+    </x:row>
+    <x:row r="10" ht="52" customHeight="1">
+      <x:c r="A10" s="266" t="str">
+        <x:v>Gap</x:v>
+      </x:c>
+      <x:c r="B10" s="251" t="str">
+        <x:v>Project/activity evidence absent</x:v>
+      </x:c>
+      <x:c r="C10" s="252" t="str">
+        <x:v>The named project has a concrete evidence/activity gap. A project-level Gap can coexist with pathway status Covered when another formal project supplies E evidence.</x:v>
+      </x:c>
+      <x:c r="E10" s="273"/>
+      <x:c r="F10" s="273"/>
+      <x:c r="G10" s="273"/>
+      <x:c r="H10" s="273"/>
+    </x:row>
+    <x:row r="11" ht="52" customHeight="1">
+      <x:c r="A11" s="266" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="B11" s="251" t="str">
+        <x:v>Reviewed limitation</x:v>
+      </x:c>
+      <x:c r="C11" s="252" t="str">
+        <x:v>Coverage is present but incomplete where the original I/P/E code does not fully express the limitation.</x:v>
+      </x:c>
+      <x:c r="E11" s="273"/>
+      <x:c r="F11" s="273"/>
+      <x:c r="G11" s="273"/>
+      <x:c r="H11" s="273"/>
+    </x:row>
+    <x:row r="12" ht="52" customHeight="1">
+      <x:c r="A12" s="266" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="B12" s="251" t="str">
+        <x:v>Not allocated here</x:v>
+      </x:c>
+      <x:c r="C12" s="252" t="str">
+        <x:v>The outcome is intentionally evidenced elsewhere in the sequence, or the project is outside the supplied current formal program; read the adjacent reason.</x:v>
+      </x:c>
+      <x:c r="E12" s="273"/>
+      <x:c r="F12" s="273"/>
+      <x:c r="G12" s="273"/>
+      <x:c r="H12" s="273"/>
+    </x:row>
+    <x:row r="13" ht="52" customHeight="1">
+      <x:c r="A13" s="267" t="str">
+        <x:v>Not yet reviewed</x:v>
+      </x:c>
+      <x:c r="B13" s="254" t="str">
+        <x:v>Evidence not audited</x:v>
+      </x:c>
+      <x:c r="C13" s="255" t="str">
+        <x:v>No conclusion has been made; the adjacent cell identifies what remains to be checked.</x:v>
+      </x:c>
+      <x:c r="E13" s="273"/>
+      <x:c r="F13" s="273"/>
+      <x:c r="G13" s="273"/>
+      <x:c r="H13" s="273"/>
+    </x:row>
+    <x:row r="14" ht="27" customHeight="1">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+    </x:row>
+    <x:row r="15" ht="27" customHeight="1">
+      <x:c r="A15" s="227" t="str">
         <x:v>Stage</x:v>
       </x:c>
-      <x:c r="B13" s="9" t="str">
-        <x:v>Project</x:v>
-      </x:c>
-      <x:c r="C13" s="9" t="str">
-        <x:v>Course position</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="27" customHeight="1">
-      <x:c r="A14" s="70" t="n">
+      <x:c r="B15" s="227" t="str">
+        <x:v>Audited hub project</x:v>
+      </x:c>
+      <x:c r="C15" s="227" t="str">
+        <x:v>Current-program status</x:v>
+      </x:c>
+      <x:c r="E15" s="269" t="str">
+        <x:v>Current-syllabus headline</x:v>
+      </x:c>
+      <x:c r="F15" s="269"/>
+      <x:c r="G15" s="269"/>
+      <x:c r="H15" s="269"/>
+    </x:row>
+    <x:row r="16" ht="32" customHeight="1">
+      <x:c r="A16" s="265" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B14" s="56" t="str">
+      <x:c r="B16" s="275" t="str">
         <x:v>Breadboard</x:v>
       </x:c>
-      <x:c r="C14" s="57" t="str">
-        <x:v>Year 9</x:v>
-      </x:c>
-      <x:c r="E14" s="50" t="str">
-        <x:v>Audit boundaries</x:v>
-      </x:c>
-      <x:c r="F14" s="50" t="str">
-        <x:v>Audit boundaries</x:v>
-      </x:c>
-      <x:c r="G14" s="50" t="str">
-        <x:v>Audit boundaries</x:v>
-      </x:c>
-      <x:c r="H14" s="50" t="str">
-        <x:v>Audit boundaries</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="27" customHeight="1">
-      <x:c r="A15" s="71" t="n">
+      <x:c r="C16" s="276" t="str">
+        <x:v>Year 9 · supplied current program</x:v>
+      </x:c>
+      <x:c r="E16" s="507" t="str">
+        <x:f>"All ten current outcomes are addressed across the two-year pathway: "&amp;COUNTIF('Current Syllabus Summary'!B11:B20,"Covered")&amp;" Covered; "&amp;COUNTIF('Current Syllabus Summary'!B11:B20,"Partially covered")&amp;" Partially covered; "&amp;COUNTIF('Current Syllabus Summary'!B11:B20,"Has gaps")&amp;" Has gaps. IND56 is covered across the pathway; Mirror's local evidence repair awaits publication and live re-audit. IND59 is explicitly evidenced at Clock, with other full outcome lists clarified as course context. Of 77 unique current-program content statements, 75 occur in represented formal projects; two Pen-only lathe statements remain pending a course-sequence decision."</x:f>
+        <x:v>All ten current outcomes are addressed across the two-year pathway: 10 Covered; 0 Partially covered; 0 Has gaps. IND56 is covered across the pathway; Mirror's local evidence repair awaits publication and live re-audit. IND59 is explicitly evidenced at Clock, with other full outcome lists clarified as course context. Of 77 unique current-program content statements, 75 occur in represented formal projects; two Pen-only lathe statements remain pending a course-sequence decision.</x:v>
+      </x:c>
+      <x:c r="F16" s="507"/>
+      <x:c r="G16" s="507"/>
+      <x:c r="H16" s="507"/>
+    </x:row>
+    <x:row r="17" ht="32" customHeight="1">
+      <x:c r="A17" s="292" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B15" s="59" t="str">
+      <x:c r="B17" s="293" t="str">
         <x:v>Small Box</x:v>
       </x:c>
-      <x:c r="C15" s="60" t="str">
-        <x:v>Year 9</x:v>
-      </x:c>
-      <x:c r="E15" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-      <x:c r="F15" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-      <x:c r="G15" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-      <x:c r="H15" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="27" customHeight="1">
-      <x:c r="A16" s="71" t="n">
+      <x:c r="C17" s="294" t="str">
+        <x:v>Year 9 · local addition; outside supplied current program</x:v>
+      </x:c>
+      <x:c r="E17" s="507"/>
+      <x:c r="F17" s="507"/>
+      <x:c r="G17" s="507"/>
+      <x:c r="H17" s="507"/>
+    </x:row>
+    <x:row r="18" ht="32" customHeight="1">
+      <x:c r="A18" s="266" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B16" s="59" t="str">
+      <x:c r="B18" s="278" t="str">
         <x:v>Clock</x:v>
       </x:c>
-      <x:c r="C16" s="60" t="str">
-        <x:v>Year 9</x:v>
-      </x:c>
-      <x:c r="E16" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-      <x:c r="F16" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-      <x:c r="G16" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-      <x:c r="H16" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="27" customHeight="1">
-      <x:c r="A17" s="71" t="n">
+      <x:c r="C18" s="279" t="str">
+        <x:v>Year 9 · supplied current program</x:v>
+      </x:c>
+      <x:c r="E18" s="507"/>
+      <x:c r="F18" s="507"/>
+      <x:c r="G18" s="507"/>
+      <x:c r="H18" s="507"/>
+    </x:row>
+    <x:row r="19" ht="32" customHeight="1">
+      <x:c r="A19" s="266" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B17" s="59" t="str">
+      <x:c r="B19" s="278" t="str">
         <x:v>Tool Carry-all</x:v>
       </x:c>
-      <x:c r="C17" s="60" t="str">
-        <x:v>Year 9</x:v>
-      </x:c>
-      <x:c r="E17" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-      <x:c r="F17" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-      <x:c r="G17" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-      <x:c r="H17" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="27" customHeight="1">
-      <x:c r="A18" s="71" t="n">
+      <x:c r="C19" s="279" t="str">
+        <x:v>Year 9 · supplied current program</x:v>
+      </x:c>
+      <x:c r="E19" s="507"/>
+      <x:c r="F19" s="507"/>
+      <x:c r="G19" s="507"/>
+      <x:c r="H19" s="507"/>
+    </x:row>
+    <x:row r="20" ht="32" customHeight="1">
+      <x:c r="A20" s="266" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B18" s="59" t="str">
+      <x:c r="B20" s="278" t="str">
         <x:v>Mirror</x:v>
       </x:c>
-      <x:c r="C18" s="60" t="str">
-        <x:v>Year 10</x:v>
-      </x:c>
-      <x:c r="E18" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-      <x:c r="F18" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-      <x:c r="G18" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-      <x:c r="H18" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="27" customHeight="1">
-      <x:c r="A19" s="71" t="n">
+      <x:c r="C20" s="279" t="str">
+        <x:v>Year 10 · supplied current program</x:v>
+      </x:c>
+      <x:c r="E20" s="507"/>
+      <x:c r="F20" s="507"/>
+      <x:c r="G20" s="507"/>
+      <x:c r="H20" s="507"/>
+    </x:row>
+    <x:row r="21" ht="32" customHeight="1">
+      <x:c r="A21" s="266" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B19" s="59" t="str">
+      <x:c r="B21" s="278" t="str">
         <x:v>Bedside Table</x:v>
       </x:c>
-      <x:c r="C19" s="60" t="str">
-        <x:v>Year 10</x:v>
-      </x:c>
-      <x:c r="E19" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-      <x:c r="F19" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-      <x:c r="G19" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-      <x:c r="H19" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="27" customHeight="1">
-      <x:c r="A20" s="76" t="n">
+      <x:c r="C21" s="279" t="str">
+        <x:v>Year 10 · supplied current program</x:v>
+      </x:c>
+      <x:c r="E21" s="507"/>
+      <x:c r="F21" s="507"/>
+      <x:c r="G21" s="507"/>
+      <x:c r="H21" s="507"/>
+    </x:row>
+    <x:row r="22" ht="32" customHeight="1">
+      <x:c r="A22" s="298" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B20" s="77" t="str">
+      <x:c r="B22" s="299" t="str">
         <x:v>Folding Chair</x:v>
       </x:c>
-      <x:c r="C20" s="78" t="str">
-        <x:v>Year 10 - developing option</x:v>
-      </x:c>
-      <x:c r="E20" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-      <x:c r="F20" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-      <x:c r="G20" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
-      <x:c r="H20" s="81" t="str">
-        <x:v>Key findings: practical process, safety, communication and evaluation evidence are generally strong. Collaboration is usually practised but seldom captured as inspectable participant evidence. Several landing pages claim IND5-9 without a dedicated emerging-technology activity; Clock and Folding Chair provide the clearest explicit technology evidence. Mirror's 20 week links were repaired to the existing support pages on 1 August 2026. Small Box has no linked plan. Small Box and Folding Chair remain outside the supplied future master program and are addressed through clearly labelled local additions.</x:v>
-      </x:c>
+      <x:c r="C22" s="300" t="str">
+        <x:v>Year 10 · local developing option; outside supplied current program</x:v>
+      </x:c>
+      <x:c r="E22" s="507"/>
+      <x:c r="F22" s="507"/>
+      <x:c r="G22" s="507"/>
+      <x:c r="H22" s="507"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="A3:H4"/>
     <x:mergeCell ref="E6:H6"/>
-    <x:mergeCell ref="E7:H12"/>
-    <x:mergeCell ref="E14:H14"/>
-    <x:mergeCell ref="E15:H20"/>
+    <x:mergeCell ref="E7:H13"/>
+    <x:mergeCell ref="E15:H15"/>
+    <x:mergeCell ref="E16:H22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1334,19 +2667,19 @@
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="52" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="38" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="11" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="27" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="11" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="27" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="11" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="27" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="11" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="27" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="11" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="27" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="11" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="27" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="11" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="16" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="27" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -1463,116 +2796,46 @@
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="B3" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="G3" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="I3" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="J3" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="K3" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="L3" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="M3" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="N3" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="O3" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="P3" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="Q3" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="R3" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
+      <x:c r="A3" s="306" t="str">
+        <x:v>Current program rows 7–16 use the supplied stage_5_timber_2021-06-16.docx outcome wording and explicit project states. Coverage is judged across the full two-year sequence: I → P → E should deepen with project complexity, and a project-level Gap can coexist with pathway Covered when another formal project supplies E. Small Box and Folding Chair are local additions excluded from the formal-current status formula. Future/new-syllabus rows 17–25 are reference only and do not determine the current result.</x:v>
+      </x:c>
+      <x:c r="B3" s="306"/>
+      <x:c r="C3" s="306"/>
+      <x:c r="D3" s="306"/>
+      <x:c r="E3" s="306"/>
+      <x:c r="F3" s="306"/>
+      <x:c r="G3" s="306"/>
+      <x:c r="H3" s="306"/>
+      <x:c r="I3" s="306"/>
+      <x:c r="J3" s="306"/>
+      <x:c r="K3" s="306"/>
+      <x:c r="L3" s="306"/>
+      <x:c r="M3" s="306"/>
+      <x:c r="N3" s="306"/>
+      <x:c r="O3" s="306"/>
+      <x:c r="P3" s="306"/>
+      <x:c r="Q3" s="306"/>
+      <x:c r="R3" s="306"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="B4" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="C4" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="D4" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="E4" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="F4" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="G4" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="H4" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="I4" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="J4" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="K4" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="L4" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="M4" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="N4" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="O4" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="P4" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="Q4" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
-      <x:c r="R4" s="7" t="str">
-        <x:v>Completed cross-reference between current IND outcomes, future-program primary codes and the live project webpages. A blank code means no supported mapping; read the adjacent reference for the reason. Future code descriptions remain deliberately unexpanded because the supplied program lists codes rather than authoritative descriptions.</x:v>
-      </x:c>
+      <x:c r="A4" s="306"/>
+      <x:c r="B4" s="306"/>
+      <x:c r="C4" s="306"/>
+      <x:c r="D4" s="306"/>
+      <x:c r="E4" s="306"/>
+      <x:c r="F4" s="306"/>
+      <x:c r="G4" s="306"/>
+      <x:c r="H4" s="306"/>
+      <x:c r="I4" s="306"/>
+      <x:c r="J4" s="306"/>
+      <x:c r="K4" s="306"/>
+      <x:c r="L4" s="306"/>
+      <x:c r="M4" s="306"/>
+      <x:c r="N4" s="306"/>
+      <x:c r="O4" s="306"/>
+      <x:c r="P4" s="306"/>
+      <x:c r="Q4" s="306"/>
+      <x:c r="R4" s="306"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="85" t="str">
@@ -1592,7 +2855,7 @@
       </x:c>
       <x:c r="F5" s="85"/>
       <x:c r="G5" s="85" t="str">
-        <x:v>Stage 2 - Small Box</x:v>
+        <x:v>Stage 2 - Small Box · local addition</x:v>
       </x:c>
       <x:c r="H5" s="85"/>
       <x:c r="I5" s="85" t="str">
@@ -1612,7 +2875,7 @@
       </x:c>
       <x:c r="P5" s="85"/>
       <x:c r="Q5" s="85" t="str">
-        <x:v>Stage 7 - Folding Chair</x:v>
+        <x:v>Stage 7 - Folding Chair · local developing option</x:v>
       </x:c>
       <x:c r="R5" s="85"/>
     </x:row>
@@ -1664,7 +2927,7 @@
         <x:v>Webpage / module reference</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="58" customHeight="1">
+    <x:row r="7" ht="66" customHeight="1">
       <x:c r="A7" s="86" t="str">
         <x:v>Current program</x:v>
       </x:c>
@@ -1720,7 +2983,7 @@
         <x:v>Weeks 1-2 risk controls; Weeks 7-8 WMS; Weeks 15-16 SDS evidence.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="58" customHeight="1">
+    <x:row r="8" ht="66" customHeight="1">
       <x:c r="A8" s="88" t="str">
         <x:v>Current program</x:v>
       </x:c>
@@ -1739,9 +3002,11 @@
       <x:c r="F8" s="113" t="str">
         <x:v>Module 02 layout/profile decisions and folio plans; modification is not explicit.</x:v>
       </x:c>
-      <x:c r="G8" s="110" t="str"/>
+      <x:c r="G8" s="308" t="str">
+        <x:v>Gap</x:v>
+      </x:c>
       <x:c r="H8" s="113" t="str">
-        <x:v>Gap - brief is introduced in Weeks 1-2, but no explicit design-development task was found.</x:v>
+        <x:v>Local addition outside the supplied formal program; no explicit design-development evidence was found. Excluded from formal-current status (SCOPE-02).</x:v>
       </x:c>
       <x:c r="I8" s="110" t="str">
         <x:v>E</x:v>
@@ -1774,7 +3039,7 @@
         <x:v>Weeks 1-2 approved variation; Weeks 9-10 design-criteria responses.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="58" customHeight="1">
+    <x:row r="9" ht="66" customHeight="1">
       <x:c r="A9" s="88" t="str">
         <x:v>Current program</x:v>
       </x:c>
@@ -1830,7 +3095,7 @@
         <x:v>Weeks 3-16 timber, mortiser, bandsaw, joinery, pivot assembly and finish.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="58" customHeight="1">
+    <x:row r="10" ht="66" customHeight="1">
       <x:c r="A10" s="88" t="str">
         <x:v>Current program</x:v>
       </x:c>
@@ -1886,7 +3151,7 @@
         <x:v>Weeks 3-4 timber selection, defects and cutting-list responses.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="58" customHeight="1">
+    <x:row r="11" ht="66" customHeight="1">
       <x:c r="A11" s="88" t="str">
         <x:v>Current program</x:v>
       </x:c>
@@ -1942,7 +3207,7 @@
         <x:v>Weeks 9-10 drawing/CAD communication and Weeks 17-18 folio evidence.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="58" customHeight="1">
+    <x:row r="12" ht="66" customHeight="1">
       <x:c r="A12" s="88" t="str">
         <x:v>Current program</x:v>
       </x:c>
@@ -1955,46 +3220,50 @@
       <x:c r="D12" s="89" t="str">
         <x:v>stage_5_timber_2021-06-16.docx - Outcomes</x:v>
       </x:c>
-      <x:c r="E12" s="110" t="str">
-        <x:v>P</x:v>
+      <x:c r="E12" s="493" t="str">
+        <x:v>E</x:v>
       </x:c>
       <x:c r="F12" s="113" t="str">
-        <x:v>Module 05 workshop handover/shared-space practice; no collaborator evidence field.</x:v>
-      </x:c>
-      <x:c r="G12" s="110" t="str"/>
+        <x:v>Module 05 activity 1 — saved peer feedback given/received, one improvement and a result check. Live verified 2026-08-02 at https://stevencowell.github.io/bread-board-guided-course/modules/module-05.html (S18).</x:v>
+      </x:c>
+      <x:c r="G12" s="308" t="str">
+        <x:v>Gap</x:v>
+      </x:c>
       <x:c r="H12" s="113" t="str">
-        <x:v>Gap - landing-page claim only; no explicit collaborative activity or evidence field found.</x:v>
+        <x:v>Local addition; see SCOPE-02.</x:v>
       </x:c>
       <x:c r="I12" s="110" t="str">
         <x:v>P</x:v>
       </x:c>
       <x:c r="J12" s="113" t="str">
-        <x:v>Weeks 5-6 shared-equipment/housekeeping response; participation is not directly captured.</x:v>
+        <x:v>Weeks 5–6 shared-equipment/housekeeping response (CUR-01).</x:v>
       </x:c>
       <x:c r="K12" s="110" t="str">
         <x:v>P</x:v>
       </x:c>
       <x:c r="L12" s="113" t="str">
-        <x:v>Weeks 15-16 team-lift and communication practice; no collaborator evidence field.</x:v>
-      </x:c>
-      <x:c r="M12" s="110" t="str"/>
+        <x:v>Weeks 15–16 team-lift and communication practice (CUR-01).</x:v>
+      </x:c>
+      <x:c r="M12" s="522" t="str">
+        <x:v>E</x:v>
+      </x:c>
       <x:c r="N12" s="113" t="str">
-        <x:v>Gap - landing-page claim only; no explicit collaborative activity or evidence field found.</x:v>
-      </x:c>
-      <x:c r="O12" s="110" t="str">
-        <x:v>P</x:v>
+        <x:v>Local implementation 2026-08-02 - Mirror Portfolio Workbook, Peer Quality Check and Workshop Handover. Captures roles, criterion/evidence, feedback, justified decision, result check and handover contribution. Local QA complete; publication and live re-audit pending (S19).</x:v>
+      </x:c>
+      <x:c r="O12" s="493" t="str">
+        <x:v>E</x:v>
       </x:c>
       <x:c r="P12" s="113" t="str">
-        <x:v>Weeks 19-20 shared-workshop handover; no explicit collaborative evidence field.</x:v>
+        <x:v>Weeks 19–20 response 1 — saved peer QA critique, justified decision, before/after evidence and workshop handover roles. Live verified 2026-08-02 at https://stevencowell.github.io/bedside-table-guided-course/weeks19-20/ (S18).</x:v>
       </x:c>
       <x:c r="Q12" s="110" t="str">
         <x:v>P</x:v>
       </x:c>
       <x:c r="R12" s="116" t="str">
-        <x:v>Weeks 1-2 teacher/partner check; collaborator role and contribution are not captured.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="58" customHeight="1">
+        <x:v>Weeks 1–2 teacher/partner check; local developing option (SCOPE-02).</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="66" customHeight="1">
       <x:c r="A13" s="88" t="str">
         <x:v>Current program</x:v>
       </x:c>
@@ -2050,7 +3319,7 @@
         <x:v>Weeks 19-20 final reflection requires transferable learning and future application.</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="58" customHeight="1">
+    <x:row r="14" ht="66" customHeight="1">
       <x:c r="A14" s="88" t="str">
         <x:v>Current program</x:v>
       </x:c>
@@ -2106,7 +3375,7 @@
         <x:v>Weeks 17-18 criterion-based product evaluation and folio evidence.</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="58" customHeight="1">
+    <x:row r="15" ht="66" customHeight="1">
       <x:c r="A15" s="88" t="str">
         <x:v>Current program</x:v>
       </x:c>
@@ -2119,13 +3388,17 @@
       <x:c r="D15" s="89" t="str">
         <x:v>stage_5_timber_2021-06-16.docx - Outcomes</x:v>
       </x:c>
-      <x:c r="E15" s="110" t="str"/>
+      <x:c r="E15" s="524" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
       <x:c r="F15" s="113" t="str">
-        <x:v>Gap - outcome appears on landing page, but no explicit emerging-technology activity was found.</x:v>
-      </x:c>
-      <x:c r="G15" s="110" t="str"/>
+        <x:v>Breadboard displays the course outcome list as context, not as a separate project-level IND59 assessment claim. Clock Weeks 15-16 remains the formal current-program E evidence for IND59; see Current Syllabus Summary IND59 and S19 local wording clarification.</x:v>
+      </x:c>
+      <x:c r="G15" s="308" t="str">
+        <x:v>Gap</x:v>
+      </x:c>
       <x:c r="H15" s="113" t="str">
-        <x:v>Gap - no explicit current, new or emerging-technology learning activity was found.</x:v>
+        <x:v>Local addition outside the supplied formal program; no inspectable IND59 evidence was found. Excluded from formal-current status (SCOPE-02).</x:v>
       </x:c>
       <x:c r="I15" s="110" t="str">
         <x:v>E</x:v>
@@ -2139,13 +3412,17 @@
       <x:c r="L15" s="113" t="str">
         <x:v>Weeks 3-4 compares traditional and industrial timber production; no emerging-tech task.</x:v>
       </x:c>
-      <x:c r="M15" s="110" t="str"/>
+      <x:c r="M15" s="524" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
       <x:c r="N15" s="113" t="str">
-        <x:v>Gap - outcome appears on landing page, but no explicit emerging-technology activity was found.</x:v>
-      </x:c>
-      <x:c r="O15" s="110" t="str"/>
+        <x:v>Mirror displays the course outcome list as context, not as a separate project-level IND59 assessment claim. Clock Weeks 15-16 remains the formal current-program E evidence for IND59; see Current Syllabus Summary IND59 and S19 local wording clarification.</x:v>
+      </x:c>
+      <x:c r="O15" s="524" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
       <x:c r="P15" s="113" t="str">
-        <x:v>Gap - outcome appears on landing page, but no explicit emerging-technology activity was found.</x:v>
+        <x:v>Bedside Table displays the course outcome list as context, not as a separate project-level IND59 assessment claim. Clock Weeks 15-16 remains the formal current-program E evidence for IND59; see Current Syllabus Summary IND59 and S19 local wording clarification.</x:v>
       </x:c>
       <x:c r="Q15" s="110" t="str">
         <x:v>E</x:v>
@@ -2154,7 +3431,7 @@
         <x:v>Weeks 9-10 CAD workflow, constraints, revision control and verification response.</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="58" customHeight="1">
+    <x:row r="16" ht="66" customHeight="1">
       <x:c r="A16" s="88" t="str">
         <x:v>Current program</x:v>
       </x:c>
@@ -2210,457 +3487,507 @@
         <x:v>Weeks 15-16 sustainability/lifecycle response and Weeks 13-14 industry-quality context.</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="58" customHeight="1">
-      <x:c r="A17" s="90" t="str">
+    <x:row r="17" ht="54" customHeight="1">
+      <x:c r="A17" s="313" t="str">
         <x:v>Future / new syllabus</x:v>
       </x:c>
-      <x:c r="B17" s="91" t="str">
+      <x:c r="B17" s="314" t="str">
         <x:v>INT5-SAF-01</x:v>
       </x:c>
-      <x:c r="C17" s="91" t="str">
+      <x:c r="C17" s="314" t="str">
         <x:v>Primary outcome code listed in the supplied future program; authoritative description not supplied in the reviewed documents.</x:v>
       </x:c>
-      <x:c r="D17" s="91" t="str">
+      <x:c r="D17" s="314" t="str">
         <x:v>2025 Timber program new syllabus.docx - Primary outcomes</x:v>
       </x:c>
-      <x:c r="E17" s="110" t="str">
+      <x:c r="E17" s="315" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="F17" s="113" t="str">
+      <x:c r="F17" s="316" t="str">
         <x:v>Program primary outcome; Module 01 and folio safety evidence.</x:v>
       </x:c>
-      <x:c r="G17" s="110" t="str"/>
-      <x:c r="H17" s="113" t="str">
+      <x:c r="G17" s="317" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="H17" s="316" t="str">
         <x:v>Not mapped - project is not named in the supplied future program.</x:v>
       </x:c>
-      <x:c r="I17" s="110" t="str"/>
-      <x:c r="J17" s="113" t="str">
+      <x:c r="I17" s="317" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="J17" s="316" t="str">
         <x:v>Not listed as a Clock primary outcome; the webpage nevertheless contains safety/WMS evidence.</x:v>
       </x:c>
-      <x:c r="K17" s="110" t="str"/>
-      <x:c r="L17" s="113" t="str">
+      <x:c r="K17" s="317" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="L17" s="316" t="str">
         <x:v>Not listed as a Carry-all primary outcome; the webpage nevertheless contains SWMS evidence.</x:v>
       </x:c>
-      <x:c r="M17" s="110" t="str"/>
-      <x:c r="N17" s="113" t="str">
+      <x:c r="M17" s="317" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N17" s="316" t="str">
         <x:v>Not listed as a Mirror primary outcome; the webpage nevertheless contains safety evidence.</x:v>
       </x:c>
-      <x:c r="O17" s="110" t="str">
+      <x:c r="O17" s="315" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="P17" s="113" t="str">
+      <x:c r="P17" s="316" t="str">
         <x:v>Program primary outcome; Weeks 1-2 and 15-16 safety/SDS evidence.</x:v>
       </x:c>
-      <x:c r="Q17" s="110" t="str"/>
-      <x:c r="R17" s="116" t="str">
+      <x:c r="Q17" s="317" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="R17" s="318" t="str">
         <x:v>Not mapped - Folding Chair is a provisional/developing option outside the supplied formal program.</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="58" customHeight="1">
-      <x:c r="A18" s="90" t="str">
+    <x:row r="18" ht="54" customHeight="1">
+      <x:c r="A18" s="319" t="str">
         <x:v>Future / new syllabus</x:v>
       </x:c>
-      <x:c r="B18" s="91" t="str">
+      <x:c r="B18" s="320" t="str">
         <x:v>INT5-USE-01</x:v>
       </x:c>
-      <x:c r="C18" s="91" t="str">
+      <x:c r="C18" s="320" t="str">
         <x:v>Primary outcome code listed in the supplied future program; authoritative description not supplied in the reviewed documents.</x:v>
       </x:c>
-      <x:c r="D18" s="91" t="str">
+      <x:c r="D18" s="320" t="str">
         <x:v>2025 Timber program new syllabus.docx - Primary outcomes</x:v>
       </x:c>
-      <x:c r="E18" s="110" t="str">
+      <x:c r="E18" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="F18" s="113" t="str">
+      <x:c r="F18" s="322" t="str">
         <x:v>Program primary outcome; Modules 02-04 and practical folio checkpoints.</x:v>
       </x:c>
-      <x:c r="G18" s="110" t="str"/>
-      <x:c r="H18" s="113" t="str">
+      <x:c r="G18" s="323" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="H18" s="322" t="str">
         <x:v>Not mapped - project is not named in the supplied future program.</x:v>
       </x:c>
-      <x:c r="I18" s="110" t="str">
+      <x:c r="I18" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="J18" s="113" t="str">
+      <x:c r="J18" s="322" t="str">
         <x:v>Program primary outcome; Weeks 5-14 process and tool-use responses.</x:v>
       </x:c>
-      <x:c r="K18" s="110" t="str">
+      <x:c r="K18" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="L18" s="113" t="str">
+      <x:c r="L18" s="322" t="str">
         <x:v>Program primary outcome; Weeks 5-18 process and tool-use responses.</x:v>
       </x:c>
-      <x:c r="M18" s="110" t="str">
+      <x:c r="M18" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="N18" s="113" t="str">
+      <x:c r="N18" s="322" t="str">
         <x:v>Program primary outcome; marking, joinery, routing and finishing activities.</x:v>
       </x:c>
-      <x:c r="O18" s="110" t="str">
+      <x:c r="O18" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="P18" s="113" t="str">
+      <x:c r="P18" s="322" t="str">
         <x:v>Program primary outcome; Weeks 3-16 process and tool-use responses.</x:v>
       </x:c>
-      <x:c r="Q18" s="110" t="str"/>
-      <x:c r="R18" s="116" t="str">
+      <x:c r="Q18" s="323" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="R18" s="324" t="str">
         <x:v>Not mapped - Folding Chair is a provisional/developing option outside the supplied formal program.</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="58" customHeight="1">
-      <x:c r="A19" s="90" t="str">
+    <x:row r="19" ht="54" customHeight="1">
+      <x:c r="A19" s="319" t="str">
         <x:v>Future / new syllabus</x:v>
       </x:c>
-      <x:c r="B19" s="91" t="str">
+      <x:c r="B19" s="320" t="str">
         <x:v>INT5-PRO-01</x:v>
       </x:c>
-      <x:c r="C19" s="91" t="str">
+      <x:c r="C19" s="320" t="str">
         <x:v>Primary outcome code listed in the supplied future program; authoritative description not supplied in the reviewed documents.</x:v>
       </x:c>
-      <x:c r="D19" s="91" t="str">
+      <x:c r="D19" s="320" t="str">
         <x:v>2025 Timber program new syllabus.docx - Primary outcomes</x:v>
       </x:c>
-      <x:c r="E19" s="110" t="str">
+      <x:c r="E19" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="F19" s="113" t="str">
+      <x:c r="F19" s="322" t="str">
         <x:v>Program primary outcome; staged making sequence and 12-point folio.</x:v>
       </x:c>
-      <x:c r="G19" s="110" t="str"/>
-      <x:c r="H19" s="113" t="str">
+      <x:c r="G19" s="323" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="H19" s="322" t="str">
         <x:v>Not mapped - project is not named in the supplied future program.</x:v>
       </x:c>
-      <x:c r="I19" s="110" t="str">
+      <x:c r="I19" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="J19" s="113" t="str">
+      <x:c r="J19" s="322" t="str">
         <x:v>Program primary outcome; staged production modules and folio.</x:v>
       </x:c>
-      <x:c r="K19" s="110" t="str">
+      <x:c r="K19" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="L19" s="113" t="str">
+      <x:c r="L19" s="322" t="str">
         <x:v>Program primary outcome; staged production modules and folio.</x:v>
       </x:c>
-      <x:c r="M19" s="110" t="str">
+      <x:c r="M19" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="N19" s="113" t="str">
+      <x:c r="N19" s="322" t="str">
         <x:v>Program primary outcome; process activities, portfolio and folio.</x:v>
       </x:c>
-      <x:c r="O19" s="110" t="str">
+      <x:c r="O19" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="P19" s="113" t="str">
+      <x:c r="P19" s="322" t="str">
         <x:v>Program primary outcome; staged production modules and folio.</x:v>
       </x:c>
-      <x:c r="Q19" s="110" t="str"/>
-      <x:c r="R19" s="116" t="str">
+      <x:c r="Q19" s="323" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="R19" s="324" t="str">
         <x:v>Not mapped - Folding Chair is a provisional/developing option outside the supplied formal program.</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="58" customHeight="1">
-      <x:c r="A20" s="90" t="str">
+    <x:row r="20" ht="54" customHeight="1">
+      <x:c r="A20" s="319" t="str">
         <x:v>Future / new syllabus</x:v>
       </x:c>
-      <x:c r="B20" s="91" t="str">
+      <x:c r="B20" s="320" t="str">
         <x:v>INT5-DES-01</x:v>
       </x:c>
-      <x:c r="C20" s="91" t="str">
+      <x:c r="C20" s="320" t="str">
         <x:v>Primary outcome code listed in the supplied future program; authoritative description not supplied in the reviewed documents.</x:v>
       </x:c>
-      <x:c r="D20" s="91" t="str">
+      <x:c r="D20" s="320" t="str">
         <x:v>2025 Timber program new syllabus.docx - Primary outcomes</x:v>
       </x:c>
-      <x:c r="E20" s="110" t="str">
+      <x:c r="E20" s="321" t="str">
         <x:v>P</x:v>
       </x:c>
-      <x:c r="F20" s="113" t="str">
+      <x:c r="F20" s="322" t="str">
         <x:v>Program primary outcome; layout/profile choices are practised, but development evidence is limited.</x:v>
       </x:c>
-      <x:c r="G20" s="110" t="str"/>
-      <x:c r="H20" s="113" t="str">
+      <x:c r="G20" s="323" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="H20" s="322" t="str">
         <x:v>Not mapped - project is not named in the supplied future program.</x:v>
       </x:c>
-      <x:c r="I20" s="110" t="str">
+      <x:c r="I20" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="J20" s="113" t="str">
+      <x:c r="J20" s="322" t="str">
         <x:v>Program primary outcome; Weeks 15-16 design-principles response.</x:v>
       </x:c>
-      <x:c r="K20" s="110" t="str">
+      <x:c r="K20" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="L20" s="113" t="str">
+      <x:c r="L20" s="322" t="str">
         <x:v>Program primary outcome; Weeks 11-12 handle design response.</x:v>
       </x:c>
-      <x:c r="M20" s="110" t="str">
+      <x:c r="M20" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="N20" s="113" t="str">
+      <x:c r="N20" s="322" t="str">
         <x:v>Program primary outcome; design activities and portfolio evidence.</x:v>
       </x:c>
-      <x:c r="O20" s="110" t="str">
+      <x:c r="O20" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="P20" s="113" t="str">
+      <x:c r="P20" s="322" t="str">
         <x:v>Program primary outcome; Weeks 1-2 design response.</x:v>
       </x:c>
-      <x:c r="Q20" s="110" t="str"/>
-      <x:c r="R20" s="116" t="str">
+      <x:c r="Q20" s="323" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="R20" s="324" t="str">
         <x:v>Not mapped - Folding Chair is a provisional/developing option outside the supplied formal program.</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="58" customHeight="1">
-      <x:c r="A21" s="90" t="str">
+    <x:row r="21" ht="54" customHeight="1">
+      <x:c r="A21" s="319" t="str">
         <x:v>Future / new syllabus</x:v>
       </x:c>
-      <x:c r="B21" s="91" t="str">
+      <x:c r="B21" s="320" t="str">
         <x:v>INT5-COM-01</x:v>
       </x:c>
-      <x:c r="C21" s="91" t="str">
+      <x:c r="C21" s="320" t="str">
         <x:v>Primary outcome code listed in the supplied future program; authoritative description not supplied in the reviewed documents.</x:v>
       </x:c>
-      <x:c r="D21" s="91" t="str">
+      <x:c r="D21" s="320" t="str">
         <x:v>2025 Timber program new syllabus.docx - Primary outcomes</x:v>
       </x:c>
-      <x:c r="E21" s="110" t="str">
+      <x:c r="E21" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="F21" s="113" t="str">
+      <x:c r="F21" s="322" t="str">
         <x:v>Program primary outcome; annotated photo/caption folio and PDF output.</x:v>
       </x:c>
-      <x:c r="G21" s="110" t="str"/>
-      <x:c r="H21" s="113" t="str">
+      <x:c r="G21" s="323" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="H21" s="322" t="str">
         <x:v>Not mapped - project is not named in the supplied future program.</x:v>
       </x:c>
-      <x:c r="I21" s="110" t="str">
+      <x:c r="I21" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="J21" s="113" t="str">
+      <x:c r="J21" s="322" t="str">
         <x:v>Program primary outcome; drawing, captions and printable folio.</x:v>
       </x:c>
-      <x:c r="K21" s="110" t="str">
+      <x:c r="K21" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="L21" s="113" t="str">
+      <x:c r="L21" s="322" t="str">
         <x:v>Program primary outcome; orthogonal drawing, captions and folio.</x:v>
       </x:c>
-      <x:c r="M21" s="110" t="str">
+      <x:c r="M21" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="N21" s="113" t="str">
+      <x:c r="N21" s="322" t="str">
         <x:v>Program primary outcome; portfolio workbook, quizzes and folio.</x:v>
       </x:c>
-      <x:c r="O21" s="110" t="str">
+      <x:c r="O21" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="P21" s="113" t="str">
+      <x:c r="P21" s="322" t="str">
         <x:v>Program primary outcome; evidence selection, captions and folio.</x:v>
       </x:c>
-      <x:c r="Q21" s="110" t="str"/>
-      <x:c r="R21" s="116" t="str">
+      <x:c r="Q21" s="323" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="R21" s="324" t="str">
         <x:v>Not mapped - Folding Chair is a provisional/developing option outside the supplied formal program.</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="58" customHeight="1">
-      <x:c r="A22" s="90" t="str">
+    <x:row r="22" ht="54" customHeight="1">
+      <x:c r="A22" s="319" t="str">
         <x:v>Future / new syllabus</x:v>
       </x:c>
-      <x:c r="B22" s="91" t="str">
+      <x:c r="B22" s="320" t="str">
         <x:v>INT5-EVL-01</x:v>
       </x:c>
-      <x:c r="C22" s="91" t="str">
+      <x:c r="C22" s="320" t="str">
         <x:v>Primary outcome code listed in the supplied future program; authoritative description not supplied in the reviewed documents.</x:v>
       </x:c>
-      <x:c r="D22" s="91" t="str">
+      <x:c r="D22" s="320" t="str">
         <x:v>2025 Timber program new syllabus.docx - Primary outcomes</x:v>
       </x:c>
-      <x:c r="E22" s="110" t="str">
+      <x:c r="E22" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="F22" s="113" t="str">
+      <x:c r="F22" s="322" t="str">
         <x:v>Program primary outcome; Module 05 and folio evaluation.</x:v>
       </x:c>
-      <x:c r="G22" s="110" t="str"/>
-      <x:c r="H22" s="113" t="str">
+      <x:c r="G22" s="323" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="H22" s="322" t="str">
         <x:v>Not mapped - project is not named in the supplied future program.</x:v>
       </x:c>
-      <x:c r="I22" s="110" t="str">
+      <x:c r="I22" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="J22" s="113" t="str">
+      <x:c r="J22" s="322" t="str">
         <x:v>Program primary outcome; Weeks 17-20 PMI and QA evidence.</x:v>
       </x:c>
-      <x:c r="K22" s="110" t="str">
+      <x:c r="K22" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="L22" s="113" t="str">
+      <x:c r="L22" s="322" t="str">
         <x:v>Program primary outcome; Weeks 19-20 PMI and correction evidence.</x:v>
       </x:c>
-      <x:c r="M22" s="110" t="str">
+      <x:c r="M22" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="N22" s="113" t="str">
+      <x:c r="N22" s="322" t="str">
         <x:v>Program primary outcome; evaluation activities and portfolio response.</x:v>
       </x:c>
-      <x:c r="O22" s="110" t="str">
+      <x:c r="O22" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="P22" s="113" t="str">
+      <x:c r="P22" s="322" t="str">
         <x:v>Program primary outcome; Weeks 17-20 evaluation and reflection.</x:v>
       </x:c>
-      <x:c r="Q22" s="110" t="str"/>
-      <x:c r="R22" s="116" t="str">
+      <x:c r="Q22" s="323" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="R22" s="324" t="str">
         <x:v>Not mapped - Folding Chair is a provisional/developing option outside the supplied formal program.</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="58" customHeight="1">
-      <x:c r="A23" s="90" t="str">
+    <x:row r="23" ht="54" customHeight="1">
+      <x:c r="A23" s="319" t="str">
         <x:v>Future / new syllabus</x:v>
       </x:c>
-      <x:c r="B23" s="91" t="str">
+      <x:c r="B23" s="320" t="str">
         <x:v>INT5-INP-01</x:v>
       </x:c>
-      <x:c r="C23" s="91" t="str">
+      <x:c r="C23" s="320" t="str">
         <x:v>Primary outcome code listed in the supplied future program; authoritative description not supplied in the reviewed documents.</x:v>
       </x:c>
-      <x:c r="D23" s="91" t="str">
+      <x:c r="D23" s="320" t="str">
         <x:v>2025 Timber program new syllabus.docx - Primary outcomes</x:v>
       </x:c>
-      <x:c r="E23" s="110" t="str"/>
-      <x:c r="F23" s="113" t="str">
+      <x:c r="E23" s="323" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="F23" s="322" t="str">
         <x:v>Code is not listed as a primary outcome for this project in the supplied future program.</x:v>
       </x:c>
-      <x:c r="G23" s="110" t="str"/>
-      <x:c r="H23" s="113" t="str">
+      <x:c r="G23" s="323" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="H23" s="322" t="str">
         <x:v>Not mapped - project is not named in the supplied future program.</x:v>
       </x:c>
-      <x:c r="I23" s="110" t="str">
+      <x:c r="I23" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="J23" s="113" t="str">
+      <x:c r="J23" s="322" t="str">
         <x:v>Program primary outcome; planning, cutting list, WMS and production evidence.</x:v>
       </x:c>
-      <x:c r="K23" s="110" t="str">
+      <x:c r="K23" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="L23" s="113" t="str">
+      <x:c r="L23" s="322" t="str">
         <x:v>Program primary outcome; planning, sequencing and production evidence.</x:v>
       </x:c>
-      <x:c r="M23" s="110" t="str">
+      <x:c r="M23" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="N23" s="113" t="str">
+      <x:c r="N23" s="322" t="str">
         <x:v>Program primary outcome; plan-and-prepare and portfolio process evidence.</x:v>
       </x:c>
-      <x:c r="O23" s="110" t="str">
+      <x:c r="O23" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="P23" s="113" t="str">
+      <x:c r="P23" s="322" t="str">
         <x:v>Program primary outcome; planning, sequencing and production evidence.</x:v>
       </x:c>
-      <x:c r="Q23" s="110" t="str"/>
-      <x:c r="R23" s="116" t="str">
+      <x:c r="Q23" s="323" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="R23" s="324" t="str">
         <x:v>Not mapped - Folding Chair is a provisional/developing option outside the supplied formal program.</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="58" customHeight="1">
-      <x:c r="A24" s="90" t="str">
+    <x:row r="24" ht="54" customHeight="1">
+      <x:c r="A24" s="319" t="str">
         <x:v>Future / new syllabus</x:v>
       </x:c>
-      <x:c r="B24" s="91" t="str">
+      <x:c r="B24" s="320" t="str">
         <x:v>INT5-ENV-01</x:v>
       </x:c>
-      <x:c r="C24" s="91" t="str">
+      <x:c r="C24" s="320" t="str">
         <x:v>Primary outcome code listed in the supplied future program; authoritative description not supplied in the reviewed documents.</x:v>
       </x:c>
-      <x:c r="D24" s="91" t="str">
+      <x:c r="D24" s="320" t="str">
         <x:v>2025 Timber program new syllabus.docx - Primary outcomes</x:v>
       </x:c>
-      <x:c r="E24" s="110" t="str"/>
-      <x:c r="F24" s="113" t="str">
+      <x:c r="E24" s="323" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="F24" s="322" t="str">
         <x:v>Not listed as a Breadboard primary outcome; Module 04 does contain sustainability evidence.</x:v>
       </x:c>
-      <x:c r="G24" s="110" t="str"/>
-      <x:c r="H24" s="113" t="str">
+      <x:c r="G24" s="323" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="H24" s="322" t="str">
         <x:v>Not mapped - project is not named in the supplied future program.</x:v>
       </x:c>
-      <x:c r="I24" s="110" t="str">
+      <x:c r="I24" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="J24" s="113" t="str">
+      <x:c r="J24" s="322" t="str">
         <x:v>Program primary outcome; waste, material responsibility and folio sustainability evidence.</x:v>
       </x:c>
-      <x:c r="K24" s="110" t="str">
+      <x:c r="K24" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="L24" s="113" t="str">
+      <x:c r="L24" s="322" t="str">
         <x:v>Program primary outcome; Weeks 3-4 responsible-use response.</x:v>
       </x:c>
-      <x:c r="M24" s="110" t="str">
+      <x:c r="M24" s="321" t="str">
         <x:v>P</x:v>
       </x:c>
-      <x:c r="N24" s="113" t="str">
+      <x:c r="N24" s="322" t="str">
         <x:v>Program primary outcome; sustainability is taught, but the evidence path is less explicit.</x:v>
       </x:c>
-      <x:c r="O24" s="110" t="str">
+      <x:c r="O24" s="321" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="P24" s="113" t="str">
+      <x:c r="P24" s="322" t="str">
         <x:v>Program primary outcome; Weeks 15-16 lifecycle-impact response.</x:v>
       </x:c>
-      <x:c r="Q24" s="110" t="str"/>
-      <x:c r="R24" s="116" t="str">
+      <x:c r="Q24" s="323" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="R24" s="324" t="str">
         <x:v>Not mapped - Folding Chair is a provisional/developing option outside the supplied formal program.</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="58" customHeight="1">
-      <x:c r="A25" s="92" t="str">
+    <x:row r="25" ht="54" customHeight="1">
+      <x:c r="A25" s="325" t="str">
         <x:v>Future / new syllabus</x:v>
       </x:c>
-      <x:c r="B25" s="93" t="str">
+      <x:c r="B25" s="326" t="str">
         <x:v>INT5-IND-01</x:v>
       </x:c>
-      <x:c r="C25" s="93" t="str">
+      <x:c r="C25" s="326" t="str">
         <x:v>Primary outcome code listed in the supplied future program; authoritative description not supplied in the reviewed documents.</x:v>
       </x:c>
-      <x:c r="D25" s="93" t="str">
+      <x:c r="D25" s="326" t="str">
         <x:v>2025 Timber program new syllabus.docx - Primary outcomes</x:v>
       </x:c>
-      <x:c r="E25" s="111" t="str"/>
-      <x:c r="F25" s="114" t="str">
+      <x:c r="E25" s="327" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="F25" s="328" t="str">
         <x:v>Code is not listed as a primary outcome for this project in the supplied future program.</x:v>
       </x:c>
-      <x:c r="G25" s="111" t="str"/>
-      <x:c r="H25" s="114" t="str">
+      <x:c r="G25" s="327" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="H25" s="328" t="str">
         <x:v>Not mapped - project is not named in the supplied future program.</x:v>
       </x:c>
-      <x:c r="I25" s="111" t="str"/>
-      <x:c r="J25" s="114" t="str">
+      <x:c r="I25" s="327" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="J25" s="328" t="str">
         <x:v>Code is not listed as a primary outcome for this project in the supplied future program.</x:v>
       </x:c>
-      <x:c r="K25" s="111" t="str">
+      <x:c r="K25" s="329" t="str">
         <x:v>E</x:v>
       </x:c>
-      <x:c r="L25" s="114" t="str">
+      <x:c r="L25" s="328" t="str">
         <x:v>Program primary outcome; Weeks 3-4 traditional/industrial practice response.</x:v>
       </x:c>
-      <x:c r="M25" s="111" t="str">
+      <x:c r="M25" s="329" t="str">
         <x:v>P</x:v>
       </x:c>
-      <x:c r="N25" s="114" t="str">
+      <x:c r="N25" s="328" t="str">
         <x:v>Program primary outcome; assessment names industry practices, but task detail is limited.</x:v>
       </x:c>
-      <x:c r="O25" s="111" t="str">
+      <x:c r="O25" s="329" t="str">
         <x:v>P</x:v>
       </x:c>
-      <x:c r="P25" s="114" t="str">
+      <x:c r="P25" s="328" t="str">
         <x:v>Program primary outcome; industry-quality practice is taught; dedicated evidence is limited.</x:v>
       </x:c>
-      <x:c r="Q25" s="111" t="str"/>
-      <x:c r="R25" s="117" t="str">
+      <x:c r="Q25" s="327" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="R25" s="330" t="str">
         <x:v>Not mapped - Folding Chair is a provisional/developing option outside the supplied formal program.</x:v>
       </x:c>
     </x:row>
@@ -2673,34 +4000,34 @@
     <x:mergeCell ref="C5:C6"/>
     <x:mergeCell ref="D5:D6"/>
     <x:mergeCell ref="E5:F5"/>
-    <x:mergeCell ref="G5:H5"/>
     <x:mergeCell ref="I5:J5"/>
     <x:mergeCell ref="K5:L5"/>
     <x:mergeCell ref="M5:N5"/>
     <x:mergeCell ref="O5:P5"/>
+    <x:mergeCell ref="G5:H5"/>
     <x:mergeCell ref="Q5:R5"/>
   </x:mergeCells>
   <x:dataValidations count="7">
     <x:dataValidation type="list" sqref="E7:E25">
-      <x:formula1>"I,P,E"</x:formula1>
+      <x:formula1>"I,P,E,Gap,Partial,Not applicable,Not yet reviewed"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="G7:G25">
-      <x:formula1>"I,P,E"</x:formula1>
+      <x:formula1>"I,P,E,Gap,Partial,Not applicable,Not yet reviewed"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="I7:I25">
-      <x:formula1>"I,P,E"</x:formula1>
+      <x:formula1>"I,P,E,Gap,Partial,Not applicable,Not yet reviewed"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="K7:K25">
-      <x:formula1>"I,P,E"</x:formula1>
+      <x:formula1>"I,P,E,Gap,Partial,Not applicable,Not yet reviewed"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="M7:M25">
-      <x:formula1>"I,P,E"</x:formula1>
+      <x:formula1>"I,P,E,Gap,Partial,Not applicable,Not yet reviewed"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="O7:O25">
-      <x:formula1>"I,P,E"</x:formula1>
+      <x:formula1>"I,P,E,Gap,Partial,Not applicable,Not yet reviewed"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="Q7:Q25">
-      <x:formula1>"I,P,E"</x:formula1>
+      <x:formula1>"I,P,E,Gap,Partial,Not applicable,Not yet reviewed"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2864,7 +4191,7 @@
         <x:v>Date reviewed</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="92" customHeight="1">
+    <x:row r="5" ht="142" customHeight="1">
       <x:c r="A5" s="47" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -2872,7 +4199,7 @@
         <x:v>Breadboard</x:v>
       </x:c>
       <x:c r="C5" s="30" t="str">
-        <x:v>Year 9</x:v>
+        <x:v>Year 9 · supplied current program</x:v>
       </x:c>
       <x:c r="D5" s="30" t="str">
         <x:v>https://stevencowell.github.io/bread-board-guided-course/</x:v>
@@ -2881,56 +4208,57 @@
         <x:v>https://stevencowell.github.io/bread-board-guided-course/assets/breadboard-plans.pdf</x:v>
       </x:c>
       <x:c r="F5" s="94" t="str">
-        <x:v>5 guided modules; saved MCQ/written responses; folio with 12 photo/caption checkpoints; Print/Save PDF.</x:v>
+        <x:v>5 guided modules; saved MCQ/written responses; folio with 12 photo/caption checkpoints; Print/Save PDF.
+Local implementation 2026-08-02 — Module 05 activity 1 captures peer feedback given/received, one improvement and a result check; it autosaves and is included in Print / Save PDF. Live verified 2026-08-02 (S18).</x:v>
       </x:c>
       <x:c r="G5" s="94" t="str">
-        <x:v>breadboard-folio.html provides staged folio evidence. No separate assessment brief was linked.</x:v>
+        <x:v>breadboard-folio.html is the selected public assessment-evidence destination: 12 project checkpoints, photo/caption evidence, autosave, backup and Print / Save PDF. It is not a formal task notification or marking rubric.</x:v>
       </x:c>
       <x:c r="H5" s="94" t="str">
-        <x:v>Collaboration and emerging technology are not explicitly evidenced; design development and transfer are partial.</x:v>
+        <x:v>Assessment access decision recorded: use the project evidence folio. Formal task notices, dates, marks and Classroom submission remain teacher-controlled.</x:v>
       </x:c>
       <x:c r="I5" s="94" t="str">
         <x:v>Reviewed</x:v>
       </x:c>
       <x:c r="J5" s="30" t="str">
-        <x:v>Webpage capability audited; this does not assert individual student achievement.</x:v>
+        <x:v>Current-program project. Webpage capability audited; this does not assert individual student achievement. IND56 evidence is live and verified 2026-08-02 (S18).</x:v>
       </x:c>
       <x:c r="K5" s="31" t="str">
-        <x:v>2026-08-01</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="92" customHeight="1">
-      <x:c r="A6" s="48" t="n">
+      <x:c r="A6" s="337" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="str">
+      <x:c r="B6" s="335" t="str">
         <x:v>Small Box</x:v>
       </x:c>
-      <x:c r="C6" s="33" t="str">
-        <x:v>Year 9</x:v>
-      </x:c>
-      <x:c r="D6" s="33" t="str">
+      <x:c r="C6" s="335" t="str">
+        <x:v>Year 9 · local addition; outside supplied current program</x:v>
+      </x:c>
+      <x:c r="D6" s="335" t="str">
         <x:v>https://stevencowell.github.io/Small-Box/</x:v>
       </x:c>
-      <x:c r="E6" s="96" t="str">
+      <x:c r="E6" s="335" t="str">
         <x:v>No source-plan file is linked from the live site.</x:v>
       </x:c>
-      <x:c r="F6" s="96" t="str">
+      <x:c r="F6" s="494" t="str">
         <x:v>3 guided modules with saved MCQ/written responses; printable project folio.</x:v>
       </x:c>
-      <x:c r="G6" s="96" t="str">
+      <x:c r="G6" s="494" t="str">
         <x:v>smallbox-folio.html provides folio evidence. No separate assessment brief was linked.</x:v>
       </x:c>
-      <x:c r="H6" s="96" t="str">
-        <x:v>No linked plan; no explicit collaboration, design-development or emerging-technology task; transfer and impact are partial.</x:v>
-      </x:c>
-      <x:c r="I6" s="96" t="str">
+      <x:c r="H6" s="494" t="str">
+        <x:v>SCOPE-02 — local addition. No linked source plan; design/transfer/impact evidence remains a local improvement, not a current formal-program gap.</x:v>
+      </x:c>
+      <x:c r="I6" s="494" t="str">
         <x:v>Reviewed</x:v>
       </x:c>
-      <x:c r="J6" s="33" t="str">
-        <x:v>The future program does not name Small Box, so future-code cells remain unmapped.</x:v>
-      </x:c>
-      <x:c r="K6" s="34" t="str">
+      <x:c r="J6" s="494" t="str">
+        <x:v>Local addition not named in the supplied current program; excluded from formal-current pathway status.</x:v>
+      </x:c>
+      <x:c r="K6" s="495" t="str">
         <x:v>2026-08-01</x:v>
       </x:c>
     </x:row>
@@ -2942,7 +4270,7 @@
         <x:v>Clock</x:v>
       </x:c>
       <x:c r="C7" s="33" t="str">
-        <x:v>Year 9</x:v>
+        <x:v>Year 9 · supplied current program</x:v>
       </x:c>
       <x:c r="D7" s="33" t="str">
         <x:v>https://stevencowell.github.io/Yr-9-Clock/</x:v>
@@ -2957,13 +4285,13 @@
         <x:v>clock-folio.html plus Clock Assessment Criteria.pdf.</x:v>
       </x:c>
       <x:c r="H7" s="96" t="str">
-        <x:v>Collaboration is practised but not directly captured as participant evidence.</x:v>
+        <x:v>IND59 is explicitly evidenced here; shared-equipment practice lacks an inspectable participant record (CUR-01).</x:v>
       </x:c>
       <x:c r="I7" s="96" t="str">
         <x:v>Reviewed</x:v>
       </x:c>
       <x:c r="J7" s="33" t="str">
-        <x:v>Strong planning, making, design, technology, communication, evaluation and transfer evidence.</x:v>
+        <x:v>Current-program project. Strong design, production, technology, communication, evaluation and transfer evidence.</x:v>
       </x:c>
       <x:c r="K7" s="34" t="str">
         <x:v>2026-08-01</x:v>
@@ -2977,7 +4305,7 @@
         <x:v>Tool Carry-all</x:v>
       </x:c>
       <x:c r="C8" s="33" t="str">
-        <x:v>Year 9</x:v>
+        <x:v>Year 9 · supplied current program</x:v>
       </x:c>
       <x:c r="D8" s="33" t="str">
         <x:v>https://stevencowell.github.io/Yr-9-Carry-All/</x:v>
@@ -2989,16 +4317,16 @@
         <x:v>10 guided modules with saved MCQ/written responses; printable Carry-all folio.</x:v>
       </x:c>
       <x:c r="G8" s="96" t="str">
-        <x:v>carry-all-folio.html provides staged evidence. No separate assessment brief was linked.</x:v>
+        <x:v>carry-all-folio.html is the selected public assessment-evidence destination: 12 project cards, responses/photos, progress, autosave, ZIP backup and Print / Save PDF. It is not a formal task notification or marking rubric.</x:v>
       </x:c>
       <x:c r="H8" s="96" t="str">
-        <x:v>Collaboration is practised but participant contribution is not captured; emerging technology is introduced only through production comparison.</x:v>
+        <x:v>IND59 is introductory here. Assessment access decision recorded: use the project evidence folio; formal task notices and Classroom submission remain teacher-controlled.</x:v>
       </x:c>
       <x:c r="I8" s="96" t="str">
         <x:v>Reviewed</x:v>
       </x:c>
       <x:c r="J8" s="33" t="str">
-        <x:v>Cultural and environmental learning is explicitly captured in Weeks 3-4.</x:v>
+        <x:v>Current-program project. Cultural/responsible-use evidence is explicit in Weeks 3–4.</x:v>
       </x:c>
       <x:c r="K8" s="34" t="str">
         <x:v>2026-08-01</x:v>
@@ -3012,7 +4340,7 @@
         <x:v>Mirror</x:v>
       </x:c>
       <x:c r="C9" s="33" t="str">
-        <x:v>Year 10</x:v>
+        <x:v>Year 10 · supplied current program</x:v>
       </x:c>
       <x:c r="D9" s="33" t="str">
         <x:v>https://stevencowell.github.io/year-10-timber-mirror-project/</x:v>
@@ -3021,25 +4349,25 @@
         <x:v>Mirror-Project-Plans.pdf is linked from the live site.</x:v>
       </x:c>
       <x:c r="F9" s="96" t="str">
-        <x:v>9 live theory/activity pages, quizzes and editable portfolio workbook; separate folio; 20 repaired support-week routes.</x:v>
+        <x:v>9 live theory/activity pages, quizzes and editable portfolio workbook; separate folio; 20 repaired support-week routes. Local implementation 2026-08-02 - Portfolio Workbook Peer Quality Check and Workshop Handover captures a reviewer role, observable criterion/evidence, feedback, justified decision, result check and workshop handover; publication pending.</x:v>
       </x:c>
       <x:c r="G9" s="96" t="str">
-        <x:v>mirror_assessment.html identifies practical, folio and class-test evidence; portfolio workbook and folio are live.</x:v>
+        <x:v>mirror_assessment.html identifies practical, folio and class-test evidence. Local assessment-guide update adds the peer quality-check and handover record to portfolio evidence and rubric; publication pending.</x:v>
       </x:c>
       <x:c r="H9" s="96" t="str">
-        <x:v>Collaboration and emerging technology still lack explicit active evidence; environmental and industry evidence remain partial.</x:v>
+        <x:v>IND56 local repair awaits publication and live re-audit (CUR-01). IND59 is a course-context outcome here, not a separate Mirror evidence claim; Clock is the designated pathway E point (CUR-02).</x:v>
       </x:c>
       <x:c r="I9" s="96" t="str">
-        <x:v>Reviewed - link repair complete</x:v>
+        <x:v>Reviewed - local evidence repair pending publication</x:v>
       </x:c>
       <x:c r="J9" s="33" t="str">
-        <x:v>The 20 week links were repaired to existing support pages on 2026-08-01; core theory, quiz, portfolio, folio, assessment and plan pages remain live.</x:v>
+        <x:v>Current-program project. Repaired support routes remain complete. Local collaboration record and assessment-rubric traceability were QA checked 2026-08-02; this does not assert individual student achievement.</x:v>
       </x:c>
       <x:c r="K9" s="34" t="str">
-        <x:v>2026-08-01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="92" customHeight="1">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="164" customHeight="1">
       <x:c r="A10" s="48" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -3047,7 +4375,7 @@
         <x:v>Bedside Table</x:v>
       </x:c>
       <x:c r="C10" s="33" t="str">
-        <x:v>Year 10</x:v>
+        <x:v>Year 10 · supplied current program</x:v>
       </x:c>
       <x:c r="D10" s="33" t="str">
         <x:v>https://stevencowell.github.io/bedside-table-guided-course/</x:v>
@@ -3056,56 +4384,57 @@
         <x:v>Bedside-Table-Project-Plans.pdf and example SDS are linked.</x:v>
       </x:c>
       <x:c r="F10" s="96" t="str">
-        <x:v>10 guided modules with saved MCQ/written responses; printable project folio.</x:v>
+        <x:v>10 guided modules with saved MCQ/written responses; printable project folio.
+Local implementation 2026-08-02 — Weeks 19–20 response 1 captures participant roles, peer QA critique, a justified technical decision, feedback-used evidence and workshop handover contribution; it autosaves and is included in Download PDF. Live verified 2026-08-02 (S18).</x:v>
       </x:c>
       <x:c r="G10" s="96" t="str">
-        <x:v>bedside-table-folio.html provides staged evidence. No separate assessment brief was linked.</x:v>
+        <x:v>bedside-table-folio.html is the selected public assessment-evidence destination: 12 evidence cards, responses/photos, progress, ZIP/JSON backup and Print / Save PDF. It is not a formal task notification or marking rubric.</x:v>
       </x:c>
       <x:c r="H10" s="96" t="str">
-        <x:v>Collaboration is practised but not directly captured; emerging-technology claim lacks a dedicated activity.</x:v>
+        <x:v>Culminating evidence is broad. Assessment access decision recorded: use the project evidence folio; formal task notices and Classroom submission remain teacher-controlled. IND56 live evidence remains verified (S18).</x:v>
       </x:c>
       <x:c r="I10" s="96" t="str">
         <x:v>Reviewed</x:v>
       </x:c>
       <x:c r="J10" s="33" t="str">
-        <x:v>Strong process, safety, sustainability, communication and evaluation evidence.</x:v>
+        <x:v>Current-program culminating project with strong process, safety, sustainability, communication and evaluation evidence. Deeper IND56 evidence is live and verified 2026-08-02 (S18).</x:v>
       </x:c>
       <x:c r="K10" s="34" t="str">
-        <x:v>2026-08-01</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="92" customHeight="1">
-      <x:c r="A11" s="125" t="n">
+      <x:c r="A11" s="341" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B11" s="123" t="str">
+      <x:c r="B11" s="342" t="str">
         <x:v>Folding Chair</x:v>
       </x:c>
-      <x:c r="C11" s="123" t="str">
-        <x:v>Year 10 - developing option</x:v>
-      </x:c>
-      <x:c r="D11" s="123" t="str">
+      <x:c r="C11" s="342" t="str">
+        <x:v>Year 10 · local developing option; outside supplied current program</x:v>
+      </x:c>
+      <x:c r="D11" s="342" t="str">
         <x:v>https://stevencowell.github.io/folding-chair-guided-course/</x:v>
       </x:c>
-      <x:c r="E11" s="123" t="str">
+      <x:c r="E11" s="342" t="str">
         <x:v>Folding-Chair-Project-Plans.pdf and example SDS are linked.</x:v>
       </x:c>
-      <x:c r="F11" s="123" t="str">
+      <x:c r="F11" s="342" t="str">
         <x:v>10 guided modules with saved MCQ/written responses; CAD task; printable project folio.</x:v>
       </x:c>
-      <x:c r="G11" s="123" t="str">
+      <x:c r="G11" s="342" t="str">
         <x:v>folding-chair-folio.html provides staged evidence. No separate assessment brief was linked.</x:v>
       </x:c>
-      <x:c r="H11" s="123" t="str">
-        <x:v>Provisional project outside supplied formal program; collaboration contribution is not directly captured.</x:v>
-      </x:c>
-      <x:c r="I11" s="123" t="str">
+      <x:c r="H11" s="342" t="str">
+        <x:v>SCOPE-02 — local developing option. Local collaboration evidence is not counted as a current formal-program gap.</x:v>
+      </x:c>
+      <x:c r="I11" s="342" t="str">
         <x:v>Reviewed</x:v>
       </x:c>
-      <x:c r="J11" s="123" t="str">
-        <x:v>Current-outcome webpage map completed; future-program codes deliberately remain unmapped.</x:v>
-      </x:c>
-      <x:c r="K11" s="124" t="str">
+      <x:c r="J11" s="342" t="str">
+        <x:v>Local developing option not named in the supplied current program; excluded from formal-current pathway status.</x:v>
+      </x:c>
+      <x:c r="K11" s="343" t="str">
         <x:v>2026-08-01</x:v>
       </x:c>
     </x:row>
@@ -3261,10 +4590,10 @@
         <x:v>Current outcome statements and teaching-program evidence</x:v>
       </x:c>
       <x:c r="G5" s="87" t="str">
-        <x:v>Reviewed 2026-08-01</x:v>
+        <x:v>Reviewed 2026-08-02</x:v>
       </x:c>
       <x:c r="H5" s="127" t="str">
-        <x:v>Local authority used for current IND outcome wording.</x:v>
+        <x:v>Primary authority for exact current outcome wording, formal project sequence, 77 unique top-level content statements and 253 statement placements. SHA-256: D3B8CA8A73AFF66FC101ECAE97B7BAB6F16604CF885D78D9A955EEBF23FF6926.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="64" customHeight="1">
@@ -3655,6 +4984,84 @@
       </x:c>
       <x:c r="H20" s="134" t="str">
         <x:v>12 live HTML pages; provisional outside supplied program.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="72" customHeight="1">
+      <x:c r="A21" s="491" t="str">
+        <x:v>S17</x:v>
+      </x:c>
+      <x:c r="B21" s="488" t="str">
+        <x:v>Current-program mapping method</x:v>
+      </x:c>
+      <x:c r="C21" s="488" t="str">
+        <x:v>Audit method / limitation</x:v>
+      </x:c>
+      <x:c r="D21" s="488" t="str">
+        <x:v>Current program companion</x:v>
+      </x:c>
+      <x:c r="E21" s="488" t="str">
+        <x:v>Current Syllabus Summary and Current Program Content Map sheets</x:v>
+      </x:c>
+      <x:c r="F21" s="488" t="str">
+        <x:v>Separates two-year outcome status, I/P/E progression, exact program content, programmed learning, named evidence and program-boundary decisions</x:v>
+      </x:c>
+      <x:c r="G21" s="488" t="str">
+        <x:v>Quality pass 2026-08-02</x:v>
+      </x:c>
+      <x:c r="H21" s="489" t="str">
+        <x:v>The supplied program maps outcomes at unit level, not per content statement. No dot-point-to-IND crosswalk, departmental approval, individual achievement or exact webpage match is inferred.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="88" customHeight="1">
+      <x:c r="A22" s="519" t="str">
+        <x:v>S18</x:v>
+      </x:c>
+      <x:c r="B22" s="516" t="str">
+        <x:v>Local IND56 collaboration-evidence implementation</x:v>
+      </x:c>
+      <x:c r="C22" s="516" t="str">
+        <x:v>Current guided-course source files</x:v>
+      </x:c>
+      <x:c r="D22" s="516" t="str">
+        <x:v>Current Stage 5 outcome IND56 and two-year scaffold</x:v>
+      </x:c>
+      <x:c r="E22" s="516" t="str">
+        <x:v>Breadboard: work/remediation-repos/bread-board-guided-course/modules/module-05-data.js and module-05.html; Bedside Table: work/remediation-repos/bedside-table-guided-course/weeks19-20/lesson-data.js</x:v>
+      </x:c>
+      <x:c r="F22" s="516" t="str">
+        <x:v>Stage 1 introductory peer feedback/improvement evidence and Stage 6 peer QA, justified-decision and handover evidence</x:v>
+      </x:c>
+      <x:c r="G22" s="516" t="str">
+        <x:v>Live verified 2026-08-02</x:v>
+      </x:c>
+      <x:c r="H22" s="517" t="str">
+        <x:v>Published and live verified 2026-08-02. Breadboard commit ad8c514: https://stevencowell.github.io/bread-board-guided-course/modules/module-05.html. Bedside Table commit 8fac5f5: https://stevencowell.github.io/bedside-table-guided-course/weeks19-20/. Both page activities were confirmed visible after GitHub Pages update.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="120" customHeight="1">
+      <x:c r="A23" s="542" t="str">
+        <x:v>S19</x:v>
+      </x:c>
+      <x:c r="B23" s="543" t="str">
+        <x:v>Remaining audit actions - local implementation</x:v>
+      </x:c>
+      <x:c r="C23" s="543" t="str">
+        <x:v>Local current-repair source</x:v>
+      </x:c>
+      <x:c r="D23" s="543" t="str">
+        <x:v>Year 9-10 Timber hub and current project repositories</x:v>
+      </x:c>
+      <x:c r="E23" s="543" t="str">
+        <x:v>Mirror Portfolio Workbook; mirror_assessment.html; Breadboard, Mirror and Bedside Table landing pages; hub assessment/program-trace updates</x:v>
+      </x:c>
+      <x:c r="F23" s="543" t="str">
+        <x:v>Mirror collaboration evidence; course-context clarification for IND59; verified Clock/Mirror assessment access; selected Breadboard, Carry-All and Bedside Table evidence-folio destinations; Pen trace note</x:v>
+      </x:c>
+      <x:c r="G23" s="543" t="str">
+        <x:v>Local QA complete 2026-08-02; publication and live re-audit pending</x:v>
+      </x:c>
+      <x:c r="H23" s="544" t="str">
+        <x:v>Selected folios: https://stevencowell.github.io/bread-board-guided-course/breadboard-folio.html; https://stevencowell.github.io/Yr-9-Carry-All/carry-all-folio.html; https://stevencowell.github.io/bedside-table-guided-course/bedside-table-folio.html. No unverified dates, marks, Classroom links or Pen project link were added.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3664,4 +5071,4191 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="31" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="43" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="47" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="49" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="346" t="str">
+        <x:v>Timber Course Gap Register</x:v>
+      </x:c>
+      <x:c r="B1" s="346"/>
+      <x:c r="C1" s="346"/>
+      <x:c r="D1" s="346"/>
+      <x:c r="E1" s="346"/>
+      <x:c r="F1" s="346"/>
+      <x:c r="G1" s="346"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="346"/>
+      <x:c r="B2" s="346"/>
+      <x:c r="C2" s="346"/>
+      <x:c r="D2" s="346"/>
+      <x:c r="E2" s="346"/>
+      <x:c r="F2" s="346"/>
+      <x:c r="G2" s="346"/>
+    </x:row>
+    <x:row r="3" ht="36" customHeight="1">
+      <x:c r="A3" s="225" t="str">
+        <x:v>Current-syllabus work plan only. Shared issues appear once here and are cross-referenced from project cells. Future/new-syllabus mapping issues are excluded from this register; local additions and formal-program scope limits are labelled explicitly.</x:v>
+      </x:c>
+      <x:c r="B3" s="225"/>
+      <x:c r="C3" s="225"/>
+      <x:c r="D3" s="225"/>
+      <x:c r="E3" s="225"/>
+      <x:c r="F3" s="225"/>
+      <x:c r="G3" s="225"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="347" t="str">
+        <x:v>Priority</x:v>
+      </x:c>
+      <x:c r="B5" s="347" t="str">
+        <x:v>Open item count</x:v>
+      </x:c>
+      <x:c r="D5" s="227" t="str">
+        <x:v>Register scope</x:v>
+      </x:c>
+      <x:c r="E5" s="227"/>
+      <x:c r="F5" s="227"/>
+      <x:c r="G5" s="227"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="361" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="B6" s="362" t="n">
+        <x:f>COUNTIF($A$12:$A$16,A6)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D6" s="367" t="str">
+        <x:v>CUR-01 and CUR-02 are locally repaired and await publication/live re-audit. CUR-03 remains an evidenced access issue for sites without a verified assessment destination. SCOPE-01 and SCOPE-02 are program-boundary decisions, not current outcome failures. Priority remains intentionally blank for Steve to set.</x:v>
+      </x:c>
+      <x:c r="E6" s="367"/>
+      <x:c r="F6" s="367"/>
+      <x:c r="G6" s="367"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="363" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="B7" s="364" t="n">
+        <x:f>COUNTIF($A$12:$A$16,A7)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D7" s="367"/>
+      <x:c r="E7" s="367"/>
+      <x:c r="F7" s="367"/>
+      <x:c r="G7" s="367"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="363" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="B8" s="364" t="n">
+        <x:f>COUNTIF($A$12:$A$16,A8)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D8" s="367"/>
+      <x:c r="E8" s="367"/>
+      <x:c r="F8" s="367"/>
+      <x:c r="G8" s="367"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="365" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="B9" s="366" t="n">
+        <x:f>COUNTIF($A$12:$A$16,A9)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="367"/>
+      <x:c r="E9" s="367"/>
+      <x:c r="F9" s="367"/>
+      <x:c r="G9" s="367"/>
+    </x:row>
+    <x:row r="11" ht="34" customHeight="1">
+      <x:c r="A11" s="370" t="str">
+        <x:v>Priority</x:v>
+      </x:c>
+      <x:c r="B11" s="370" t="str">
+        <x:v>Project(s)</x:v>
+      </x:c>
+      <x:c r="C11" s="370" t="str">
+        <x:v>Gap or risk</x:v>
+      </x:c>
+      <x:c r="D11" s="370" t="str">
+        <x:v>Why it matters for syllabus/evidence/scaffold</x:v>
+      </x:c>
+      <x:c r="E11" s="370" t="str">
+        <x:v>Evidence/source</x:v>
+      </x:c>
+      <x:c r="F11" s="370" t="str">
+        <x:v>Recommended next action</x:v>
+      </x:c>
+      <x:c r="G11" s="370" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="116" customHeight="1">
+      <x:c r="A12" s="207" t="str"/>
+      <x:c r="B12" s="213" t="str">
+        <x:v>Mirror</x:v>
+      </x:c>
+      <x:c r="C12" s="193" t="str">
+        <x:v>CUR-01 - Mirror now has a local peer quality-check and workshop-handover evidence record; publication and live re-audit remain required.</x:v>
+      </x:c>
+      <x:c r="D12" s="193" t="str">
+        <x:v>The IND56 record now captures roles, observable criterion/evidence, feedback, a justified technical decision, feedback used and a shared-workshop handover. This extends the existing Year 9-to-Year 10 scaffold without claiming individual achievement.</x:v>
+      </x:c>
+      <x:c r="E12" s="193" t="str">
+        <x:v>Local Mirror Portfolio Workbook and mirror_assessment.html update, 2026-08-02; Matrix row 12; Project Evidence row 9; Source Register S19.</x:v>
+      </x:c>
+      <x:c r="F12" s="193" t="str">
+        <x:v>Commit and publish the three local Mirror files, then confirm the live workbook activity and assessment-guide criterion before closing.</x:v>
+      </x:c>
+      <x:c r="G12" s="528" t="str">
+        <x:v>Resolved - re-audit required</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="94" customHeight="1">
+      <x:c r="A13" s="208" t="str"/>
+      <x:c r="B13" s="214" t="str">
+        <x:v>Breadboard; Clock; Tool Carry-all; Mirror; Bedside Table</x:v>
+      </x:c>
+      <x:c r="C13" s="196" t="str">
+        <x:v>CUR-02 - IND59 evidence is now clearly sequenced: Clock is the formal current-program E point; Carry-all is an introductory comparison; full outcome lists on Breadboard, Mirror and Bedside Table are course context only.</x:v>
+      </x:c>
+      <x:c r="D13" s="196" t="str">
+        <x:v>This prevents a reviewer treating every project outcome list as a separate assessment claim. The two-year pathway retains one explicit formal evidence point rather than generic duplicated commentary.</x:v>
+      </x:c>
+      <x:c r="E13" s="196" t="str">
+        <x:v>Current Syllabus Summary IND59; Matrix row 15; local course-context wording updates at Breadboard, Mirror and Bedside Table; Source Register S19.</x:v>
+      </x:c>
+      <x:c r="F13" s="196" t="str">
+        <x:v>Commit and publish the local wording updates, then live recheck the three landing pages. No additional generic technology activity is required for pathway coverage.</x:v>
+      </x:c>
+      <x:c r="G13" s="534" t="str">
+        <x:v>Resolved - re-audit required</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="122" customHeight="1">
+      <x:c r="A14" s="208" t="str"/>
+      <x:c r="B14" s="214" t="str">
+        <x:v>Breadboard; Tool Carry-all; Bedside Table</x:v>
+      </x:c>
+      <x:c r="C14" s="196" t="str">
+        <x:v>CUR-03 - project-specific assessment-evidence destinations have been selected and added to the local hub; publication and live verification remain required.</x:v>
+      </x:c>
+      <x:c r="D14" s="196" t="str">
+        <x:v>Each repository has a strong editable student evidence folio but no separate public task notification or marking rubric. The hub labels them as evidence folios so a reviewer can open the strongest real destination without overclaiming what it is.</x:v>
+      </x:c>
+      <x:c r="E14" s="196" t="str">
+        <x:v>Bread Board Project Folio: https://stevencowell.github.io/bread-board-guided-course/breadboard-folio.html; Carry-All Student Project Folio: https://stevencowell.github.io/Yr-9-Carry-All/carry-all-folio.html; Bedside Table Student Folio: https://stevencowell.github.io/bedside-table-guided-course/bedside-table-folio.html; Source Register S19.</x:v>
+      </x:c>
+      <x:c r="F14" s="196" t="str">
+        <x:v>Publish the hub link update, then verify all three folio routes and labels live. Keep task notices, dates, marks and Classroom links teacher-controlled unless a verified destination is later supplied.</x:v>
+      </x:c>
+      <x:c r="G14" s="546" t="str">
+        <x:v>Resolved - re-audit required</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="94" customHeight="1">
+      <x:c r="A15" s="208" t="str"/>
+      <x:c r="B15" s="214" t="str">
+        <x:v>Pen</x:v>
+      </x:c>
+      <x:c r="C15" s="196" t="str">
+        <x:v>SCOPE-01 - Pen is now visibly traced on the local hub and audit, but its formal placement, duration and two lathe-specific content points still need a course decision and evidence location.</x:v>
+      </x:c>
+      <x:c r="D15" s="196" t="str">
+        <x:v>The current program names Pen, while the agreed hub pathway does not include it. The local audit makes the boundary visible without claiming that 77/77 content points are represented.</x:v>
+      </x:c>
+      <x:c r="E15" s="196" t="str">
+        <x:v>Current Program Content Map CP038 and CP039; current program tables 21-24; local hub program-trace note.</x:v>
+      </x:c>
+      <x:c r="F15" s="196" t="str">
+        <x:v>Steve to confirm whether Pen is retained, omitted or replaced, and which duration governs. Then map the two content points or formally record the replacement.</x:v>
+      </x:c>
+      <x:c r="G15" s="535" t="str">
+        <x:v>Open - course decision needed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="94" customHeight="1">
+      <x:c r="A16" s="208" t="str"/>
+      <x:c r="B16" s="214" t="str">
+        <x:v>Small Box; Folding Chair</x:v>
+      </x:c>
+      <x:c r="C16" s="196" t="str">
+        <x:v>SCOPE-02 - local additions outside the supplied current formal program.</x:v>
+      </x:c>
+      <x:c r="D16" s="196" t="str">
+        <x:v>Their evidence is useful to the pathway but must not be presented as proof that the supplied current program formally names them. Small Box also has no linked plan and retains local design/transfer/impact improvements.</x:v>
+      </x:c>
+      <x:c r="E16" s="196" t="str">
+        <x:v>Overview project status; Project Evidence rows 6 and 11; current program project sequence; Matrix local-addition headers.</x:v>
+      </x:c>
+      <x:c r="F16" s="196" t="str">
+        <x:v>Keep both projects clearly labelled as local additions. Treat Small Box plan/evidence improvements as local work, and keep Folding Chair labelled developing until Steve changes its status.</x:v>
+      </x:c>
+      <x:c r="G16" s="535" t="str">
+        <x:v>Open - scope retained</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="84" customHeight="1">
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+    </x:row>
+    <x:row r="18" ht="84" customHeight="1">
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
+    </x:row>
+    <x:row r="19" ht="84" customHeight="1">
+      <x:c r="A19"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+    </x:row>
+    <x:row r="20" ht="84" customHeight="1">
+      <x:c r="A20"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+    </x:row>
+    <x:row r="21" ht="84" customHeight="1">
+      <x:c r="A21"/>
+      <x:c r="B21"/>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
+      <x:c r="G21"/>
+    </x:row>
+    <x:row r="22" ht="84" customHeight="1">
+      <x:c r="A22"/>
+      <x:c r="B22"/>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
+      <x:c r="E22"/>
+      <x:c r="F22"/>
+      <x:c r="G22"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:G2"/>
+    <x:mergeCell ref="A3:G3"/>
+    <x:mergeCell ref="D5:G5"/>
+    <x:mergeCell ref="D6:G9"/>
+  </x:mergeCells>
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" sqref="A12:A16">
+      <x:formula1>"Critical,High,Medium,Low"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="G12:G16">
+      <x:formula1>"Open - priority to be set,Open - source needed,Open - course decision needed,Open - scope retained,In progress,Resolved - re-audit required,Closed - verified"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="19" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="52" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="55" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="50" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="50" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="346" t="str">
+        <x:v>Current Stage 5 Outcome Coverage</x:v>
+      </x:c>
+      <x:c r="B1" s="346"/>
+      <x:c r="C1" s="346"/>
+      <x:c r="D1" s="346"/>
+      <x:c r="E1" s="346"/>
+      <x:c r="F1" s="346"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="346"/>
+      <x:c r="B2" s="346"/>
+      <x:c r="C2" s="346"/>
+      <x:c r="D2" s="346"/>
+      <x:c r="E2" s="346"/>
+      <x:c r="F2" s="346"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="225" t="str">
+        <x:v>Authority: stage_5_timber_2021-06-16.docx. Status is assessed across the full two-year sequence, not by forcing every outcome into every project. Covered means explicit E evidence exists in a represented formal project; Partially covered means only I/P evidence is present; Has gaps means required formal evidence remains unresolved. This program companion does not claim departmental approval, individual achievement or exhaustive coverage of an official syllabus beyond the supplied program.</x:v>
+      </x:c>
+      <x:c r="B3" s="225"/>
+      <x:c r="C3" s="225"/>
+      <x:c r="D3" s="225"/>
+      <x:c r="E3" s="225"/>
+      <x:c r="F3" s="225"/>
+    </x:row>
+    <x:row r="4" ht="30" customHeight="1">
+      <x:c r="A4" s="225"/>
+      <x:c r="B4" s="225"/>
+      <x:c r="C4" s="225"/>
+      <x:c r="D4" s="225"/>
+      <x:c r="E4" s="225"/>
+      <x:c r="F4" s="225"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="347" t="str">
+        <x:v>Pathway status</x:v>
+      </x:c>
+      <x:c r="B6" s="347" t="str">
+        <x:v>Outcome count</x:v>
+      </x:c>
+      <x:c r="D6" s="227" t="str">
+        <x:v>Formal-program and hub scope</x:v>
+      </x:c>
+      <x:c r="E6" s="227"/>
+      <x:c r="F6" s="227"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="404" t="str">
+        <x:v>Covered</x:v>
+      </x:c>
+      <x:c r="B7" s="405" t="n">
+        <x:f>COUNTIF($B$11:$B$20,A7)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D7" s="412" t="str">
+        <x:v>Supplied current-program sequence: Breadboard → Clock → Pen (additional turning unit after Clock or Carry-all) → Tool Carry-all → Mirror → Bedside Table. The Pen duration is inconsistent in the source (1 week, 2-week sequence and 1–2 week overview). Audited hub sequence: Breadboard → Small Box (local) → Clock → Tool Carry-all → Mirror → Bedside Table → Folding Chair (local developing option). Pen lacks an audited hub trace; local additions are excluded from the formal-current status calculation.</x:v>
+      </x:c>
+      <x:c r="E7" s="412"/>
+      <x:c r="F7" s="412"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="406" t="str">
+        <x:v>Partially covered</x:v>
+      </x:c>
+      <x:c r="B8" s="407" t="n">
+        <x:f>COUNTIF($B$11:$B$20,A8)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D8" s="412"/>
+      <x:c r="E8" s="412"/>
+      <x:c r="F8" s="412"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="408" t="str">
+        <x:v>Has gaps</x:v>
+      </x:c>
+      <x:c r="B9" s="409" t="n">
+        <x:f>COUNTIF($B$11:$B$20,A9)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="412"/>
+      <x:c r="E9" s="412"/>
+      <x:c r="F9" s="412"/>
+    </x:row>
+    <x:row r="10" ht="36" customHeight="1">
+      <x:c r="A10" s="370" t="str">
+        <x:v>Outcome</x:v>
+      </x:c>
+      <x:c r="B10" s="370" t="str">
+        <x:v>Pathway status</x:v>
+      </x:c>
+      <x:c r="C10" s="370" t="str">
+        <x:v>Exact wording in supplied current program</x:v>
+      </x:c>
+      <x:c r="D10" s="370" t="str">
+        <x:v>Progression across Years 9–10</x:v>
+      </x:c>
+      <x:c r="E10" s="370" t="str">
+        <x:v>Strongest evidence / workbook references</x:v>
+      </x:c>
+      <x:c r="F10" s="370" t="str">
+        <x:v>Gap or next assurance</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="96" customHeight="1">
+      <x:c r="A11" s="265" t="str">
+        <x:v>IND51</x:v>
+      </x:c>
+      <x:c r="B11" s="422" t="str">
+        <x:f>IF(COUNTIF('Syllabus Alignment Matrix'!E7,"E")+COUNTIF('Syllabus Alignment Matrix'!I7,"E")+COUNTIF('Syllabus Alignment Matrix'!K7,"E")+COUNTIF('Syllabus Alignment Matrix'!M7,"E")+COUNTIF('Syllabus Alignment Matrix'!O7,"E")&gt;0,"Covered",IF(COUNTIF('Syllabus Alignment Matrix'!E7,"Gap")+COUNTIF('Syllabus Alignment Matrix'!I7,"Gap")+COUNTIF('Syllabus Alignment Matrix'!K7,"Gap")+COUNTIF('Syllabus Alignment Matrix'!M7,"Gap")+COUNTIF('Syllabus Alignment Matrix'!O7,"Gap")&gt;0,"Has gaps",IF(COUNTIF('Syllabus Alignment Matrix'!E7,"I")+COUNTIF('Syllabus Alignment Matrix'!I7,"I")+COUNTIF('Syllabus Alignment Matrix'!K7,"I")+COUNTIF('Syllabus Alignment Matrix'!M7,"I")+COUNTIF('Syllabus Alignment Matrix'!O7,"I")+COUNTIF('Syllabus Alignment Matrix'!E7,"P")+COUNTIF('Syllabus Alignment Matrix'!I7,"P")+COUNTIF('Syllabus Alignment Matrix'!K7,"P")+COUNTIF('Syllabus Alignment Matrix'!M7,"P")+COUNTIF('Syllabus Alignment Matrix'!O7,"P")+COUNTIF('Syllabus Alignment Matrix'!E7,"Partial")+COUNTIF('Syllabus Alignment Matrix'!I7,"Partial")+COUNTIF('Syllabus Alignment Matrix'!K7,"Partial")+COUNTIF('Syllabus Alignment Matrix'!M7,"Partial")+COUNTIF('Syllabus Alignment Matrix'!O7,"Partial")&gt;0,"Partially covered","Has gaps")))</x:f>
+        <x:v>Covered</x:v>
+      </x:c>
+      <x:c r="C11" s="193" t="str">
+        <x:v>identifies, assesses, applies and manages the risks and WHS issues associated with the use of a range of tools, equipment, materials, processes and technologies</x:v>
+      </x:c>
+      <x:c r="D11" s="193" t="str">
+        <x:v>Stage 1 risk response and folio safety evidence → Clock and Carry-all WMS/SWMS → Year 10 SDS, finishing and workshop controls. The evidence repeats at increasing workshop complexity.</x:v>
+      </x:c>
+      <x:c r="E11" s="193" t="str">
+        <x:v>Matrix row 7; Breadboard Module 01; Clock Weeks 1–4; Carry-all Weeks 1–2 and 15–16; Mirror safety activities; Bedside Table Weeks 1–2 and 15–16.</x:v>
+      </x:c>
+      <x:c r="F11" s="194" t="str">
+        <x:v>Preserve the increasing-complexity WHS I → P → E trail; no current repair identified.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="96" customHeight="1">
+      <x:c r="A12" s="266" t="str">
+        <x:v>IND52</x:v>
+      </x:c>
+      <x:c r="B12" s="423" t="str">
+        <x:f>IF(COUNTIF('Syllabus Alignment Matrix'!E8,"E")+COUNTIF('Syllabus Alignment Matrix'!I8,"E")+COUNTIF('Syllabus Alignment Matrix'!K8,"E")+COUNTIF('Syllabus Alignment Matrix'!M8,"E")+COUNTIF('Syllabus Alignment Matrix'!O8,"E")&gt;0,"Covered",IF(COUNTIF('Syllabus Alignment Matrix'!E8,"Gap")+COUNTIF('Syllabus Alignment Matrix'!I8,"Gap")+COUNTIF('Syllabus Alignment Matrix'!K8,"Gap")+COUNTIF('Syllabus Alignment Matrix'!M8,"Gap")+COUNTIF('Syllabus Alignment Matrix'!O8,"Gap")&gt;0,"Has gaps",IF(COUNTIF('Syllabus Alignment Matrix'!E8,"I")+COUNTIF('Syllabus Alignment Matrix'!I8,"I")+COUNTIF('Syllabus Alignment Matrix'!K8,"I")+COUNTIF('Syllabus Alignment Matrix'!M8,"I")+COUNTIF('Syllabus Alignment Matrix'!O8,"I")+COUNTIF('Syllabus Alignment Matrix'!E8,"P")+COUNTIF('Syllabus Alignment Matrix'!I8,"P")+COUNTIF('Syllabus Alignment Matrix'!K8,"P")+COUNTIF('Syllabus Alignment Matrix'!M8,"P")+COUNTIF('Syllabus Alignment Matrix'!O8,"P")+COUNTIF('Syllabus Alignment Matrix'!E8,"Partial")+COUNTIF('Syllabus Alignment Matrix'!I8,"Partial")+COUNTIF('Syllabus Alignment Matrix'!K8,"Partial")+COUNTIF('Syllabus Alignment Matrix'!M8,"Partial")+COUNTIF('Syllabus Alignment Matrix'!O8,"Partial")&gt;0,"Partially covered","Has gaps")))</x:f>
+        <x:v>Covered</x:v>
+      </x:c>
+      <x:c r="C12" s="196" t="str">
+        <x:v>applies design principles in the modification, development and production of projects</x:v>
+      </x:c>
+      <x:c r="D12" s="196" t="str">
+        <x:v>Breadboard practises layout/profile decisions → Clock, Carry-all, Mirror and Bedside Table evidence design development, approved choices or variations. Later projects complete the pathway.</x:v>
+      </x:c>
+      <x:c r="E12" s="196" t="str">
+        <x:v>Matrix row 8; Clock Weeks 15–16; Carry-all Weeks 11–12; Mirror design/portfolio activities; Bedside Table Weeks 1–2.</x:v>
+      </x:c>
+      <x:c r="F12" s="197" t="str">
+        <x:v>Keep the later approved design decisions as the evidence point that completes Breadboard practice.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="96" customHeight="1">
+      <x:c r="A13" s="266" t="str">
+        <x:v>IND53</x:v>
+      </x:c>
+      <x:c r="B13" s="423" t="str">
+        <x:f>IF(COUNTIF('Syllabus Alignment Matrix'!E9,"E")+COUNTIF('Syllabus Alignment Matrix'!I9,"E")+COUNTIF('Syllabus Alignment Matrix'!K9,"E")+COUNTIF('Syllabus Alignment Matrix'!M9,"E")+COUNTIF('Syllabus Alignment Matrix'!O9,"E")&gt;0,"Covered",IF(COUNTIF('Syllabus Alignment Matrix'!E9,"Gap")+COUNTIF('Syllabus Alignment Matrix'!I9,"Gap")+COUNTIF('Syllabus Alignment Matrix'!K9,"Gap")+COUNTIF('Syllabus Alignment Matrix'!M9,"Gap")+COUNTIF('Syllabus Alignment Matrix'!O9,"Gap")&gt;0,"Has gaps",IF(COUNTIF('Syllabus Alignment Matrix'!E9,"I")+COUNTIF('Syllabus Alignment Matrix'!I9,"I")+COUNTIF('Syllabus Alignment Matrix'!K9,"I")+COUNTIF('Syllabus Alignment Matrix'!M9,"I")+COUNTIF('Syllabus Alignment Matrix'!O9,"I")+COUNTIF('Syllabus Alignment Matrix'!E9,"P")+COUNTIF('Syllabus Alignment Matrix'!I9,"P")+COUNTIF('Syllabus Alignment Matrix'!K9,"P")+COUNTIF('Syllabus Alignment Matrix'!M9,"P")+COUNTIF('Syllabus Alignment Matrix'!O9,"P")+COUNTIF('Syllabus Alignment Matrix'!E9,"Partial")+COUNTIF('Syllabus Alignment Matrix'!I9,"Partial")+COUNTIF('Syllabus Alignment Matrix'!K9,"Partial")+COUNTIF('Syllabus Alignment Matrix'!M9,"Partial")+COUNTIF('Syllabus Alignment Matrix'!O9,"Partial")&gt;0,"Partially covered","Has gaps")))</x:f>
+        <x:v>Covered</x:v>
+      </x:c>
+      <x:c r="C13" s="196" t="str">
+        <x:v>identifies, selects and uses a range of hand and machine tools, equipment and processes to produce quality practical projects</x:v>
+      </x:c>
+      <x:c r="D13" s="196" t="str">
+        <x:v>Breadboard basic marking and jointing → Clock and Carry-all multi-step production → Mirror and Bedside Table complex joinery, jigs, assembly and finishing.</x:v>
+      </x:c>
+      <x:c r="E13" s="196" t="str">
+        <x:v>Matrix row 9; Breadboard Modules 02–04; Clock Weeks 5–14; Carry-all Weeks 5–18; Mirror process activities; Bedside Table Weeks 3–16.</x:v>
+      </x:c>
+      <x:c r="F13" s="197" t="str">
+        <x:v>Retain the nominated production records across simple, multi-step and complex joinery stages.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="96" customHeight="1">
+      <x:c r="A14" s="266" t="str">
+        <x:v>IND54</x:v>
+      </x:c>
+      <x:c r="B14" s="423" t="str">
+        <x:f>IF(COUNTIF('Syllabus Alignment Matrix'!E10,"E")+COUNTIF('Syllabus Alignment Matrix'!I10,"E")+COUNTIF('Syllabus Alignment Matrix'!K10,"E")+COUNTIF('Syllabus Alignment Matrix'!M10,"E")+COUNTIF('Syllabus Alignment Matrix'!O10,"E")&gt;0,"Covered",IF(COUNTIF('Syllabus Alignment Matrix'!E10,"Gap")+COUNTIF('Syllabus Alignment Matrix'!I10,"Gap")+COUNTIF('Syllabus Alignment Matrix'!K10,"Gap")+COUNTIF('Syllabus Alignment Matrix'!M10,"Gap")+COUNTIF('Syllabus Alignment Matrix'!O10,"Gap")&gt;0,"Has gaps",IF(COUNTIF('Syllabus Alignment Matrix'!E10,"I")+COUNTIF('Syllabus Alignment Matrix'!I10,"I")+COUNTIF('Syllabus Alignment Matrix'!K10,"I")+COUNTIF('Syllabus Alignment Matrix'!M10,"I")+COUNTIF('Syllabus Alignment Matrix'!O10,"I")+COUNTIF('Syllabus Alignment Matrix'!E10,"P")+COUNTIF('Syllabus Alignment Matrix'!I10,"P")+COUNTIF('Syllabus Alignment Matrix'!K10,"P")+COUNTIF('Syllabus Alignment Matrix'!M10,"P")+COUNTIF('Syllabus Alignment Matrix'!O10,"P")+COUNTIF('Syllabus Alignment Matrix'!E10,"Partial")+COUNTIF('Syllabus Alignment Matrix'!I10,"Partial")+COUNTIF('Syllabus Alignment Matrix'!K10,"Partial")+COUNTIF('Syllabus Alignment Matrix'!M10,"Partial")+COUNTIF('Syllabus Alignment Matrix'!O10,"Partial")&gt;0,"Partially covered","Has gaps")))</x:f>
+        <x:v>Covered</x:v>
+      </x:c>
+      <x:c r="C14" s="196" t="str">
+        <x:v>selects, justifies and uses a range of relevant and associated materials for specific applications</x:v>
+      </x:c>
+      <x:c r="D14" s="196" t="str">
+        <x:v>Breadboard grain/layout selection → Clock and Carry-all timber choice and responsible use → Year 10 cutting lists, matched grain and application-specific selection.</x:v>
+      </x:c>
+      <x:c r="E14" s="196" t="str">
+        <x:v>Matrix row 10; Breadboard Module 02; Clock Weeks 3–4 and 11–12; Carry-all Weeks 3–4; Mirror materials/cutting list; Bedside Table Weeks 3–4.</x:v>
+      </x:c>
+      <x:c r="F14" s="197" t="str">
+        <x:v>Retain the project-specific timber selection and justification records across the sequence.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="96" customHeight="1">
+      <x:c r="A15" s="266" t="str">
+        <x:v>IND55</x:v>
+      </x:c>
+      <x:c r="B15" s="423" t="str">
+        <x:f>IF(COUNTIF('Syllabus Alignment Matrix'!E11,"E")+COUNTIF('Syllabus Alignment Matrix'!I11,"E")+COUNTIF('Syllabus Alignment Matrix'!K11,"E")+COUNTIF('Syllabus Alignment Matrix'!M11,"E")+COUNTIF('Syllabus Alignment Matrix'!O11,"E")&gt;0,"Covered",IF(COUNTIF('Syllabus Alignment Matrix'!E11,"Gap")+COUNTIF('Syllabus Alignment Matrix'!I11,"Gap")+COUNTIF('Syllabus Alignment Matrix'!K11,"Gap")+COUNTIF('Syllabus Alignment Matrix'!M11,"Gap")+COUNTIF('Syllabus Alignment Matrix'!O11,"Gap")&gt;0,"Has gaps",IF(COUNTIF('Syllabus Alignment Matrix'!E11,"I")+COUNTIF('Syllabus Alignment Matrix'!I11,"I")+COUNTIF('Syllabus Alignment Matrix'!K11,"I")+COUNTIF('Syllabus Alignment Matrix'!M11,"I")+COUNTIF('Syllabus Alignment Matrix'!O11,"I")+COUNTIF('Syllabus Alignment Matrix'!E11,"P")+COUNTIF('Syllabus Alignment Matrix'!I11,"P")+COUNTIF('Syllabus Alignment Matrix'!K11,"P")+COUNTIF('Syllabus Alignment Matrix'!M11,"P")+COUNTIF('Syllabus Alignment Matrix'!O11,"P")+COUNTIF('Syllabus Alignment Matrix'!E11,"Partial")+COUNTIF('Syllabus Alignment Matrix'!I11,"Partial")+COUNTIF('Syllabus Alignment Matrix'!K11,"Partial")+COUNTIF('Syllabus Alignment Matrix'!M11,"Partial")+COUNTIF('Syllabus Alignment Matrix'!O11,"Partial")&gt;0,"Partially covered","Has gaps")))</x:f>
+        <x:v>Covered</x:v>
+      </x:c>
+      <x:c r="C15" s="196" t="str">
+        <x:v>selects, interprets and applies a range of suitable communication techniques in the development, planning, production and presentation of ideas and projects</x:v>
+      </x:c>
+      <x:c r="D15" s="196" t="str">
+        <x:v>Early photo/caption folios → drawings and cutting lists → Year 10 portfolio, folio, evidence selection and criterion-based presentation.</x:v>
+      </x:c>
+      <x:c r="E15" s="196" t="str">
+        <x:v>Matrix row 11; project folios, drawings, captions, portfolio activities and PDF/print outputs across the audited pathway.</x:v>
+      </x:c>
+      <x:c r="F15" s="197" t="str">
+        <x:v>Retain the named folio, drawing, caption, portfolio and PDF outputs as the communication trail.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="116" customHeight="1">
+      <x:c r="A16" s="266" t="str">
+        <x:v>IND56</x:v>
+      </x:c>
+      <x:c r="B16" s="506" t="str">
+        <x:f>IF(COUNTIF('Syllabus Alignment Matrix'!E12,"E")+COUNTIF('Syllabus Alignment Matrix'!I12,"E")+COUNTIF('Syllabus Alignment Matrix'!K12,"E")+COUNTIF('Syllabus Alignment Matrix'!M12,"E")+COUNTIF('Syllabus Alignment Matrix'!O12,"E")&gt;0,"Covered",IF(COUNTIF('Syllabus Alignment Matrix'!E12,"Gap")+COUNTIF('Syllabus Alignment Matrix'!I12,"Gap")+COUNTIF('Syllabus Alignment Matrix'!K12,"Gap")+COUNTIF('Syllabus Alignment Matrix'!M12,"Gap")+COUNTIF('Syllabus Alignment Matrix'!O12,"Gap")&gt;0,"Has gaps",IF(COUNTIF('Syllabus Alignment Matrix'!E12,"I")+COUNTIF('Syllabus Alignment Matrix'!I12,"I")+COUNTIF('Syllabus Alignment Matrix'!K12,"I")+COUNTIF('Syllabus Alignment Matrix'!M12,"I")+COUNTIF('Syllabus Alignment Matrix'!O12,"I")+COUNTIF('Syllabus Alignment Matrix'!E12,"P")+COUNTIF('Syllabus Alignment Matrix'!I12,"P")+COUNTIF('Syllabus Alignment Matrix'!K12,"P")+COUNTIF('Syllabus Alignment Matrix'!M12,"P")+COUNTIF('Syllabus Alignment Matrix'!O12,"P")+COUNTIF('Syllabus Alignment Matrix'!E12,"Partial")+COUNTIF('Syllabus Alignment Matrix'!I12,"Partial")+COUNTIF('Syllabus Alignment Matrix'!K12,"Partial")+COUNTIF('Syllabus Alignment Matrix'!M12,"Partial")+COUNTIF('Syllabus Alignment Matrix'!O12,"Partial")&gt;0,"Partially covered","Has gaps")))</x:f>
+        <x:v>Covered</x:v>
+      </x:c>
+      <x:c r="C16" s="196" t="str">
+        <x:v>identifies and participates in collaborative work practices in the learning environment</x:v>
+      </x:c>
+      <x:c r="D16" s="196" t="str">
+        <x:v>Stage 1 Breadboard introduces a structured peer-feedback record. The Mirror Portfolio Workbook now adds a local Year 10 peer quality check: named roles, criterion/evidence, feedback, a justified decision, result check and workshop handover. Bedside Table retains the deeper live peer QA response. The record deepens across Years 9-10; Mirror publication and live re-audit remain pending.</x:v>
+      </x:c>
+      <x:c r="E16" s="196" t="str">
+        <x:v>Matrix row 12; Breadboard Module 05 live activity; Mirror Portfolio Workbook local Peer Quality Check and Workshop Handover; Bedside Table Weeks 19-20 live response; Project Evidence rows 5, 9 and 10; Source Register S18-S19.</x:v>
+      </x:c>
+      <x:c r="F16" s="197" t="str">
+        <x:v>Pathway evidence is covered. Mirror's project-level evidence is locally repaired and awaits publication/live re-audit; individual student achievement is not asserted.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="96" customHeight="1">
+      <x:c r="A17" s="266" t="str">
+        <x:v>IND57</x:v>
+      </x:c>
+      <x:c r="B17" s="423" t="str">
+        <x:f>IF(COUNTIF('Syllabus Alignment Matrix'!E13,"E")+COUNTIF('Syllabus Alignment Matrix'!I13,"E")+COUNTIF('Syllabus Alignment Matrix'!K13,"E")+COUNTIF('Syllabus Alignment Matrix'!M13,"E")+COUNTIF('Syllabus Alignment Matrix'!O13,"E")&gt;0,"Covered",IF(COUNTIF('Syllabus Alignment Matrix'!E13,"Gap")+COUNTIF('Syllabus Alignment Matrix'!I13,"Gap")+COUNTIF('Syllabus Alignment Matrix'!K13,"Gap")+COUNTIF('Syllabus Alignment Matrix'!M13,"Gap")+COUNTIF('Syllabus Alignment Matrix'!O13,"Gap")&gt;0,"Has gaps",IF(COUNTIF('Syllabus Alignment Matrix'!E13,"I")+COUNTIF('Syllabus Alignment Matrix'!I13,"I")+COUNTIF('Syllabus Alignment Matrix'!K13,"I")+COUNTIF('Syllabus Alignment Matrix'!M13,"I")+COUNTIF('Syllabus Alignment Matrix'!O13,"I")+COUNTIF('Syllabus Alignment Matrix'!E13,"P")+COUNTIF('Syllabus Alignment Matrix'!I13,"P")+COUNTIF('Syllabus Alignment Matrix'!K13,"P")+COUNTIF('Syllabus Alignment Matrix'!M13,"P")+COUNTIF('Syllabus Alignment Matrix'!O13,"P")+COUNTIF('Syllabus Alignment Matrix'!E13,"Partial")+COUNTIF('Syllabus Alignment Matrix'!I13,"Partial")+COUNTIF('Syllabus Alignment Matrix'!K13,"Partial")+COUNTIF('Syllabus Alignment Matrix'!M13,"Partial")+COUNTIF('Syllabus Alignment Matrix'!O13,"Partial")&gt;0,"Partially covered","Has gaps")))</x:f>
+        <x:v>Covered</x:v>
+      </x:c>
+      <x:c r="C17" s="196" t="str">
+        <x:v>applies and transfers skills, processes and materials to a variety of contexts and projects</x:v>
+      </x:c>
+      <x:c r="D17" s="196" t="str">
+        <x:v>Breadboard transfer remains implicit → Clock, Carry-all and Bedside Table require explicit future-use or problem-solving transfer evidence; Mirror remains practised/developed.</x:v>
+      </x:c>
+      <x:c r="E17" s="196" t="str">
+        <x:v>Matrix row 13; Clock and Bedside Table Weeks 19–20; Carry-all Weeks 5–6 and 19–20; Breadboard/Mirror supporting practice.</x:v>
+      </x:c>
+      <x:c r="F17" s="197" t="str">
+        <x:v>Retain the later explicit transfer prompts that complete the earlier implicit practice.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="96" customHeight="1">
+      <x:c r="A18" s="266" t="str">
+        <x:v>IND58</x:v>
+      </x:c>
+      <x:c r="B18" s="423" t="str">
+        <x:f>IF(COUNTIF('Syllabus Alignment Matrix'!E14,"E")+COUNTIF('Syllabus Alignment Matrix'!I14,"E")+COUNTIF('Syllabus Alignment Matrix'!K14,"E")+COUNTIF('Syllabus Alignment Matrix'!M14,"E")+COUNTIF('Syllabus Alignment Matrix'!O14,"E")&gt;0,"Covered",IF(COUNTIF('Syllabus Alignment Matrix'!E14,"Gap")+COUNTIF('Syllabus Alignment Matrix'!I14,"Gap")+COUNTIF('Syllabus Alignment Matrix'!K14,"Gap")+COUNTIF('Syllabus Alignment Matrix'!M14,"Gap")+COUNTIF('Syllabus Alignment Matrix'!O14,"Gap")&gt;0,"Has gaps",IF(COUNTIF('Syllabus Alignment Matrix'!E14,"I")+COUNTIF('Syllabus Alignment Matrix'!I14,"I")+COUNTIF('Syllabus Alignment Matrix'!K14,"I")+COUNTIF('Syllabus Alignment Matrix'!M14,"I")+COUNTIF('Syllabus Alignment Matrix'!O14,"I")+COUNTIF('Syllabus Alignment Matrix'!E14,"P")+COUNTIF('Syllabus Alignment Matrix'!I14,"P")+COUNTIF('Syllabus Alignment Matrix'!K14,"P")+COUNTIF('Syllabus Alignment Matrix'!M14,"P")+COUNTIF('Syllabus Alignment Matrix'!O14,"P")+COUNTIF('Syllabus Alignment Matrix'!E14,"Partial")+COUNTIF('Syllabus Alignment Matrix'!I14,"Partial")+COUNTIF('Syllabus Alignment Matrix'!K14,"Partial")+COUNTIF('Syllabus Alignment Matrix'!M14,"Partial")+COUNTIF('Syllabus Alignment Matrix'!O14,"Partial")&gt;0,"Partially covered","Has gaps")))</x:f>
+        <x:v>Covered</x:v>
+      </x:c>
+      <x:c r="C18" s="196" t="str">
+        <x:v>evaluates products in terms of functional, economic, aesthetic and environmental qualities and quality of construction</x:v>
+      </x:c>
+      <x:c r="D18" s="196" t="str">
+        <x:v>Early PMI/folio evaluation → Carry-all problem-correction evidence → Year 10 criterion-based product evaluation and final reflection.</x:v>
+      </x:c>
+      <x:c r="E18" s="196" t="str">
+        <x:v>Matrix row 14; folio/PMI evaluation at Breadboard and Clock; problem correction at Carry-all; criterion-based Year 10 evaluation.</x:v>
+      </x:c>
+      <x:c r="F18" s="197" t="str">
+        <x:v>Retain the criterion-linked Year 10 evaluation and reflection evidence.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="96" customHeight="1">
+      <x:c r="A19" s="266" t="str">
+        <x:v>IND59</x:v>
+      </x:c>
+      <x:c r="B19" s="423" t="str">
+        <x:f>IF(COUNTIF('Syllabus Alignment Matrix'!E15,"E")+COUNTIF('Syllabus Alignment Matrix'!I15,"E")+COUNTIF('Syllabus Alignment Matrix'!K15,"E")+COUNTIF('Syllabus Alignment Matrix'!M15,"E")+COUNTIF('Syllabus Alignment Matrix'!O15,"E")&gt;0,"Covered",IF(COUNTIF('Syllabus Alignment Matrix'!E15,"Gap")+COUNTIF('Syllabus Alignment Matrix'!I15,"Gap")+COUNTIF('Syllabus Alignment Matrix'!K15,"Gap")+COUNTIF('Syllabus Alignment Matrix'!M15,"Gap")+COUNTIF('Syllabus Alignment Matrix'!O15,"Gap")&gt;0,"Has gaps",IF(COUNTIF('Syllabus Alignment Matrix'!E15,"I")+COUNTIF('Syllabus Alignment Matrix'!I15,"I")+COUNTIF('Syllabus Alignment Matrix'!K15,"I")+COUNTIF('Syllabus Alignment Matrix'!M15,"I")+COUNTIF('Syllabus Alignment Matrix'!O15,"I")+COUNTIF('Syllabus Alignment Matrix'!E15,"P")+COUNTIF('Syllabus Alignment Matrix'!I15,"P")+COUNTIF('Syllabus Alignment Matrix'!K15,"P")+COUNTIF('Syllabus Alignment Matrix'!M15,"P")+COUNTIF('Syllabus Alignment Matrix'!O15,"P")+COUNTIF('Syllabus Alignment Matrix'!E15,"Partial")+COUNTIF('Syllabus Alignment Matrix'!I15,"Partial")+COUNTIF('Syllabus Alignment Matrix'!K15,"Partial")+COUNTIF('Syllabus Alignment Matrix'!M15,"Partial")+COUNTIF('Syllabus Alignment Matrix'!O15,"Partial")&gt;0,"Partially covered","Has gaps")))</x:f>
+        <x:v>Covered</x:v>
+      </x:c>
+      <x:c r="C19" s="196" t="str">
+        <x:v>describes, analyses and uses a range of current, new and emerging technologies and their various applications</x:v>
+      </x:c>
+      <x:c r="D19" s="196" t="str">
+        <x:v>Clock Weeks 15-16 is the explicit formal-current evidence point. Carry-all provides a later introductory comparison; Breadboard, Mirror and Bedside Table list the outcome for course context but do not claim a separate project-level IND59 assessment.</x:v>
+      </x:c>
+      <x:c r="E19" s="196" t="str">
+        <x:v>Matrix row 15; Clock Weeks 15-16; Carry-all Weeks 3-4; local course-context wording updates recorded at S19.</x:v>
+      </x:c>
+      <x:c r="F19" s="197" t="str">
+        <x:v>Pathway coverage is retained through Clock. Local wording clarification awaits publication/live re-audit; no generic duplicated technology activity is required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="96" customHeight="1">
+      <x:c r="A20" s="267" t="str">
+        <x:v>IND510</x:v>
+      </x:c>
+      <x:c r="B20" s="424" t="str">
+        <x:f>IF(COUNTIF('Syllabus Alignment Matrix'!E16,"E")+COUNTIF('Syllabus Alignment Matrix'!I16,"E")+COUNTIF('Syllabus Alignment Matrix'!K16,"E")+COUNTIF('Syllabus Alignment Matrix'!M16,"E")+COUNTIF('Syllabus Alignment Matrix'!O16,"E")&gt;0,"Covered",IF(COUNTIF('Syllabus Alignment Matrix'!E16,"Gap")+COUNTIF('Syllabus Alignment Matrix'!I16,"Gap")+COUNTIF('Syllabus Alignment Matrix'!K16,"Gap")+COUNTIF('Syllabus Alignment Matrix'!M16,"Gap")+COUNTIF('Syllabus Alignment Matrix'!O16,"Gap")&gt;0,"Has gaps",IF(COUNTIF('Syllabus Alignment Matrix'!E16,"I")+COUNTIF('Syllabus Alignment Matrix'!I16,"I")+COUNTIF('Syllabus Alignment Matrix'!K16,"I")+COUNTIF('Syllabus Alignment Matrix'!M16,"I")+COUNTIF('Syllabus Alignment Matrix'!O16,"I")+COUNTIF('Syllabus Alignment Matrix'!E16,"P")+COUNTIF('Syllabus Alignment Matrix'!I16,"P")+COUNTIF('Syllabus Alignment Matrix'!K16,"P")+COUNTIF('Syllabus Alignment Matrix'!M16,"P")+COUNTIF('Syllabus Alignment Matrix'!O16,"P")+COUNTIF('Syllabus Alignment Matrix'!E16,"Partial")+COUNTIF('Syllabus Alignment Matrix'!I16,"Partial")+COUNTIF('Syllabus Alignment Matrix'!K16,"Partial")+COUNTIF('Syllabus Alignment Matrix'!M16,"Partial")+COUNTIF('Syllabus Alignment Matrix'!O16,"Partial")&gt;0,"Partially covered","Has gaps")))</x:f>
+        <x:v>Covered</x:v>
+      </x:c>
+      <x:c r="C20" s="199" t="str">
+        <x:v>describes, analyses and evaluates the impact of technology on society, the environment and cultural issues locally and globally</x:v>
+      </x:c>
+      <x:c r="D20" s="199" t="str">
+        <x:v>Breadboard sustainability evidence → Carry-all cultural/responsible-use evidence → Bedside Table lifecycle/impact evidence. Clock and Mirror provide supporting practice.</x:v>
+      </x:c>
+      <x:c r="E20" s="199" t="str">
+        <x:v>Matrix row 16; Breadboard Module 04; Carry-all Weeks 3–4; Bedside Table Weeks 15–16; Clock/Mirror supporting practice.</x:v>
+      </x:c>
+      <x:c r="F20" s="200" t="str">
+        <x:v>Retain the lifecycle, sustainability and cultural-impact evidence that completes earlier supporting practice.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F2"/>
+    <x:mergeCell ref="A3:F4"/>
+    <x:mergeCell ref="D6:F6"/>
+    <x:mergeCell ref="D7:F9"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="54" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="46" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="54" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="62" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="31" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="17" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="38" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="42" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="346" t="str">
+        <x:v>Current Program Content Map</x:v>
+      </x:c>
+      <x:c r="B1" s="346"/>
+      <x:c r="C1" s="346"/>
+      <x:c r="D1" s="346"/>
+      <x:c r="E1" s="346"/>
+      <x:c r="F1" s="346"/>
+      <x:c r="G1" s="346"/>
+      <x:c r="H1" s="346"/>
+      <x:c r="I1" s="346"/>
+      <x:c r="J1" s="346"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="346"/>
+      <x:c r="B2" s="346"/>
+      <x:c r="C2" s="346"/>
+      <x:c r="D2" s="346"/>
+      <x:c r="E2" s="346"/>
+      <x:c r="F2" s="346"/>
+      <x:c r="G2" s="346"/>
+      <x:c r="H2" s="346"/>
+      <x:c r="I2" s="346"/>
+      <x:c r="J2" s="346"/>
+    </x:row>
+    <x:row r="3" ht="40" customHeight="1">
+      <x:c r="A3" s="225" t="str">
+        <x:v>Authority: stage_5_timber_2021-06-16.docx. This sheet consolidates 253 source placements into 77 unique exact top-level statements; spacing alone is normalised. The program links outcomes to whole units, not individual content statements, so no dot-point-to-IND crosswalk is inferred. This is complete against the supplied program, not proof that every official syllabus dot point has been extracted.</x:v>
+      </x:c>
+      <x:c r="B3" s="225"/>
+      <x:c r="C3" s="225"/>
+      <x:c r="D3" s="225"/>
+      <x:c r="E3" s="225"/>
+      <x:c r="F3" s="225"/>
+      <x:c r="G3" s="225"/>
+      <x:c r="H3" s="225"/>
+      <x:c r="I3" s="225"/>
+      <x:c r="J3" s="225"/>
+    </x:row>
+    <x:row r="4" ht="40" customHeight="1">
+      <x:c r="A4" s="225"/>
+      <x:c r="B4" s="225"/>
+      <x:c r="C4" s="225"/>
+      <x:c r="D4" s="225"/>
+      <x:c r="E4" s="225"/>
+      <x:c r="F4" s="225"/>
+      <x:c r="G4" s="225"/>
+      <x:c r="H4" s="225"/>
+      <x:c r="I4" s="225"/>
+      <x:c r="J4" s="225"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="427" t="str">
+        <x:v>Formal project</x:v>
+      </x:c>
+      <x:c r="B6" s="427" t="str">
+        <x:v>Source-defined scaffold role</x:v>
+      </x:c>
+      <x:c r="C6" s="427" t="str">
+        <x:v>Source authority</x:v>
+      </x:c>
+      <x:c r="E6" s="347" t="str">
+        <x:v>Content-map status</x:v>
+      </x:c>
+      <x:c r="F6" s="347" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="H6" s="227" t="str">
+        <x:v>Traceability boundary</x:v>
+      </x:c>
+      <x:c r="I6" s="227"/>
+      <x:c r="J6" s="227"/>
+    </x:row>
+    <x:row r="7" ht="72" customHeight="1">
+      <x:c r="A7" s="259" t="str">
+        <x:v>Breadboard</x:v>
+      </x:c>
+      <x:c r="B7" s="248" t="str">
+        <x:v>For the commencement of the 200-hour course, this unit provides the opportunity for students to gain basic hand skills and confidence in working with timber. Students are required to select and use skills, techniques, tools, equipment and materials specifically suited to their individual project. Students are required to comprehensively document the skills they have learned to demonstrate their understanding of content and safety related to the basic woodworking skills</x:v>
+      </x:c>
+      <x:c r="C7" s="249" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 10, row 1</x:v>
+      </x:c>
+      <x:c r="E7" s="404" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="F7" s="405" t="n">
+        <x:f>COUNTIF($H$16:$H$92,E7)</x:f>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H7" s="412" t="str">
+        <x:v>Mapped means the exact statement occurs in at least one formal project represented in the audited hub. It does not claim an exact webpage module match unless a page is named elsewhere. Has gaps is reserved for the two Pen-only lathe statements: the program contains them, but no Pen project/site evidence row exists. Named teaching activities, student evidence and resources are preserved from the source rather than inferred.</x:v>
+      </x:c>
+      <x:c r="I7" s="412"/>
+      <x:c r="J7" s="412"/>
+    </x:row>
+    <x:row r="8" ht="72" customHeight="1">
+      <x:c r="A8" s="260" t="str">
+        <x:v>Clock</x:v>
+      </x:c>
+      <x:c r="B8" s="251" t="str">
+        <x:v>As the following unit to the breadboard, this unit enables students to use the basic skills they have developed to make decisions about the design and manufacture of this project. Students are encouraged to work more autonomously, though still guided. This subject aims to promote students’ confidence in their own abilities. Students will learn about timber conversion and seasoning throughout this unit.</x:v>
+      </x:c>
+      <x:c r="C8" s="252" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 16, row 1</x:v>
+      </x:c>
+      <x:c r="E8" s="408" t="str">
+        <x:v>Has gaps</x:v>
+      </x:c>
+      <x:c r="F8" s="409" t="n">
+        <x:f>COUNTIF($H$16:$H$92,E8)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H8" s="412"/>
+      <x:c r="I8" s="412"/>
+      <x:c r="J8" s="412"/>
+    </x:row>
+    <x:row r="9" ht="72" customHeight="1">
+      <x:c r="A9" s="260" t="str">
+        <x:v>Pen</x:v>
+      </x:c>
+      <x:c r="B9" s="251" t="str">
+        <x:v>The pen is an additional unit carried out after either the clock or the tool carryall. This unit is designed to give students some exposure to wood turning. This unit can be completed in one to two week.</x:v>
+      </x:c>
+      <x:c r="C9" s="252" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 22, row 1</x:v>
+      </x:c>
+      <x:c r="H9" s="412"/>
+      <x:c r="I9" s="412"/>
+      <x:c r="J9" s="412"/>
+    </x:row>
+    <x:row r="10" ht="72" customHeight="1">
+      <x:c r="A10" s="260" t="str">
+        <x:v>Tool Carry-all</x:v>
+      </x:c>
+      <x:c r="B10" s="251" t="str">
+        <x:v>As the final large unit of the year 9 wood technology course the tool carry all is aimed at developing some more advanced techniques in joinery. Students have the option to attempt a box pin joint or a dovetail joint for their project, this challenges students to utilise their newly developed knowledge and skills. Students will also gain knowledge in the theory of joinery both traditional and modern, and research different finishing techniques that can be used for the project.</x:v>
+      </x:c>
+      <x:c r="C10" s="252" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 28, row 1</x:v>
+      </x:c>
+      <x:c r="H10" s="412"/>
+      <x:c r="I10" s="412"/>
+      <x:c r="J10" s="412"/>
+    </x:row>
+    <x:row r="11" ht="72" customHeight="1">
+      <x:c r="A11" s="260" t="str">
+        <x:v>Mirror</x:v>
+      </x:c>
+      <x:c r="B11" s="251" t="str">
+        <x:v>The mirror frames’ flexible design allows students to use design principles to enhance and individualise their project. Students will develop and use jigs to manufacture components of the project. Students will be asked to investigate various joining and fabrication techniques.</x:v>
+      </x:c>
+      <x:c r="C11" s="252" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 34, row 1</x:v>
+      </x:c>
+      <x:c r="H11" s="412"/>
+      <x:c r="I11" s="412"/>
+      <x:c r="J11" s="412"/>
+    </x:row>
+    <x:row r="12" ht="72" customHeight="1">
+      <x:c r="A12" s="261" t="str">
+        <x:v>Bedside Table</x:v>
+      </x:c>
+      <x:c r="B12" s="254" t="str">
+        <x:v>As the culmination of the 200-hour course, this unit provides the opportunity for students to draw together all the knowledge, skills and understanding developed in the previous units Students are required to select and use skills, techniques, tools, equipment and materials specifically suited to their individual project. The development and production of the project are documented in detail and presented in a comprehensive project report using appropriate workplace communication skills.</x:v>
+      </x:c>
+      <x:c r="C12" s="255" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 40, row 1</x:v>
+      </x:c>
+      <x:c r="H12" s="412"/>
+      <x:c r="I12" s="412"/>
+      <x:c r="J12" s="412"/>
+    </x:row>
+    <x:row r="15" ht="40" customHeight="1">
+      <x:c r="A15" s="370" t="str">
+        <x:v>Content ID</x:v>
+      </x:c>
+      <x:c r="B15" s="370" t="str">
+        <x:v>Exact current-program content statement</x:v>
+      </x:c>
+      <x:c r="C15" s="370" t="str">
+        <x:v>Exact examples / elaborations</x:v>
+      </x:c>
+      <x:c r="D15" s="370" t="str">
+        <x:v>Formal project and week placements</x:v>
+      </x:c>
+      <x:c r="E15" s="370" t="str">
+        <x:v>Programmed learning / activity</x:v>
+      </x:c>
+      <x:c r="F15" s="370" t="str">
+        <x:v>Source-named student evidence / resource</x:v>
+      </x:c>
+      <x:c r="G15" s="370" t="str">
+        <x:v>Audited hub evidence pointer</x:v>
+      </x:c>
+      <x:c r="H15" s="370" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="I15" s="370" t="str">
+        <x:v>Source authority</x:v>
+      </x:c>
+      <x:c r="J15" s="370" t="str">
+        <x:v>Required action / limitation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="594" hidden="0" customHeight="1">
+      <x:c r="A16" s="465" t="str">
+        <x:v>CP001</x:v>
+      </x:c>
+      <x:c r="B16" s="448" t="str">
+        <x:v>safely use and maintain hand, power and machine tools</x:v>
+      </x:c>
+      <x:c r="C16" s="448" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D16" s="448" t="str">
+        <x:v>Breadboard Week 1
+Breadboard Week 2
+Breadboard Week 10
+Clock Week 1
+Tool Carry-all Week 10
+Mirror Week 2
+Mirror Week 4
+Mirror Week 5
+Mirror Week 6
+Mirror Week 10
+Bedside Table Week 2
+Bedside Table Week 3
+Bedside Table Week 4
+Bedside Table Week 5
+Bedside Table Week 6</x:v>
+      </x:c>
+      <x:c r="E16" s="448" t="str">
+        <x:v>Breadboard Week 1: Workshop introduction. Marking and measuring exercise.
+Breadboard Week 2: Mark, cut and plane each side of the breadboard. Onguard safety tests.
+Breadboard Week 10: Present Project and Booklet for marking. Workshop maintenance.
+Clock Week 1: Mark, cut and dress front and back.
+Tool Carry-all Week 10: Cut housing joints for handle (optional depending on student progress) - Workshop Maintenance.
+Mirror Week 2: Design and sketches. Measure and Mark-out. Safe use of Tools and Equipment.
+Mirror Week 4: Dowel, biscuit and Domino Joints. Research and select suitable timbers. Timber properties and suitable joinery
+Mirror Week 5: Dowel, biscuit and Domino Joints, or other suitable Joints.
+Mirror Week 6: Dowel, biscuit and Domino Joints, or other suitable Joints.
+Mirror Week 10: Adding Design Features. Workshop Maintenence.
+Bedside Table Week 2: Design and sketches. Measure and Mark-out.
+Bedside Table Week 3: Dress and prepare timber to size. DAR - FEWTEL
+Bedside Table Week 4: On-guard Mortiser
+Bedside Table Week 5: Mortise and Tenon Joints. On guard - Bandsaw
+Bedside Table Week 6: Mortise and Tenon Joints - SOP Bandsaw</x:v>
+      </x:c>
+      <x:c r="F16" s="448" t="str">
+        <x:v>Breadboard Week 1: Theory: Onguard topics and quiz's General Machine Safety (BasicWorkshop) General Workshop Safety (BasicWorkshop) Workplace Safety Signs (BasicWorkshop) Workshop Tour Discussion and demonstrate - The safe handling of tools, and PPE. Workbook/Folio: Design Brief, constraints and considerations General Workshop Safety Practical: Demonstrate / Observe: Mark out lengths using hand tools. | Resource: Google Classroom - Week 1
+Breadboard Week 2: Theory: Onguard topics and quiz's Woodworking Handtools (BasicWorkshop) Workplace Safety Signs (BasicWorkshop) Discussion: Cup, bow, twist, knots, grain direction, sap veins, heartwood, sapwood Manmade faults. E.g. dents, poor machining etc. Workbook/Folio: SOP Disc Sander Practical: Demonstrate / Observe: The use of Jack Plane, parts and their function. How to apply face /edge marks. | Resource: Google Classroom - Week 2
+Breadboard Week 10: Theory: Workbook/Folio Research timber types and features Practical: Demonstrate / Observe: Workshop maintenance and clean up | Resource: Google Classroom - Week 10
+Clock Week 1: Theory: Onguard topics and quiz's Reinforce the safe use of machines. Refresh the importance of PPE Discussion: Workbook/Folio: Design Constraints SOP for Using the large Forstner Bit. Practical: Demonstrate / Observe: Mark out lengths Apply face marks. Cut timber to length | Resource: Google Classroom - Week 1
+Tool Carry-all Week 10: Theory: Discussion: The importance of good workshop maintenance Practical: Demonstrate / Observe: Manual handling Techniques | Resource: No resource location stated in source row.
+Mirror Week 2: Theory: Discussion: Look at past projects and discuss design ideas as a group. Workbook/Folio: PMI's on existing designs SOP's Sketch out design ideas Practical: Demonstrate / Observe: Cut timber to lengths for mirror frame | Resource: No resource location stated in source row.
+Mirror Week 4: Theory: Discussion: Refresh safety aspects for powertool use Suitability of dowel, biscuits and dominos Workbook/Folio: Joinery Research Practical: Demonstrate / Observe: The use of the dowel, biscuit and domino cutters | Resource: No resource location stated in source row.
+Mirror Week 5: Theory: Discussion: Cont' Refresh safety aspects for powertool use Suitability of dowel, biscuits and dominos Workbook/Folio: Con't Joinery Research Practical: Demonstrate / Observe: Cont' The use of the dowel, biscuit and domino cutters | Resource: No resource location stated in source row.
+Mirror Week 6: Theory: Discussion: Cont' Refresh safety aspects for powertool use Suitability of dowel, biscuits and dominos Workbook/Folio: Con't Joinery Research Practical: Demonstrate / Observe: Cont' The use of the dowel, biscuit and domino cutters | Resource: No resource location stated in source row.
+Mirror Week 10: Theory: Discussion: The importance of good workshop maintenance Practical: Demonstrate / Observe: Manual handling techniques | Resource: No resource location stated in source row.
+Bedside Table Week 2: Theory: Discussion: Look at past projects and discuss design ideas as a group. Workbook/Folio: PMI's on existing designs SOP's Mortise Machine Sketch out design ideas Practical: Demonstrate / Observe: Cut timber to lengths for bedside table | Resource: No resource location stated in source row.
+Bedside Table Week 3: Theory: Discussion: Refresh FEWTEL. DAR Workbook/Folio: Sketch out design ideas (Cont') Modification of existing plans Practical: Demonstrate / Observe: Refresh The use of the handplane / Thicknesser | Resource: No resource location stated in source row.
+Bedside Table Week 4: Theory: Discussion: Refresh safety aspects for Machine use Suitability of Mortise and Tenon Joints Workbook/Folio: Tools, machinery and their uses in making the bedside table Onguard - Mortiser Practical: Demonstrate / Observe: The use of the Mortise Machine | Resource: No resource location stated in source row.
+Bedside Table Week 5: Theory: Discussion: Uses of the bandsaw. Tracking and trouble shooting Workbook/Folio: Onguard - Bandsaw Practical: Demonstrate / Observe: Using the mortise machine and Bandsaw to cut mortise and tenon joints | Resource: No resource location stated in source row.
+Bedside Table Week 6: Theory: Discussion: Uses of the bandsaw. Tracking and trouble shooting Workbook/Folio: SOP - Bandsaw Practical: Demonstrate / Observe: Using the mortise machine and Bandsaw to cut mortise and tenon joints | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G16" s="448" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7
+Tool Carry-all: Project Evidence row 8
+Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H16" s="474" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I16" s="448" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 1
+stage_5_timber_2021-06-16.docx, table 12, row 2
+stage_5_timber_2021-06-16.docx, table 12, row 10
+stage_5_timber_2021-06-16.docx, table 18, row 1
+stage_5_timber_2021-06-16.docx, table 30, row 10
+stage_5_timber_2021-06-16.docx, table 36, row 2
+stage_5_timber_2021-06-16.docx, table 36, row 4
+stage_5_timber_2021-06-16.docx, table 36, row 5
+stage_5_timber_2021-06-16.docx, table 36, row 6
+stage_5_timber_2021-06-16.docx, table 36, row 10
+stage_5_timber_2021-06-16.docx, table 42, row 2
+stage_5_timber_2021-06-16.docx, table 42, row 3
+stage_5_timber_2021-06-16.docx, table 42, row 4
+stage_5_timber_2021-06-16.docx, table 42, row 5
+stage_5_timber_2021-06-16.docx, table 42, row 6</x:v>
+      </x:c>
+      <x:c r="J16" s="449" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="216" hidden="0" customHeight="1">
+      <x:c r="A17" s="466" t="str">
+        <x:v>CP002</x:v>
+      </x:c>
+      <x:c r="B17" s="451" t="str">
+        <x:v>measure and mark out materials accurately from a workshop drawing</x:v>
+      </x:c>
+      <x:c r="C17" s="451" t="str">
+        <x:v>mark out using a try square and marking gauge</x:v>
+      </x:c>
+      <x:c r="D17" s="451" t="str">
+        <x:v>Breadboard Week 1
+Breadboard Week 2
+Clock Week 1
+Tool Carry-all Week 3
+Tool Carry-all Week 9</x:v>
+      </x:c>
+      <x:c r="E17" s="451" t="str">
+        <x:v>Breadboard Week 1: Workshop introduction. Marking and measuring exercise.
+Breadboard Week 2: Mark, cut and plane each side of the breadboard. Onguard safety tests.
+Clock Week 1: Mark, cut and dress front and back.
+Tool Carry-all Week 3: Mark and cut sides of carry-all. Start cutting box-pin or dovetail.
+Tool Carry-all Week 9: Mark, out cut and shape handle.</x:v>
+      </x:c>
+      <x:c r="F17" s="451" t="str">
+        <x:v>Breadboard Week 1: Theory: Onguard topics and quiz's General Machine Safety (BasicWorkshop) General Workshop Safety (BasicWorkshop) Workplace Safety Signs (BasicWorkshop) Workshop Tour Discussion and demonstrate - The safe handling of tools, and PPE. Workbook/Folio: Design Brief, constraints and considerations General Workshop Safety Practical: Demonstrate / Observe: Mark out lengths using hand tools. | Resource: Google Classroom - Week 1
+Breadboard Week 2: Theory: Onguard topics and quiz's Woodworking Handtools (BasicWorkshop) Workplace Safety Signs (BasicWorkshop) Discussion: Cup, bow, twist, knots, grain direction, sap veins, heartwood, sapwood Manmade faults. E.g. dents, poor machining etc. Workbook/Folio: SOP Disc Sander Practical: Demonstrate / Observe: The use of Jack Plane, parts and their function. How to apply face /edge marks. | Resource: Google Classroom - Week 2
+Clock Week 1: Theory: Onguard topics and quiz's Reinforce the safe use of machines. Refresh the importance of PPE Discussion: Workbook/Folio: Design Constraints SOP for Using the large Forstner Bit. Practical: Demonstrate / Observe: Mark out lengths Apply face marks. Cut timber to length | Resource: Google Classroom - Week 1
+Tool Carry-all Week 3: Theory: Discussion: Suitable Joints for this project Workbook/Folio: Qualities of Radiata Pine Practical: Demonstrate / Observe: Mark out lengths Apply face marks. Cut timber to length | Resource: No resource location stated in source row.
+Tool Carry-all Week 9: Theory: Discussion: The use of templates Workbook/Folio: Handle Designs Practical: Demonstrate / Observe: Mark, cut and shape handle | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G17" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7
+Tool Carry-all: Project Evidence row 8</x:v>
+      </x:c>
+      <x:c r="H17" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I17" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 1
+stage_5_timber_2021-06-16.docx, table 12, row 2
+stage_5_timber_2021-06-16.docx, table 18, row 1
+stage_5_timber_2021-06-16.docx, table 30, row 3
+stage_5_timber_2021-06-16.docx, table 30, row 9</x:v>
+      </x:c>
+      <x:c r="J17" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="54" hidden="0" customHeight="1">
+      <x:c r="A18" s="466" t="str">
+        <x:v>CP003</x:v>
+      </x:c>
+      <x:c r="B18" s="451" t="str">
+        <x:v>recognise and comply with WHS signage, for example:</x:v>
+      </x:c>
+      <x:c r="C18" s="451" t="str">
+        <x:v>identify the colours and shapes associated with types of WHS signage</x:v>
+      </x:c>
+      <x:c r="D18" s="451" t="str">
+        <x:v>Breadboard Week 1</x:v>
+      </x:c>
+      <x:c r="E18" s="451" t="str">
+        <x:v>Breadboard Week 1: Workshop introduction. Marking and measuring exercise.</x:v>
+      </x:c>
+      <x:c r="F18" s="451" t="str">
+        <x:v>Breadboard Week 1: Theory: Onguard topics and quiz's General Machine Safety (BasicWorkshop) General Workshop Safety (BasicWorkshop) Workplace Safety Signs (BasicWorkshop) Workshop Tour Discussion and demonstrate - The safe handling of tools, and PPE. Workbook/Folio: Design Brief, constraints and considerations General Workshop Safety Practical: Demonstrate / Observe: Mark out lengths using hand tools. | Resource: Google Classroom - Week 1</x:v>
+      </x:c>
+      <x:c r="G18" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5</x:v>
+      </x:c>
+      <x:c r="H18" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I18" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 1</x:v>
+      </x:c>
+      <x:c r="J18" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="291.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A19" s="466" t="str">
+        <x:v>CP004</x:v>
+      </x:c>
+      <x:c r="B19" s="451" t="str">
+        <x:v>select and use personal protective equipment (PPE) when working with tools, materials and machines, for example:</x:v>
+      </x:c>
+      <x:c r="C19" s="451" t="str">
+        <x:v>wear appropriate footwear
+wear eye protection, eg safety glasses when drilling
+wear protective clothing
+wear ear protection, eg ear muffs when using machinery
+wear eye protection, eg safety glasses when woodturning</x:v>
+      </x:c>
+      <x:c r="D19" s="451" t="str">
+        <x:v>Breadboard Week 2
+Clock Week 1
+Pen Week 1
+Pen Week 2
+Tool Carry-all Week 12
+Mirror Week 2
+Bedside Table Week 2</x:v>
+      </x:c>
+      <x:c r="E19" s="451" t="str">
+        <x:v>Breadboard Week 2: Mark, cut and plane each side of the breadboard. Onguard safety tests.
+Clock Week 1: Mark, cut and dress front and back.
+Pen Week 1: Demonstration of turning. Practice on scrap.
+Pen Week 2: Work on and complete pen.
+Tool Carry-all Week 12: SWMS for tool carry all.
+Mirror Week 2: Design and sketches. Measure and Mark-out. Safe use of Tools and Equipment.
+Bedside Table Week 2: Design and sketches. Measure and Mark-out.</x:v>
+      </x:c>
+      <x:c r="F19" s="451" t="str">
+        <x:v>Breadboard Week 2: Theory: Onguard topics and quiz's Woodworking Handtools (BasicWorkshop) Workplace Safety Signs (BasicWorkshop) Discussion: Cup, bow, twist, knots, grain direction, sap veins, heartwood, sapwood Manmade faults. E.g. dents, poor machining etc. Workbook/Folio: SOP Disc Sander Practical: Demonstrate / Observe: The use of Jack Plane, parts and their function. How to apply face /edge marks. | Resource: Google Classroom - Week 2
+Clock Week 1: Theory: Onguard topics and quiz's Reinforce the safe use of machines. Refresh the importance of PPE Discussion: Workbook/Folio: Design Constraints SOP for Using the large Forstner Bit. Practical: Demonstrate / Observe: Mark out lengths Apply face marks. Cut timber to length | Resource: Google Classroom - Week 1
+Pen Week 1: Theory: Discussion: Types of uses for the Wood Lathe Workbook/Folio: Risk management for using the Lathe Practical: Demonstrate / Observe: Setup and demonstrate turning techniques. Simple scraping and cutting between centres Sanding and finishing on the lathe Turn a timber pen - Start to finish | Resource: No resource location stated in source row.
+Pen Week 2: Demonstrate / Observe: Setup for turning. Simple scraping and cutting between centres - Techniques Sanding and finishing on the lathe Turn a timber pen - Start to finish | Resource: No resource location stated in source row.
+Tool Carry-all Week 12: Theory: Workbook/Folio: Sequencing exercise Safe Work Method Statement Practical: Demonstrate / Observe: Dry assembly glue and clamping process checking for square | Resource: No resource location stated in source row.
+Mirror Week 2: Theory: Discussion: Look at past projects and discuss design ideas as a group. Workbook/Folio: PMI's on existing designs SOP's Sketch out design ideas Practical: Demonstrate / Observe: Cut timber to lengths for mirror frame | Resource: No resource location stated in source row.
+Bedside Table Week 2: Theory: Discussion: Look at past projects and discuss design ideas as a group. Workbook/Folio: PMI's on existing designs SOP's Mortise Machine Sketch out design ideas Practical: Demonstrate / Observe: Cut timber to lengths for bedside table | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G19" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7
+Pen: SCOPE-01; no Project Evidence row
+Tool Carry-all: Project Evidence row 8
+Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H19" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I19" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 2
+stage_5_timber_2021-06-16.docx, table 18, row 1
+stage_5_timber_2021-06-16.docx, table 24, row 1
+stage_5_timber_2021-06-16.docx, table 24, row 2
+stage_5_timber_2021-06-16.docx, table 30, row 12
+stage_5_timber_2021-06-16.docx, table 36, row 2
+stage_5_timber_2021-06-16.docx, table 42, row 2</x:v>
+      </x:c>
+      <x:c r="J19" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="226.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A20" s="466" t="str">
+        <x:v>CP005</x:v>
+      </x:c>
+      <x:c r="B20" s="451" t="str">
+        <x:v>select, use and adjust hand tools in the production of practical projects, for example:</x:v>
+      </x:c>
+      <x:c r="C20" s="451" t="str">
+        <x:v>plane a timber edge in preparation for joining
+using a tenon saw to cut on waste side of line
+using sash cramps to join two boards of timber
+mark out using a try square and marking gauge</x:v>
+      </x:c>
+      <x:c r="D20" s="451" t="str">
+        <x:v>Breadboard Week 2
+Breadboard Week 3
+Clock Week 5
+Tool Carry-all Week 1
+Tool Carry-all Week 3
+Tool Carry-all Week 11</x:v>
+      </x:c>
+      <x:c r="E20" s="451" t="str">
+        <x:v>Breadboard Week 2: Mark, cut and plane each side of the breadboard. Onguard safety tests.
+Breadboard Week 3: Biscuit join sides of breadboard together and cut ends.
+Clock Week 5: Mark, cut and plane chamfer top and bottom of clock and glue to body.
+Tool Carry-all Week 1: Demonstration of how to cut dovetail joint. Students to cut a practice from scrap.
+Tool Carry-all Week 3: Mark and cut sides of carry-all. Start cutting box-pin or dovetail.
+Tool Carry-all Week 11: Assembly of tool carry-all</x:v>
+      </x:c>
+      <x:c r="F20" s="451" t="str">
+        <x:v>Breadboard Week 2: Theory: Onguard topics and quiz's Woodworking Handtools (BasicWorkshop) Workplace Safety Signs (BasicWorkshop) Discussion: Cup, bow, twist, knots, grain direction, sap veins, heartwood, sapwood Manmade faults. E.g. dents, poor machining etc. Workbook/Folio: SOP Disc Sander Practical: Demonstrate / Observe: The use of Jack Plane, parts and their function. How to apply face /edge marks. | Resource: Google Classroom - Week 2
+Breadboard Week 3: Theory: Onguard topics and quiz's Disc Sander (WOODTech) Festo Domino Jointer - Corded/Electric (WOODTech) Bench &amp; Pedestal Drill (BasicWorkshop) Discussion: Grain direction and board layout Workbook/Folio SOP Biscuit Cutter Practical: Demonstrate / Observe: The use of the Biscuit Jointer, Pedestal Drill and disc sander. | Resource: Google Classroom - Week 3
+Clock Week 5: Theory: Discussion: Discuss correct grain direction. Workbook/Folio: Drill/Turning Processes Practical: Demonstrate / Observe: Dry fit and glue carcass. Test for square. Set out and plane back. Design top and bottom. | Resource: Google Classroom - Week 5
+Tool Carry-all Week 1: Theory: Discussion: Refresh Onguard topics and quiz's Reinforce the safe use of machines. Refresh the importance of PPE Workbook/Folio: Materials List Practical: Demonstrate / Observe: Mark out and cut Finger joints / Dovetail joints | Resource: Student Workbook
+Tool Carry-all Week 3: Theory: Discussion: Suitable Joints for this project Workbook/Folio: Qualities of Radiata Pine Practical: Demonstrate / Observe: Mark out lengths Apply face marks. Cut timber to length | Resource: No resource location stated in source row.
+Tool Carry-all Week 11: Theory: Discussion: The importance of dry assembly and checking for square. Workbook/Folio: Nails and Glues worksheets Practical: Demonstrate / Observe: Dry assembly glue and clamping process checking for square | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G20" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7
+Tool Carry-all: Project Evidence row 8</x:v>
+      </x:c>
+      <x:c r="H20" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I20" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 2
+stage_5_timber_2021-06-16.docx, table 12, row 3
+stage_5_timber_2021-06-16.docx, table 18, row 5
+stage_5_timber_2021-06-16.docx, table 30, row 1
+stage_5_timber_2021-06-16.docx, table 30, row 3
+stage_5_timber_2021-06-16.docx, table 30, row 11</x:v>
+      </x:c>
+      <x:c r="J20" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="216" hidden="0" customHeight="1">
+      <x:c r="A21" s="466" t="str">
+        <x:v>CP006</x:v>
+      </x:c>
+      <x:c r="B21" s="451" t="str">
+        <x:v>identify and cut a range of timber joints, for example:</x:v>
+      </x:c>
+      <x:c r="C21" s="451" t="str">
+        <x:v>widening joints, eg biscuit
+box joints, eg rebate, housing, mitre
+carcase joints, eg mortise and tenon, bridle</x:v>
+      </x:c>
+      <x:c r="D21" s="451" t="str">
+        <x:v>Breadboard Week 3
+Breadboard Week 5
+Clock Week 2
+Tool Carry-all Week 1
+Tool Carry-all Week 3
+Tool Carry-all Week 10</x:v>
+      </x:c>
+      <x:c r="E21" s="451" t="str">
+        <x:v>Breadboard Week 3: Biscuit join sides of breadboard together and cut ends.
+Breadboard Week 5: Begin completing laser-cut patterns. Biscuit join ends to the main board.
+Clock Week 2: Mark, cut and dress sides. Drill front with oversize forstner bit.
+Tool Carry-all Week 1: Demonstration of how to cut dovetail joint. Students to cut a practice from scrap.
+Tool Carry-all Week 3: Mark and cut sides of carry-all. Start cutting box-pin or dovetail.
+Tool Carry-all Week 10: Cut housing joints for handle (optional depending on student progress) - Workshop Maintenance.</x:v>
+      </x:c>
+      <x:c r="F21" s="451" t="str">
+        <x:v>Breadboard Week 3: Theory: Onguard topics and quiz's Disc Sander (WOODTech) Festo Domino Jointer - Corded/Electric (WOODTech) Bench &amp; Pedestal Drill (BasicWorkshop) Discussion: Grain direction and board layout Workbook/Folio SOP Biscuit Cutter Practical: Demonstrate / Observe: The use of the Biscuit Jointer, Pedestal Drill and disc sander. | Resource: Google Classroom - Week 3
+Breadboard Week 5: Theory: Discussion Joining techniques Workbook/Folio Joinery Research Practical: Demonstrate / Observe: Dry fitting using sash cramps. Glue and Clamping process | Resource: Google Classroom - Week 5
+Clock Week 2: Theory: Discussion: Discuss the working characteristics of Softwoods in contrast to Hardwoods. Workbook/Folio: Joinery Research Hardware Research Cutting List (Paper Version) Practical: Demonstrate / Observe: Cut Rebates (Sides) Grain direction &amp; strength. Chiseling | Resource: Google Classroom - Week 2
+Tool Carry-all Week 1: Theory: Discussion: Refresh Onguard topics and quiz's Reinforce the safe use of machines. Refresh the importance of PPE Workbook/Folio: Materials List Practical: Demonstrate / Observe: Mark out and cut Finger joints / Dovetail joints | Resource: Student Workbook
+Tool Carry-all Week 3: Theory: Discussion: Suitable Joints for this project Workbook/Folio: Qualities of Radiata Pine Practical: Demonstrate / Observe: Mark out lengths Apply face marks. Cut timber to length | Resource: No resource location stated in source row.
+Tool Carry-all Week 10: Theory: Discussion: The importance of good workshop maintenance Practical: Demonstrate / Observe: Manual handling Techniques | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G21" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7
+Tool Carry-all: Project Evidence row 8</x:v>
+      </x:c>
+      <x:c r="H21" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I21" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 3
+stage_5_timber_2021-06-16.docx, table 12, row 5
+stage_5_timber_2021-06-16.docx, table 18, row 2
+stage_5_timber_2021-06-16.docx, table 30, row 1
+stage_5_timber_2021-06-16.docx, table 30, row 3
+stage_5_timber_2021-06-16.docx, table 30, row 10</x:v>
+      </x:c>
+      <x:c r="J21" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="248.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A22" s="466" t="str">
+        <x:v>CP007</x:v>
+      </x:c>
+      <x:c r="B22" s="451" t="str">
+        <x:v>identify and investigate factors influencing design in timber projects, for example:</x:v>
+      </x:c>
+      <x:c r="C22" s="451" t="str">
+        <x:v>grain
+hardware
+colour
+proportion</x:v>
+      </x:c>
+      <x:c r="D22" s="451" t="str">
+        <x:v>Breadboard Week 3
+Breadboard Week 7
+Clock Week 2
+Tool Carry-all Week 2
+Mirror Week 1
+Bedside Table Week 1</x:v>
+      </x:c>
+      <x:c r="E22" s="451" t="str">
+        <x:v>Breadboard Week 3: Biscuit join sides of breadboard together and cut ends.
+Breadboard Week 7: Patterns must be finished by this week. Sand and prep for finishing.
+Clock Week 2: Mark, cut and dress sides. Drill front with oversize forstner bit.
+Tool Carry-all Week 2: Tools and Techniques used by Aboriginal and/or Torres Strait Islanders.
+Mirror Week 1: Introduction and Workshop Safety. Constraints and limitations.
+Bedside Table Week 1: Introduction. OHS and Risk Management.</x:v>
+      </x:c>
+      <x:c r="F22" s="451" t="str">
+        <x:v>Breadboard Week 3: Theory: Onguard topics and quiz's Disc Sander (WOODTech) Festo Domino Jointer - Corded/Electric (WOODTech) Bench &amp; Pedestal Drill (BasicWorkshop) Discussion: Grain direction and board layout Workbook/Folio SOP Biscuit Cutter Practical: Demonstrate / Observe: The use of the Biscuit Jointer, Pedestal Drill and disc sander. | Resource: Google Classroom - Week 3
+Breadboard Week 7: Theory: Discussion - Types of abrasive material used for surface preparation Workbook/Folio Research Timber Seasoning Practical: Demonstrate / Observe: Sanding Techniques | Resource: Google Classroom - Week 7
+Clock Week 2: Theory: Discussion: Discuss the working characteristics of Softwoods in contrast to Hardwoods. Workbook/Folio: Joinery Research Hardware Research Cutting List (Paper Version) Practical: Demonstrate / Observe: Cut Rebates (Sides) Grain direction &amp; strength. Chiseling | Resource: Google Classroom - Week 2
+Tool Carry-all Week 2: Theory: Discussion: Tools and Techniques used by Aboriginal and/or Torres Strait Islanders. Workbook/Folio: Research types of timbers aboriginal people used for making their tools and equipment. What qualities did these have that made them suitable. | Resource: No resource location stated in source row.
+Mirror Week 1: Theory: Discussion: Refresh Onguard Topics and Quiz's Reinforce the safe use of machines. Refresh the importance of PPE Workbook/Folio: Design brief, constraints and considerations General Workshop Safety Sheet Practical: Demonstrate / Observe: Refresh - Measure, mark and cut a rebate and housing joint. | Resource: No resource location stated in source row.
+Bedside Table Week 1: Theory: Discussion: Refresh Onguard Topics and Quiz's Reinforce the safe use of machines. Refresh the importance of PPE Workbook/Folio: General Workshop Safety Sheet - Refresh Purpose of the table and design Input Practical: Demonstrate / Observe: Refresh - Measure, mark and cut a mortice and tenon joint | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G22" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7
+Tool Carry-all: Project Evidence row 8
+Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H22" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I22" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 3
+stage_5_timber_2021-06-16.docx, table 12, row 7
+stage_5_timber_2021-06-16.docx, table 18, row 2
+stage_5_timber_2021-06-16.docx, table 30, row 2
+stage_5_timber_2021-06-16.docx, table 36, row 1
+stage_5_timber_2021-06-16.docx, table 42, row 1</x:v>
+      </x:c>
+      <x:c r="J22" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="183.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A23" s="466" t="str">
+        <x:v>CP008</x:v>
+      </x:c>
+      <x:c r="B23" s="451" t="str">
+        <x:v>produce practical projects using machines and portable power tools, for example:</x:v>
+      </x:c>
+      <x:c r="C23" s="451" t="str">
+        <x:v>cutting a curve using a jigsaw
+cutting a profile using a router</x:v>
+      </x:c>
+      <x:c r="D23" s="451" t="str">
+        <x:v>Breadboard Week 4
+Breadboard Week 6
+Clock Week 4
+Clock Week 7
+Tool Carry-all Week 9</x:v>
+      </x:c>
+      <x:c r="E23" s="451" t="str">
+        <x:v>Breadboard Week 4: Shape ends. Demonstration of using a laser cutter for patterns. Students to design patterns.
+Breadboard Week 6: Demonstration on how to use the router. Onguard test. Router edges.
+Clock Week 4: Assemble main body component of clock. Cut rebates inside of clock. Industry Connections
+Clock Week 7: Mark and cut rebates for drawer. Mark, cut and plane sides.
+Tool Carry-all Week 9: Mark, out cut and shape handle.</x:v>
+      </x:c>
+      <x:c r="F23" s="451" t="str">
+        <x:v>Breadboard Week 4: Theory: Onguard topics and quiz's Laser Cutter (CleanTech) Discussion: Design options for ends and handles Workbook/Folio: SOP Disc Sander SOP Pedestal Drill Freehand sketches of design ideas Practical: Demonstrate / Observe: The use of the laser cutter (Teacher use only) The use of the jigsaw The use of the pedestal drill and hole saw | Resource: Google Classroom - Week 4
+Breadboard Week 6: Theory: Onguard topics and quiz's Router - Corded/Electric (WOODTech) Discussion Types of router bits and design options Workbook/Folio Router profile sheet Practical: Demonstrate / Observe: The use of a router to cut a profile | Resource: Google Classroom - Week 6
+Clock Week 4: Theory: Discussion: Compare to industry methods. Workbook/Folio: Tools / Machines Used / SOP Make a List and compare the tools/machines the students and industry used. Practical: Demonstrate / Observe: Mark and cut out front and back pieces. Set out sub-top and sub-bottom. | Resource: Google Classroom - Week 4
+Clock Week 7: Theory: Discussion: Possible environmental impact through production of such products. Practical: Demonstrate / Observe: Cut out ‘secret drawer’. Route 6mm chamfer around inside of dial | Resource: Google Classroom - Week 7
+Tool Carry-all Week 9: Theory: Discussion: The use of templates Workbook/Folio: Handle Designs Practical: Demonstrate / Observe: Mark, cut and shape handle | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G23" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7
+Tool Carry-all: Project Evidence row 8</x:v>
+      </x:c>
+      <x:c r="H23" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I23" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 4
+stage_5_timber_2021-06-16.docx, table 12, row 6
+stage_5_timber_2021-06-16.docx, table 18, row 4
+stage_5_timber_2021-06-16.docx, table 18, row 7
+stage_5_timber_2021-06-16.docx, table 30, row 9</x:v>
+      </x:c>
+      <x:c r="J23" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A24" s="466" t="str">
+        <x:v>CP009</x:v>
+      </x:c>
+      <x:c r="B24" s="451" t="str">
+        <x:v>explore timber decoration techniques, for example:</x:v>
+      </x:c>
+      <x:c r="C24" s="451" t="str">
+        <x:v>laser engraving</x:v>
+      </x:c>
+      <x:c r="D24" s="451" t="str">
+        <x:v>Breadboard Week 4
+Breadboard Week 5</x:v>
+      </x:c>
+      <x:c r="E24" s="451" t="str">
+        <x:v>Breadboard Week 4: Shape ends. Demonstration of using a laser cutter for patterns. Students to design patterns.
+Breadboard Week 5: Begin completing laser-cut patterns. Biscuit join ends to the main board.</x:v>
+      </x:c>
+      <x:c r="F24" s="451" t="str">
+        <x:v>Breadboard Week 4: Theory: Onguard topics and quiz's Laser Cutter (CleanTech) Discussion: Design options for ends and handles Workbook/Folio: SOP Disc Sander SOP Pedestal Drill Freehand sketches of design ideas Practical: Demonstrate / Observe: The use of the laser cutter (Teacher use only) The use of the jigsaw The use of the pedestal drill and hole saw | Resource: Google Classroom - Week 4
+Breadboard Week 5: Theory: Discussion Joining techniques Workbook/Folio Joinery Research Practical: Demonstrate / Observe: Dry fitting using sash cramps. Glue and Clamping process | Resource: Google Classroom - Week 5</x:v>
+      </x:c>
+      <x:c r="G24" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5</x:v>
+      </x:c>
+      <x:c r="H24" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I24" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 4
+stage_5_timber_2021-06-16.docx, table 12, row 5</x:v>
+      </x:c>
+      <x:c r="J24" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="216" hidden="0" customHeight="1">
+      <x:c r="A25" s="466" t="str">
+        <x:v>CP010</x:v>
+      </x:c>
+      <x:c r="B25" s="451" t="str">
+        <x:v>use and/or modify existing designs when completing projects</x:v>
+      </x:c>
+      <x:c r="C25" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D25" s="451" t="str">
+        <x:v>Breadboard Week 4
+Clock Week 1
+Tool Carry-all Week 4
+Tool Carry-all Week 5
+Tool Carry-all Week 6</x:v>
+      </x:c>
+      <x:c r="E25" s="451" t="str">
+        <x:v>Breadboard Week 4: Shape ends. Demonstration of using a laser cutter for patterns. Students to design patterns.
+Clock Week 1: Mark, cut and dress front and back.
+Tool Carry-all Week 4: Industry research exercise. Continue with Joint Construction.
+Tool Carry-all Week 5: Industry Research Task. Continue cutting box-pins or dovetails.
+Tool Carry-all Week 6: Industry Research Task. Complete joinery and begin to cut rebate for bottom.</x:v>
+      </x:c>
+      <x:c r="F25" s="451" t="str">
+        <x:v>Breadboard Week 4: Theory: Onguard topics and quiz's Laser Cutter (CleanTech) Discussion: Design options for ends and handles Workbook/Folio: SOP Disc Sander SOP Pedestal Drill Freehand sketches of design ideas Practical: Demonstrate / Observe: The use of the laser cutter (Teacher use only) The use of the jigsaw The use of the pedestal drill and hole saw | Resource: Google Classroom - Week 4
+Clock Week 1: Theory: Onguard topics and quiz's Reinforce the safe use of machines. Refresh the importance of PPE Discussion: Workbook/Folio: Design Constraints SOP for Using the large Forstner Bit. Practical: Demonstrate / Observe: Mark out lengths Apply face marks. Cut timber to length | Resource: Google Classroom - Week 1
+Tool Carry-all Week 4: Theory: Discussion: Discuss the relationships between classroom techniques and Industry manufacturing processes. Workbook/Folio: Industry Research Task Practical: Demonstrate / Observe: Mark out joints - Box-pin or Dovetail Cut joints Chiseling and fine tuning joint fit | Resource: No resource location stated in source row.
+Tool Carry-all Week 5: Theory: Discussion: Discuss the relationships between classroom techniques and Industry manufacturing processes. Workbook/Folio: Industry Research Task Practical: Demonstrate / Observe: Mark out joints - Box-pin or Dovetail Cut joints Chiseling and fine tuning joint fit | Resource: No resource location stated in source row.
+Tool Carry-all Week 6: Theory: Discussion: Discuss the relationships between classroom techniques and Industry manufacturing processes. Workbook/Folio: Industry Research Task Practical: Demonstrate / Observe: Mark out joints - Box-pin or Dovetail Cut joints Chiseling and fine tuning joint fit Cut rebate for bottom | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G25" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7
+Tool Carry-all: Project Evidence row 8</x:v>
+      </x:c>
+      <x:c r="H25" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I25" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 4
+stage_5_timber_2021-06-16.docx, table 18, row 1
+stage_5_timber_2021-06-16.docx, table 30, row 4
+stage_5_timber_2021-06-16.docx, table 30, row 5
+stage_5_timber_2021-06-16.docx, table 30, row 6</x:v>
+      </x:c>
+      <x:c r="J25" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="442.79998779296875" hidden="0" customHeight="1">
+      <x:c r="A26" s="466" t="str">
+        <x:v>CP011</x:v>
+      </x:c>
+      <x:c r="B26" s="451" t="str">
+        <x:v>demonstrate safe workshop practices and procedures, for example:</x:v>
+      </x:c>
+      <x:c r="C26" s="451" t="str">
+        <x:v>clamp materials securely when cutting or drilling
+manage trip hazards in the workshop
+work collaboratively
+lift and carry materials safely
+follow workshop signage instructions
+clamp materials securely when cutting, drilling or routing
+apply finishes in a well-ventilated area</x:v>
+      </x:c>
+      <x:c r="D26" s="451" t="str">
+        <x:v>Breadboard Week 5
+Breadboard Week 10
+Clock Week 1
+Clock Week 10
+Pen Week 1
+Pen Week 2
+Tool Carry-all Week 12
+Mirror Week 1
+Mirror Week 8
+Mirror Week 16
+Bedside Table Week 1
+Bedside Table Week 8
+Bedside Table Week 16</x:v>
+      </x:c>
+      <x:c r="E26" s="451" t="str">
+        <x:v>Breadboard Week 5: Begin completing laser-cut patterns. Biscuit join ends to the main board.
+Breadboard Week 10: Present Project and Booklet for marking. Workshop maintenance.
+Clock Week 1: Mark, cut and dress front and back.
+Clock Week 10: Workshop Maintenance.
+Pen Week 1: Demonstration of turning. Practice on scrap.
+Pen Week 2: Work on and complete pen.
+Tool Carry-all Week 12: SWMS for tool carry all.
+Mirror Week 1: Introduction and Workshop Safety. Constraints and limitations.
+Mirror Week 8: Dry Clamping. Work Method Statements and SOP's.
+Mirror Week 16: Polishing. Sustainability
+Bedside Table Week 1: Introduction. OHS and Risk Management.
+Bedside Table Week 8: Dry Clamping. Work Method Statements and SOP's
+Bedside Table Week 16: Polishing. Sustainability and Environmental Impact</x:v>
+      </x:c>
+      <x:c r="F26" s="451" t="str">
+        <x:v>Breadboard Week 5: Theory: Discussion Joining techniques Workbook/Folio Joinery Research Practical: Demonstrate / Observe: Dry fitting using sash cramps. Glue and Clamping process | Resource: Google Classroom - Week 5
+Breadboard Week 10: Theory: Workbook/Folio Research timber types and features Practical: Demonstrate / Observe: Workshop maintenance and clean up | Resource: Google Classroom - Week 10
+Clock Week 1: Theory: Onguard topics and quiz's Reinforce the safe use of machines. Refresh the importance of PPE Discussion: Workbook/Folio: Design Constraints SOP for Using the large Forstner Bit. Practical: Demonstrate / Observe: Mark out lengths Apply face marks. Cut timber to length | Resource: Google Classroom - Week 1
+Clock Week 10: Theory: Discussion: The importance of good workshop maintenance Practical: Demonstrate / Observe: Manual handling Techniques | Resource: Google Classroom - Week 10
+Pen Week 1: Theory: Discussion: Types of uses for the Wood Lathe Workbook/Folio: Risk management for using the Lathe Practical: Demonstrate / Observe: Setup and demonstrate turning techniques. Simple scraping and cutting between centres Sanding and finishing on the lathe Turn a timber pen - Start to finish | Resource: No resource location stated in source row.
+Pen Week 2: Demonstrate / Observe: Setup for turning. Simple scraping and cutting between centres - Techniques Sanding and finishing on the lathe Turn a timber pen - Start to finish | Resource: No resource location stated in source row.
+Tool Carry-all Week 12: Theory: Workbook/Folio: Sequencing exercise Safe Work Method Statement Practical: Demonstrate / Observe: Dry assembly glue and clamping process checking for square | Resource: No resource location stated in source row.
+Mirror Week 1: Theory: Discussion: Refresh Onguard Topics and Quiz's Reinforce the safe use of machines. Refresh the importance of PPE Workbook/Folio: Design brief, constraints and considerations General Workshop Safety Sheet Practical: Demonstrate / Observe: Refresh - Measure, mark and cut a rebate and housing joint. | Resource: No resource location stated in source row.
+Mirror Week 8: Theory: Discussion: The importance of dry clamping and checking for square Workbook/Folio: WMS for the mirror Practical: Demonstrate / Observe: Dry clamping and adjusting for square. | Resource: No resource location stated in source row.
+Mirror Week 16: Theory: Discussion: The purposes of Timber polishes Practical: Demonstrate / Observe: Ongoing safe workshop procedures | Resource: No resource location stated in source row.
+Bedside Table Week 1: Theory: Discussion: Refresh Onguard Topics and Quiz's Reinforce the safe use of machines. Refresh the importance of PPE Workbook/Folio: General Workshop Safety Sheet - Refresh Purpose of the table and design Input Practical: Demonstrate / Observe: Refresh - Measure, mark and cut a mortice and tenon joint | Resource: No resource location stated in source row.
+Bedside Table Week 8: Theory: Discussion: Refresh The importance of dry clamping and checking for square Workbook/Folio: WMS for the bedside table Practical: Demonstrate / Observe: Dry clamping and adjusting for square. | Resource: No resource location stated in source row.
+Bedside Table Week 16: Theory: Discussion: Refresh The purposes of timber polishes Practical: Demonstrate / Observe: Ongoing safe workshop procedures | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G26" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7
+Pen: SCOPE-01; no Project Evidence row
+Tool Carry-all: Project Evidence row 8
+Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H26" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I26" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 5
+stage_5_timber_2021-06-16.docx, table 12, row 10
+stage_5_timber_2021-06-16.docx, table 18, row 1
+stage_5_timber_2021-06-16.docx, table 18, row 10
+stage_5_timber_2021-06-16.docx, table 24, row 1
+stage_5_timber_2021-06-16.docx, table 24, row 2
+stage_5_timber_2021-06-16.docx, table 30, row 12
+stage_5_timber_2021-06-16.docx, table 36, row 1
+stage_5_timber_2021-06-16.docx, table 36, row 8
+stage_5_timber_2021-06-16.docx, table 36, row 16
+stage_5_timber_2021-06-16.docx, table 42, row 1
+stage_5_timber_2021-06-16.docx, table 42, row 8
+stage_5_timber_2021-06-16.docx, table 42, row 16</x:v>
+      </x:c>
+      <x:c r="J26" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="129.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A27" s="466" t="str">
+        <x:v>CP012</x:v>
+      </x:c>
+      <x:c r="B27" s="451" t="str">
+        <x:v>identify and use a variety of joining methods, for example:</x:v>
+      </x:c>
+      <x:c r="C27" s="451" t="str">
+        <x:v>adhesives/glue
+nails/screws</x:v>
+      </x:c>
+      <x:c r="D27" s="451" t="str">
+        <x:v>Breadboard Week 5
+Clock Week 5
+Clock Week 6
+Tool Carry-all Week 11</x:v>
+      </x:c>
+      <x:c r="E27" s="451" t="str">
+        <x:v>Breadboard Week 5: Begin completing laser-cut patterns. Biscuit join ends to the main board.
+Clock Week 5: Mark, cut and plane chamfer top and bottom of clock and glue to body.
+Clock Week 6: Timber seasoning documentary and exercise. Assemble Carcass.
+Tool Carry-all Week 11: Assembly of tool carry-all</x:v>
+      </x:c>
+      <x:c r="F27" s="451" t="str">
+        <x:v>Breadboard Week 5: Theory: Discussion Joining techniques Workbook/Folio Joinery Research Practical: Demonstrate / Observe: Dry fitting using sash cramps. Glue and Clamping process | Resource: Google Classroom - Week 5
+Clock Week 5: Theory: Discussion: Discuss correct grain direction. Workbook/Folio: Drill/Turning Processes Practical: Demonstrate / Observe: Dry fit and glue carcass. Test for square. Set out and plane back. Design top and bottom. | Resource: Google Classroom - Week 5
+Clock Week 6: Theory: Discussion: Design of ‘secret’ draw. Workbook/Folio: Research Types of hand planes and their uses Practical: Demonstrate / Observe: Plane Carcass flat and square. Position and glue clock face. | Resource: Google Classroom - Week 6
+Tool Carry-all Week 11: Theory: Discussion: The importance of dry assembly and checking for square. Workbook/Folio: Nails and Glues worksheets Practical: Demonstrate / Observe: Dry assembly glue and clamping process checking for square | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G27" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7
+Tool Carry-all: Project Evidence row 8</x:v>
+      </x:c>
+      <x:c r="H27" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I27" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 5
+stage_5_timber_2021-06-16.docx, table 18, row 5
+stage_5_timber_2021-06-16.docx, table 18, row 6
+stage_5_timber_2021-06-16.docx, table 30, row 11</x:v>
+      </x:c>
+      <x:c r="J27" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="129.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A28" s="466" t="str">
+        <x:v>CP013</x:v>
+      </x:c>
+      <x:c r="B28" s="451" t="str">
+        <x:v>apply the principles of risk management, for example:</x:v>
+      </x:c>
+      <x:c r="C28" s="451" t="str">
+        <x:v>identify a particular risk and implement risk-reduction procedures
+hierarchies of control</x:v>
+      </x:c>
+      <x:c r="D28" s="451" t="str">
+        <x:v>Breadboard Week 6
+Clock Week 3
+Clock Week 11
+Tool Carry-all Week 12</x:v>
+      </x:c>
+      <x:c r="E28" s="451" t="str">
+        <x:v>Breadboard Week 6: Demonstration on how to use the router. Onguard test. Router edges.
+Clock Week 3: Timber Properties and workshop drawings.
+Clock Week 11: Complete SWMS for clock.
+Tool Carry-all Week 12: SWMS for tool carry all.</x:v>
+      </x:c>
+      <x:c r="F28" s="451" t="str">
+        <x:v>Breadboard Week 6: Theory: Onguard topics and quiz's Router - Corded/Electric (WOODTech) Discussion Types of router bits and design options Workbook/Folio Router profile sheet Practical: Demonstrate / Observe: The use of a router to cut a profile | Resource: Google Classroom - Week 6
+Clock Week 3: Theory: Discussion: Timber properties and Characteristics Workbook/Folio: Isometric Drawing Orthogonal drawing. WMS. Practical: Demonstrate / Observe: Reinforce proper hand tool use. Continue on with rebates. Reinforce the significance of accuracy to plan. Start front and back pieces. | Resource: Google Classroom - Week 3
+Clock Week 11: Theory: Workbook/Folio: Sequencing exercise Safe Work Method Statement | Resource: No resource location stated in source row.
+Tool Carry-all Week 12: Theory: Workbook/Folio: Sequencing exercise Safe Work Method Statement Practical: Demonstrate / Observe: Dry assembly glue and clamping process checking for square | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G28" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7
+Tool Carry-all: Project Evidence row 8</x:v>
+      </x:c>
+      <x:c r="H28" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I28" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 6
+stage_5_timber_2021-06-16.docx, table 18, row 3
+stage_5_timber_2021-06-16.docx, table 18, row 11
+stage_5_timber_2021-06-16.docx, table 30, row 12</x:v>
+      </x:c>
+      <x:c r="J28" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="86.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A29" s="466" t="str">
+        <x:v>CP014</x:v>
+      </x:c>
+      <x:c r="B29" s="451" t="str">
+        <x:v>identify reasons for preparing surfaces and applying timber finishes</x:v>
+      </x:c>
+      <x:c r="C29" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D29" s="451" t="str">
+        <x:v>Breadboard Week 7
+Clock Week 12
+Tool Carry-all Week 13</x:v>
+      </x:c>
+      <x:c r="E29" s="451" t="str">
+        <x:v>Breadboard Week 7: Patterns must be finished by this week. Sand and prep for finishing.
+Clock Week 12: Sand and prep clock for finishing.
+Tool Carry-all Week 13: Sand and Prep project for finishing. Timber finishing and prep research.</x:v>
+      </x:c>
+      <x:c r="F29" s="451" t="str">
+        <x:v>Breadboard Week 7: Theory: Discussion - Types of abrasive material used for surface preparation Workbook/Folio Research Timber Seasoning Practical: Demonstrate / Observe: Sanding Techniques | Resource: Google Classroom - Week 7
+Clock Week 12: Practical: Demonstrate / Observe: Sanding and finishing Techniques | Resource: No resource location stated in source row.
+Tool Carry-all Week 13: Theory: Discussion: Sanding and prep' techniques Different types of finishes Workbook/Folio: Finishing methods worksheet Practical: Demonstrate / Observe: Preparing surfaces for finishing Apply finishes | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G29" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7
+Tool Carry-all: Project Evidence row 8</x:v>
+      </x:c>
+      <x:c r="H29" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I29" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 7
+stage_5_timber_2021-06-16.docx, table 18, row 12
+stage_5_timber_2021-06-16.docx, table 30, row 13</x:v>
+      </x:c>
+      <x:c r="J29" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A30" s="466" t="str">
+        <x:v>CP015</x:v>
+      </x:c>
+      <x:c r="B30" s="451" t="str">
+        <x:v>investigate timber conversion and seasoning processes, for example:</x:v>
+      </x:c>
+      <x:c r="C30" s="451" t="str">
+        <x:v>compare the advantages and disadvantages of air and kiln seasoning
+outline and apply the appropriate method of stacking cut timber for seasoning and storage</x:v>
+      </x:c>
+      <x:c r="D30" s="451" t="str">
+        <x:v>Breadboard Week 7
+Clock Week 6</x:v>
+      </x:c>
+      <x:c r="E30" s="451" t="str">
+        <x:v>Breadboard Week 7: Patterns must be finished by this week. Sand and prep for finishing.
+Clock Week 6: Timber seasoning documentary and exercise. Assemble Carcass.</x:v>
+      </x:c>
+      <x:c r="F30" s="451" t="str">
+        <x:v>Breadboard Week 7: Theory: Discussion - Types of abrasive material used for surface preparation Workbook/Folio Research Timber Seasoning Practical: Demonstrate / Observe: Sanding Techniques | Resource: Google Classroom - Week 7
+Clock Week 6: Theory: Discussion: Design of ‘secret’ draw. Workbook/Folio: Research Types of hand planes and their uses Practical: Demonstrate / Observe: Plane Carcass flat and square. Position and glue clock face. | Resource: Google Classroom - Week 6</x:v>
+      </x:c>
+      <x:c r="G30" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7</x:v>
+      </x:c>
+      <x:c r="H30" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I30" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 7
+stage_5_timber_2021-06-16.docx, table 18, row 6</x:v>
+      </x:c>
+      <x:c r="J30" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="108" hidden="0" customHeight="1">
+      <x:c r="A31" s="466" t="str">
+        <x:v>CP016</x:v>
+      </x:c>
+      <x:c r="B31" s="451" t="str">
+        <x:v>describe a range of timber finishes and their applications, for example:</x:v>
+      </x:c>
+      <x:c r="C31" s="451" t="str">
+        <x:v>clear finishes
+oils</x:v>
+      </x:c>
+      <x:c r="D31" s="451" t="str">
+        <x:v>Breadboard Week 8
+Clock Week 13
+Tool Carry-all Week 13</x:v>
+      </x:c>
+      <x:c r="E31" s="451" t="str">
+        <x:v>Breadboard Week 8: Oil timber. Once complete students complete SWMS.
+Clock Week 13: Oil Project - Self-evaluation of project.
+Tool Carry-all Week 13: Sand and Prep project for finishing. Timber finishing and prep research.</x:v>
+      </x:c>
+      <x:c r="F31" s="451" t="str">
+        <x:v>Breadboard Week 8: Theory: Onguard topics and quiz's Finishing Materials (BasicWorkshop) Discussion: Different types of methods used for finishing timber. Workbook/Folio Research - Environmental Sustainability Practical: Demonstrate / Observe: Finishing Technique - Using Danish Oil | Resource: Google Classroom - Week 8
+Clock Week 13: Theory: Discussion: Different types of Finishing Techniques Workbook/Folio: Self Evaluation Practical: Demonstrate / Observe: Oiling Techniques | Resource: No resource location stated in source row.
+Tool Carry-all Week 13: Theory: Discussion: Sanding and prep' techniques Different types of finishes Workbook/Folio: Finishing methods worksheet Practical: Demonstrate / Observe: Preparing surfaces for finishing Apply finishes | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G31" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7
+Tool Carry-all: Project Evidence row 8</x:v>
+      </x:c>
+      <x:c r="H31" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I31" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 8
+stage_5_timber_2021-06-16.docx, table 18, row 13
+stage_5_timber_2021-06-16.docx, table 30, row 13</x:v>
+      </x:c>
+      <x:c r="J31" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="108" hidden="0" customHeight="1">
+      <x:c r="A32" s="466" t="str">
+        <x:v>CP017</x:v>
+      </x:c>
+      <x:c r="B32" s="451" t="str">
+        <x:v>apply a range of processes and techniques for finishing timber, for example:</x:v>
+      </x:c>
+      <x:c r="C32" s="451" t="str">
+        <x:v>applying an oil finish</x:v>
+      </x:c>
+      <x:c r="D32" s="451" t="str">
+        <x:v>Breadboard Week 8
+Clock Week 13
+Tool Carry-all Week 13</x:v>
+      </x:c>
+      <x:c r="E32" s="451" t="str">
+        <x:v>Breadboard Week 8: Oil timber. Once complete students complete SWMS.
+Clock Week 13: Oil Project - Self-evaluation of project.
+Tool Carry-all Week 13: Sand and Prep project for finishing. Timber finishing and prep research.</x:v>
+      </x:c>
+      <x:c r="F32" s="451" t="str">
+        <x:v>Breadboard Week 8: Theory: Onguard topics and quiz's Finishing Materials (BasicWorkshop) Discussion: Different types of methods used for finishing timber. Workbook/Folio Research - Environmental Sustainability Practical: Demonstrate / Observe: Finishing Technique - Using Danish Oil | Resource: Google Classroom - Week 8
+Clock Week 13: Theory: Discussion: Different types of Finishing Techniques Workbook/Folio: Self Evaluation Practical: Demonstrate / Observe: Oiling Techniques | Resource: No resource location stated in source row.
+Tool Carry-all Week 13: Theory: Discussion: Sanding and prep' techniques Different types of finishes Workbook/Folio: Finishing methods worksheet Practical: Demonstrate / Observe: Preparing surfaces for finishing Apply finishes | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G32" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7
+Tool Carry-all: Project Evidence row 8</x:v>
+      </x:c>
+      <x:c r="H32" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I32" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 8
+stage_5_timber_2021-06-16.docx, table 18, row 13
+stage_5_timber_2021-06-16.docx, table 30, row 13</x:v>
+      </x:c>
+      <x:c r="J32" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A33" s="466" t="str">
+        <x:v>CP018</x:v>
+      </x:c>
+      <x:c r="B33" s="451" t="str">
+        <x:v>identify renewable and non-renewable resources in the timber industry</x:v>
+      </x:c>
+      <x:c r="C33" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D33" s="451" t="str">
+        <x:v>Breadboard Week 8
+Clock Week 7</x:v>
+      </x:c>
+      <x:c r="E33" s="451" t="str">
+        <x:v>Breadboard Week 8: Oil timber. Once complete students complete SWMS.
+Clock Week 7: Mark and cut rebates for drawer. Mark, cut and plane sides.</x:v>
+      </x:c>
+      <x:c r="F33" s="451" t="str">
+        <x:v>Breadboard Week 8: Theory: Onguard topics and quiz's Finishing Materials (BasicWorkshop) Discussion: Different types of methods used for finishing timber. Workbook/Folio Research - Environmental Sustainability Practical: Demonstrate / Observe: Finishing Technique - Using Danish Oil | Resource: Google Classroom - Week 8
+Clock Week 7: Theory: Discussion: Possible environmental impact through production of such products. Practical: Demonstrate / Observe: Cut out ‘secret drawer’. Route 6mm chamfer around inside of dial | Resource: Google Classroom - Week 7</x:v>
+      </x:c>
+      <x:c r="G33" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7</x:v>
+      </x:c>
+      <x:c r="H33" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I33" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 8
+stage_5_timber_2021-06-16.docx, table 18, row 7</x:v>
+      </x:c>
+      <x:c r="J33" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A34" s="466" t="str">
+        <x:v>CP019</x:v>
+      </x:c>
+      <x:c r="B34" s="451" t="str">
+        <x:v>recognise the importance of conservation of materials and recycling in the timber industry, for example:</x:v>
+      </x:c>
+      <x:c r="C34" s="451" t="str">
+        <x:v>the use of plantation timbers in the production of manufactured boards
+recycling of timbers, eg beams from old warehouses</x:v>
+      </x:c>
+      <x:c r="D34" s="451" t="str">
+        <x:v>Breadboard Week 8
+Clock Week 7</x:v>
+      </x:c>
+      <x:c r="E34" s="451" t="str">
+        <x:v>Breadboard Week 8: Oil timber. Once complete students complete SWMS.
+Clock Week 7: Mark and cut rebates for drawer. Mark, cut and plane sides.</x:v>
+      </x:c>
+      <x:c r="F34" s="451" t="str">
+        <x:v>Breadboard Week 8: Theory: Onguard topics and quiz's Finishing Materials (BasicWorkshop) Discussion: Different types of methods used for finishing timber. Workbook/Folio Research - Environmental Sustainability Practical: Demonstrate / Observe: Finishing Technique - Using Danish Oil | Resource: Google Classroom - Week 8
+Clock Week 7: Theory: Discussion: Possible environmental impact through production of such products. Practical: Demonstrate / Observe: Cut out ‘secret drawer’. Route 6mm chamfer around inside of dial | Resource: Google Classroom - Week 7</x:v>
+      </x:c>
+      <x:c r="G34" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7</x:v>
+      </x:c>
+      <x:c r="H34" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I34" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 8
+stage_5_timber_2021-06-16.docx, table 18, row 7</x:v>
+      </x:c>
+      <x:c r="J34" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A35" s="466" t="str">
+        <x:v>CP020</x:v>
+      </x:c>
+      <x:c r="B35" s="451" t="str">
+        <x:v>select and use specialist terminology in context, for example:</x:v>
+      </x:c>
+      <x:c r="C35" s="451" t="str">
+        <x:v>procedure/record of production
+glossary
+procedure/storyboard
+record of production</x:v>
+      </x:c>
+      <x:c r="D35" s="451" t="str">
+        <x:v>Breadboard Week 9
+Mirror Week 18
+Bedside Table Week 18</x:v>
+      </x:c>
+      <x:c r="E35" s="451" t="str">
+        <x:v>Breadboard Week 9: Self-evaluation of completed work.
+Mirror Week 18: Class Test
+Bedside Table Week 18: Class Test</x:v>
+      </x:c>
+      <x:c r="F35" s="451" t="str">
+        <x:v>Breadboard Week 9: Theory: Discussion The importance of self-evaluation Workbook/Folio Create a Safe Work Method Statement Self Evaluation of completed project Research - Terms | Resource: Google Classroom - Week 9
+Mirror Week 18: Theory: Workbook/Folio: Class Test Practical: Demonstrate / Observe: Ongoing safe workshop procedures | Resource: No resource location stated in source row.
+Bedside Table Week 18: Theory: Workbook/Folio: Class Test Practical: Demonstrate / Observe: Ongoing safe workshop procedures | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G35" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H35" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I35" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 9
+stage_5_timber_2021-06-16.docx, table 36, row 18
+stage_5_timber_2021-06-16.docx, table 42, row 18</x:v>
+      </x:c>
+      <x:c r="J35" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="194.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A36" s="466" t="str">
+        <x:v>CP021</x:v>
+      </x:c>
+      <x:c r="B36" s="451" t="str">
+        <x:v>apply project management techniques and follow a planned sequence through to project completion</x:v>
+      </x:c>
+      <x:c r="C36" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D36" s="451" t="str">
+        <x:v>Breadboard Week 9
+Clock Week 3
+Clock Week 11
+Mirror Week 3
+Bedside Table Week 3
+Bedside Table Week 12</x:v>
+      </x:c>
+      <x:c r="E36" s="451" t="str">
+        <x:v>Breadboard Week 9: Self-evaluation of completed work.
+Clock Week 3: Timber Properties and workshop drawings.
+Clock Week 11: Complete SWMS for clock.
+Mirror Week 3: Dress and prepare timber to size. Function of the Plane. Project Management
+Bedside Table Week 3: Dress and prepare timber to size. DAR - FEWTEL
+Bedside Table Week 12: Assemble / Gluing. Sequencing and Time planning</x:v>
+      </x:c>
+      <x:c r="F36" s="451" t="str">
+        <x:v>Breadboard Week 9: Theory: Discussion The importance of self-evaluation Workbook/Folio Create a Safe Work Method Statement Self Evaluation of completed project Research - Terms | Resource: Google Classroom - Week 9
+Clock Week 3: Theory: Discussion: Timber properties and Characteristics Workbook/Folio: Isometric Drawing Orthogonal drawing. WMS. Practical: Demonstrate / Observe: Reinforce proper hand tool use. Continue on with rebates. Reinforce the significance of accuracy to plan. Start front and back pieces. | Resource: Google Classroom - Week 3
+Clock Week 11: Theory: Workbook/Folio: Sequencing exercise Safe Work Method Statement | Resource: No resource location stated in source row.
+Mirror Week 3: Theory: Discussion: Refresh FEWTEL. DAR Workbook/Folio: Sketch out design ideas (Cont') Modification of existing plans Practical: Demonstrate / Observe: The use of the handplane / Thicknesser Checking for square face/side | Resource: No resource location stated in source row.
+Bedside Table Week 3: Theory: Discussion: Refresh FEWTEL. DAR Workbook/Folio: Sketch out design ideas (Cont') Modification of existing plans Practical: Demonstrate / Observe: Refresh The use of the handplane / Thicknesser | Resource: No resource location stated in source row.
+Bedside Table Week 12: Discussion: Refresh Gluing and clamping - assembly and clamping times Workbook/Folio: Sequencing and time-planning exercise - Gantt Chart Practical: Demonstrate / Observe: Glueing and clamping processes | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G36" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7
+Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H36" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I36" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 9
+stage_5_timber_2021-06-16.docx, table 18, row 3
+stage_5_timber_2021-06-16.docx, table 18, row 11
+stage_5_timber_2021-06-16.docx, table 36, row 3
+stage_5_timber_2021-06-16.docx, table 42, row 3
+stage_5_timber_2021-06-16.docx, table 42, row 12</x:v>
+      </x:c>
+      <x:c r="J36" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="226.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A37" s="466" t="str">
+        <x:v>CP022</x:v>
+      </x:c>
+      <x:c r="B37" s="451" t="str">
+        <x:v>evaluate the impact of design and work practices/processes on the quality of finished projects</x:v>
+      </x:c>
+      <x:c r="C37" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D37" s="451" t="str">
+        <x:v>Breadboard Week 9
+Clock Week 9
+Clock Week 14
+Clock Week 15
+Tool Carry-all Week 14
+Mirror Week 17
+Bedside Table Week 17</x:v>
+      </x:c>
+      <x:c r="E37" s="451" t="str">
+        <x:v>Breadboard Week 9: Self-evaluation of completed work.
+Clock Week 9: Assemble drawer - Properties of timber exercise.
+Clock Week 14: Class Test and Feedback
+Clock Week 15: Hand in project and workbook for marking.
+Tool Carry-all Week 14: Finish job and complete self evaluation.
+Mirror Week 17: Port Folio Presentation and Evaluation.
+Bedside Table Week 17: Port Folio Presentation and Assessment</x:v>
+      </x:c>
+      <x:c r="F37" s="451" t="str">
+        <x:v>Breadboard Week 9: Theory: Discussion The importance of self-evaluation Workbook/Folio Create a Safe Work Method Statement Self Evaluation of completed project Research - Terms | Resource: Google Classroom - Week 9
+Clock Week 9: Theory: Discussion: Possible ways to improve project. Practical: Demonstrate / Observe: Plane and fit drawer for Carcass. | Resource: Google Classroom - Week 9
+Clock Week 14: Theory: Discussion: What has been the success/failures during this unit Workbook/Folio: Class Test Student Feedback Sheet Hand in Project and Folio for marking Practical: Demonstrate / Observe: Oiling Techniques | Resource: No resource location stated in source row.
+Clock Week 15: Theory: Discussion: (Cont') What has been the success/failures during this unit Workbook/Folio: (Cont') Class Test Student Feedback Sheet Hand in Project and Folio for marking Practical: Demonstrate / Observe: (Cont') Oiling Techniques | Resource: No resource location stated in source row.
+Tool Carry-all Week 14: Theory: Discussion: Sanding and prep' techniques Different types of finishes Workbook/Folio: Finishing methods worksheet Practical: Demonstrate / Observe: Preparing surfaces for finishing Apply finishes | Resource: No resource location stated in source row.
+Mirror Week 17: Theory: Discussion: Presentation Techniques Workbook/Folio: Evaluation of completed projects Practical: Demonstrate / Observe: Ongoing safe workshop procedures | Resource: No resource location stated in source row.
+Bedside Table Week 17: Theory: Discussion: Presentation Techniques Workbook/Folio: Evaluation of completed projects Practical: Demonstrate / Observe: Ongoing safe workshop procedures | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G37" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7
+Tool Carry-all: Project Evidence row 8
+Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H37" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I37" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 9
+stage_5_timber_2021-06-16.docx, table 18, row 9
+stage_5_timber_2021-06-16.docx, table 18, row 14
+stage_5_timber_2021-06-16.docx, table 18, row 15
+stage_5_timber_2021-06-16.docx, table 30, row 14
+stage_5_timber_2021-06-16.docx, table 36, row 17
+stage_5_timber_2021-06-16.docx, table 42, row 17</x:v>
+      </x:c>
+      <x:c r="J37" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="259.20001220703125" hidden="0" customHeight="1">
+      <x:c r="A38" s="466" t="str">
+        <x:v>CP023</x:v>
+      </x:c>
+      <x:c r="B38" s="451" t="str">
+        <x:v>prepare design and production folios to describe the management and processes undertaken in the production of practical projects</x:v>
+      </x:c>
+      <x:c r="C38" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D38" s="451" t="str">
+        <x:v>Breadboard Week 10
+Clock Week 14
+Clock Week 15
+Mirror Week 2
+Mirror Week 17
+Bedside Table Week 2
+Bedside Table Week 17</x:v>
+      </x:c>
+      <x:c r="E38" s="451" t="str">
+        <x:v>Breadboard Week 10: Present Project and Booklet for marking. Workshop maintenance.
+Clock Week 14: Class Test and Feedback
+Clock Week 15: Hand in project and workbook for marking.
+Mirror Week 2: Design and sketches. Measure and Mark-out. Safe use of Tools and Equipment.
+Mirror Week 17: Port Folio Presentation and Evaluation.
+Bedside Table Week 2: Design and sketches. Measure and Mark-out.
+Bedside Table Week 17: Port Folio Presentation and Assessment</x:v>
+      </x:c>
+      <x:c r="F38" s="451" t="str">
+        <x:v>Breadboard Week 10: Theory: Workbook/Folio Research timber types and features Practical: Demonstrate / Observe: Workshop maintenance and clean up | Resource: Google Classroom - Week 10
+Clock Week 14: Theory: Discussion: What has been the success/failures during this unit Workbook/Folio: Class Test Student Feedback Sheet Hand in Project and Folio for marking Practical: Demonstrate / Observe: Oiling Techniques | Resource: No resource location stated in source row.
+Clock Week 15: Theory: Discussion: (Cont') What has been the success/failures during this unit Workbook/Folio: (Cont') Class Test Student Feedback Sheet Hand in Project and Folio for marking Practical: Demonstrate / Observe: (Cont') Oiling Techniques | Resource: No resource location stated in source row.
+Mirror Week 2: Theory: Discussion: Look at past projects and discuss design ideas as a group. Workbook/Folio: PMI's on existing designs SOP's Sketch out design ideas Practical: Demonstrate / Observe: Cut timber to lengths for mirror frame | Resource: No resource location stated in source row.
+Mirror Week 17: Theory: Discussion: Presentation Techniques Workbook/Folio: Evaluation of completed projects Practical: Demonstrate / Observe: Ongoing safe workshop procedures | Resource: No resource location stated in source row.
+Bedside Table Week 2: Theory: Discussion: Look at past projects and discuss design ideas as a group. Workbook/Folio: PMI's on existing designs SOP's Mortise Machine Sketch out design ideas Practical: Demonstrate / Observe: Cut timber to lengths for bedside table | Resource: No resource location stated in source row.
+Bedside Table Week 17: Theory: Discussion: Presentation Techniques Workbook/Folio: Evaluation of completed projects Practical: Demonstrate / Observe: Ongoing safe workshop procedures | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G38" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7
+Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H38" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I38" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 10
+stage_5_timber_2021-06-16.docx, table 18, row 14
+stage_5_timber_2021-06-16.docx, table 18, row 15
+stage_5_timber_2021-06-16.docx, table 36, row 2
+stage_5_timber_2021-06-16.docx, table 36, row 17
+stage_5_timber_2021-06-16.docx, table 42, row 2
+stage_5_timber_2021-06-16.docx, table 42, row 17</x:v>
+      </x:c>
+      <x:c r="J38" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A39" s="466" t="str">
+        <x:v>CP024</x:v>
+      </x:c>
+      <x:c r="B39" s="451" t="str">
+        <x:v>investigate the structure of trees and how they grow</x:v>
+      </x:c>
+      <x:c r="C39" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D39" s="451" t="str">
+        <x:v>Breadboard Week 10
+Clock Week 3</x:v>
+      </x:c>
+      <x:c r="E39" s="451" t="str">
+        <x:v>Breadboard Week 10: Present Project and Booklet for marking. Workshop maintenance.
+Clock Week 3: Timber Properties and workshop drawings.</x:v>
+      </x:c>
+      <x:c r="F39" s="451" t="str">
+        <x:v>Breadboard Week 10: Theory: Workbook/Folio Research timber types and features Practical: Demonstrate / Observe: Workshop maintenance and clean up | Resource: Google Classroom - Week 10
+Clock Week 3: Theory: Discussion: Timber properties and Characteristics Workbook/Folio: Isometric Drawing Orthogonal drawing. WMS. Practical: Demonstrate / Observe: Reinforce proper hand tool use. Continue on with rebates. Reinforce the significance of accuracy to plan. Start front and back pieces. | Resource: Google Classroom - Week 3</x:v>
+      </x:c>
+      <x:c r="G39" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7</x:v>
+      </x:c>
+      <x:c r="H39" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I39" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 10
+stage_5_timber_2021-06-16.docx, table 18, row 3</x:v>
+      </x:c>
+      <x:c r="J39" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A40" s="466" t="str">
+        <x:v>CP025</x:v>
+      </x:c>
+      <x:c r="B40" s="451" t="str">
+        <x:v>describe the differences between hardwoods and softwoods and justify their selection in a range of projects</x:v>
+      </x:c>
+      <x:c r="C40" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D40" s="451" t="str">
+        <x:v>Breadboard Week 10
+Clock Week 2</x:v>
+      </x:c>
+      <x:c r="E40" s="451" t="str">
+        <x:v>Breadboard Week 10: Present Project and Booklet for marking. Workshop maintenance.
+Clock Week 2: Mark, cut and dress sides. Drill front with oversize forstner bit.</x:v>
+      </x:c>
+      <x:c r="F40" s="451" t="str">
+        <x:v>Breadboard Week 10: Theory: Workbook/Folio Research timber types and features Practical: Demonstrate / Observe: Workshop maintenance and clean up | Resource: Google Classroom - Week 10
+Clock Week 2: Theory: Discussion: Discuss the working characteristics of Softwoods in contrast to Hardwoods. Workbook/Folio: Joinery Research Hardware Research Cutting List (Paper Version) Practical: Demonstrate / Observe: Cut Rebates (Sides) Grain direction &amp; strength. Chiseling | Resource: Google Classroom - Week 2</x:v>
+      </x:c>
+      <x:c r="G40" s="451" t="str">
+        <x:v>Breadboard: Project Evidence row 5
+Clock: Project Evidence row 7</x:v>
+      </x:c>
+      <x:c r="H40" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I40" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 12, row 10
+stage_5_timber_2021-06-16.docx, table 18, row 2</x:v>
+      </x:c>
+      <x:c r="J40" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="140.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A41" s="466" t="str">
+        <x:v>CP026</x:v>
+      </x:c>
+      <x:c r="B41" s="451" t="str">
+        <x:v>accurately cut and prepare materials to size, for example:</x:v>
+      </x:c>
+      <x:c r="C41" s="451" t="str">
+        <x:v>using a tenon saw to cut on waste side of line
+cutting curves in timber using a coping saw</x:v>
+      </x:c>
+      <x:c r="D41" s="451" t="str">
+        <x:v>Clock Week 1
+Tool Carry-all Week 1
+Tool Carry-all Week 3
+Tool Carry-all Week 9</x:v>
+      </x:c>
+      <x:c r="E41" s="451" t="str">
+        <x:v>Clock Week 1: Mark, cut and dress front and back.
+Tool Carry-all Week 1: Demonstration of how to cut dovetail joint. Students to cut a practice from scrap.
+Tool Carry-all Week 3: Mark and cut sides of carry-all. Start cutting box-pin or dovetail.
+Tool Carry-all Week 9: Mark, out cut and shape handle.</x:v>
+      </x:c>
+      <x:c r="F41" s="451" t="str">
+        <x:v>Clock Week 1: Theory: Onguard topics and quiz's Reinforce the safe use of machines. Refresh the importance of PPE Discussion: Workbook/Folio: Design Constraints SOP for Using the large Forstner Bit. Practical: Demonstrate / Observe: Mark out lengths Apply face marks. Cut timber to length | Resource: Google Classroom - Week 1
+Tool Carry-all Week 1: Theory: Discussion: Refresh Onguard topics and quiz's Reinforce the safe use of machines. Refresh the importance of PPE Workbook/Folio: Materials List Practical: Demonstrate / Observe: Mark out and cut Finger joints / Dovetail joints | Resource: Student Workbook
+Tool Carry-all Week 3: Theory: Discussion: Suitable Joints for this project Workbook/Folio: Qualities of Radiata Pine Practical: Demonstrate / Observe: Mark out lengths Apply face marks. Cut timber to length | Resource: No resource location stated in source row.
+Tool Carry-all Week 9: Theory: Discussion: The use of templates Workbook/Folio: Handle Designs Practical: Demonstrate / Observe: Mark, cut and shape handle | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G41" s="451" t="str">
+        <x:v>Clock: Project Evidence row 7
+Tool Carry-all: Project Evidence row 8</x:v>
+      </x:c>
+      <x:c r="H41" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I41" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 18, row 1
+stage_5_timber_2021-06-16.docx, table 30, row 1
+stage_5_timber_2021-06-16.docx, table 30, row 3
+stage_5_timber_2021-06-16.docx, table 30, row 9</x:v>
+      </x:c>
+      <x:c r="J41" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A42" s="466" t="str">
+        <x:v>CP027</x:v>
+      </x:c>
+      <x:c r="B42" s="451" t="str">
+        <x:v>read and interpret plans and/or materials lists to prepare materials for the completion of projects, for example:</x:v>
+      </x:c>
+      <x:c r="C42" s="451" t="str">
+        <x:v>workshop drawings of joints</x:v>
+      </x:c>
+      <x:c r="D42" s="451" t="str">
+        <x:v>Clock Week 2</x:v>
+      </x:c>
+      <x:c r="E42" s="451" t="str">
+        <x:v>Clock Week 2: Mark, cut and dress sides. Drill front with oversize forstner bit.</x:v>
+      </x:c>
+      <x:c r="F42" s="451" t="str">
+        <x:v>Clock Week 2: Theory: Discussion: Discuss the working characteristics of Softwoods in contrast to Hardwoods. Workbook/Folio: Joinery Research Hardware Research Cutting List (Paper Version) Practical: Demonstrate / Observe: Cut Rebates (Sides) Grain direction &amp; strength. Chiseling | Resource: Google Classroom - Week 2</x:v>
+      </x:c>
+      <x:c r="G42" s="451" t="str">
+        <x:v>Clock: Project Evidence row 7</x:v>
+      </x:c>
+      <x:c r="H42" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I42" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 18, row 2</x:v>
+      </x:c>
+      <x:c r="J42" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A43" s="466" t="str">
+        <x:v>CP028</x:v>
+      </x:c>
+      <x:c r="B43" s="451" t="str">
+        <x:v>investigate the properties and working characteristics of solid timber, for example:</x:v>
+      </x:c>
+      <x:c r="C43" s="451" t="str">
+        <x:v>colour
+defects, eg gum veins in Tasmanian oak
+density
+strength</x:v>
+      </x:c>
+      <x:c r="D43" s="451" t="str">
+        <x:v>Clock Week 3</x:v>
+      </x:c>
+      <x:c r="E43" s="451" t="str">
+        <x:v>Clock Week 3: Timber Properties and workshop drawings.</x:v>
+      </x:c>
+      <x:c r="F43" s="451" t="str">
+        <x:v>Clock Week 3: Theory: Discussion: Timber properties and Characteristics Workbook/Folio: Isometric Drawing Orthogonal drawing. WMS. Practical: Demonstrate / Observe: Reinforce proper hand tool use. Continue on with rebates. Reinforce the significance of accuracy to plan. Start front and back pieces. | Resource: Google Classroom - Week 3</x:v>
+      </x:c>
+      <x:c r="G43" s="451" t="str">
+        <x:v>Clock: Project Evidence row 7</x:v>
+      </x:c>
+      <x:c r="H43" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I43" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 18, row 3</x:v>
+      </x:c>
+      <x:c r="J43" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A44" s="466" t="str">
+        <x:v>CP029</x:v>
+      </x:c>
+      <x:c r="B44" s="451" t="str">
+        <x:v>produce freehand sketches of project components and/or projects</x:v>
+      </x:c>
+      <x:c r="C44" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D44" s="451" t="str">
+        <x:v>Clock Week 3</x:v>
+      </x:c>
+      <x:c r="E44" s="451" t="str">
+        <x:v>Clock Week 3: Timber Properties and workshop drawings.</x:v>
+      </x:c>
+      <x:c r="F44" s="451" t="str">
+        <x:v>Clock Week 3: Theory: Discussion: Timber properties and Characteristics Workbook/Folio: Isometric Drawing Orthogonal drawing. WMS. Practical: Demonstrate / Observe: Reinforce proper hand tool use. Continue on with rebates. Reinforce the significance of accuracy to plan. Start front and back pieces. | Resource: Google Classroom - Week 3</x:v>
+      </x:c>
+      <x:c r="G44" s="451" t="str">
+        <x:v>Clock: Project Evidence row 7</x:v>
+      </x:c>
+      <x:c r="H44" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I44" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 18, row 3</x:v>
+      </x:c>
+      <x:c r="J44" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="259.20001220703125" hidden="0" customHeight="1">
+      <x:c r="A45" s="466" t="str">
+        <x:v>CP030</x:v>
+      </x:c>
+      <x:c r="B45" s="451" t="str">
+        <x:v>develop design and production folios using appropriate ICT, for example:</x:v>
+      </x:c>
+      <x:c r="C45" s="451" t="str">
+        <x:v>CAD
+project management tools, eg timeline, cutting list</x:v>
+      </x:c>
+      <x:c r="D45" s="451" t="str">
+        <x:v>Clock Week 3
+Tool Carry-all Week 7
+Tool Carry-all Week 8
+Mirror Week 17
+Bedside Table Week 9
+Bedside Table Week 10
+Bedside Table Week 17</x:v>
+      </x:c>
+      <x:c r="E45" s="451" t="str">
+        <x:v>Clock Week 3: Timber Properties and workshop drawings.
+Tool Carry-all Week 7: Handle design exercise. Orthogonal drawing exercise.
+Tool Carry-all Week 8: Handle design exercise cont'. Orthogonal drawing exercise cont'.
+Mirror Week 17: Port Folio Presentation and Evaluation.
+Bedside Table Week 9: Adding Design Features. Orthogonal Drawings
+Bedside Table Week 10: Adding Design Features. Orthogonal Drawings
+Bedside Table Week 17: Port Folio Presentation and Assessment</x:v>
+      </x:c>
+      <x:c r="F45" s="451" t="str">
+        <x:v>Clock Week 3: Theory: Discussion: Timber properties and Characteristics Workbook/Folio: Isometric Drawing Orthogonal drawing. WMS. Practical: Demonstrate / Observe: Reinforce proper hand tool use. Continue on with rebates. Reinforce the significance of accuracy to plan. Start front and back pieces. | Resource: Google Classroom - Week 3
+Tool Carry-all Week 7: Theory: Discussion: CAD / CAM used in Industry Workbook/Folio: Handle Designs Practical: Demonstrate / Observe: Laser cut template for handle designs | Resource: No resource location stated in source row.
+Tool Carry-all Week 8: Theory: Discussion: CAD / CAM used in Industry Workbook/Folio: Handle Designs Practical: Demonstrate / Observe: Laser cut template for handle designs | Resource: No resource location stated in source row.
+Mirror Week 17: Theory: Discussion: Presentation Techniques Workbook/Folio: Evaluation of completed projects Practical: Demonstrate / Observe: Ongoing safe workshop procedures | Resource: No resource location stated in source row.
+Bedside Table Week 9: Theory: Discussion: Refresh Discuss factors that affect good design - form and function. Workbook/Folio: Adding design features to CAD orthogonal drawings ie. Inlays, secret drawers, routered mouldings etc. Practical: Demonstrate / Observe: The use of hinges, handles, runners and other suitable hardware | Resource: No resource location stated in source row.
+Bedside Table Week 10: Theory: Discussion: Refresh Discuss factors that affect good design - form and function. Workbook/Folio: Adding design features to CAD orthogonal drawings ie. Inlays, secret drawers, routered mouldings etc. Practical: Demonstrate / Observe: The use of hinges, handles, runners and other suitable hardware | Resource: No resource location stated in source row.
+Bedside Table Week 17: Theory: Discussion: Presentation Techniques Workbook/Folio: Evaluation of completed projects Practical: Demonstrate / Observe: Ongoing safe workshop procedures | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G45" s="451" t="str">
+        <x:v>Clock: Project Evidence row 7
+Tool Carry-all: Project Evidence row 8
+Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H45" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I45" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 18, row 3
+stage_5_timber_2021-06-16.docx, table 30, row 7
+stage_5_timber_2021-06-16.docx, table 30, row 8
+stage_5_timber_2021-06-16.docx, table 36, row 17
+stage_5_timber_2021-06-16.docx, table 42, row 9
+stage_5_timber_2021-06-16.docx, table 42, row 10
+stage_5_timber_2021-06-16.docx, table 42, row 17</x:v>
+      </x:c>
+      <x:c r="J45" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A46" s="466" t="str">
+        <x:v>CP031</x:v>
+      </x:c>
+      <x:c r="B46" s="451" t="str">
+        <x:v>maintain hand and machine tools</x:v>
+      </x:c>
+      <x:c r="C46" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D46" s="451" t="str">
+        <x:v>Clock Week 4
+Clock Week 10</x:v>
+      </x:c>
+      <x:c r="E46" s="451" t="str">
+        <x:v>Clock Week 4: Assemble main body component of clock. Cut rebates inside of clock. Industry Connections
+Clock Week 10: Workshop Maintenance.</x:v>
+      </x:c>
+      <x:c r="F46" s="451" t="str">
+        <x:v>Clock Week 4: Theory: Discussion: Compare to industry methods. Workbook/Folio: Tools / Machines Used / SOP Make a List and compare the tools/machines the students and industry used. Practical: Demonstrate / Observe: Mark and cut out front and back pieces. Set out sub-top and sub-bottom. | Resource: Google Classroom - Week 4
+Clock Week 10: Theory: Discussion: The importance of good workshop maintenance Practical: Demonstrate / Observe: Manual handling Techniques | Resource: Google Classroom - Week 10</x:v>
+      </x:c>
+      <x:c r="G46" s="451" t="str">
+        <x:v>Clock: Project Evidence row 7</x:v>
+      </x:c>
+      <x:c r="H46" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I46" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 18, row 4
+stage_5_timber_2021-06-16.docx, table 18, row 10</x:v>
+      </x:c>
+      <x:c r="J46" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A47" s="466" t="str">
+        <x:v>CP032</x:v>
+      </x:c>
+      <x:c r="B47" s="451" t="str">
+        <x:v>identify, select and use a range of hardware and cabinet fittings in the completion of projects, for example:</x:v>
+      </x:c>
+      <x:c r="C47" s="451" t="str">
+        <x:v>drawer handles</x:v>
+      </x:c>
+      <x:c r="D47" s="451" t="str">
+        <x:v>Clock Week 6</x:v>
+      </x:c>
+      <x:c r="E47" s="451" t="str">
+        <x:v>Clock Week 6: Timber seasoning documentary and exercise. Assemble Carcass.</x:v>
+      </x:c>
+      <x:c r="F47" s="451" t="str">
+        <x:v>Clock Week 6: Theory: Discussion: Design of ‘secret’ draw. Workbook/Folio: Research Types of hand planes and their uses Practical: Demonstrate / Observe: Plane Carcass flat and square. Position and glue clock face. | Resource: Google Classroom - Week 6</x:v>
+      </x:c>
+      <x:c r="G47" s="451" t="str">
+        <x:v>Clock: Project Evidence row 7</x:v>
+      </x:c>
+      <x:c r="H47" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I47" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 18, row 6</x:v>
+      </x:c>
+      <x:c r="J47" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A48" s="466" t="str">
+        <x:v>CP033</x:v>
+      </x:c>
+      <x:c r="B48" s="451" t="str">
+        <x:v>incorporate features into projects, for example:</x:v>
+      </x:c>
+      <x:c r="C48" s="451" t="str">
+        <x:v>drawers</x:v>
+      </x:c>
+      <x:c r="D48" s="451" t="str">
+        <x:v>Clock Week 6
+Tool Carry-all Week 2</x:v>
+      </x:c>
+      <x:c r="E48" s="451" t="str">
+        <x:v>Clock Week 6: Timber seasoning documentary and exercise. Assemble Carcass.
+Tool Carry-all Week 2: Tools and Techniques used by Aboriginal and/or Torres Strait Islanders.</x:v>
+      </x:c>
+      <x:c r="F48" s="451" t="str">
+        <x:v>Clock Week 6: Theory: Discussion: Design of ‘secret’ draw. Workbook/Folio: Research Types of hand planes and their uses Practical: Demonstrate / Observe: Plane Carcass flat and square. Position and glue clock face. | Resource: Google Classroom - Week 6
+Tool Carry-all Week 2: Theory: Discussion: Tools and Techniques used by Aboriginal and/or Torres Strait Islanders. Workbook/Folio: Research types of timbers aboriginal people used for making their tools and equipment. What qualities did these have that made them suitable. | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G48" s="451" t="str">
+        <x:v>Clock: Project Evidence row 7
+Tool Carry-all: Project Evidence row 8</x:v>
+      </x:c>
+      <x:c r="H48" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I48" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 18, row 6
+stage_5_timber_2021-06-16.docx, table 30, row 2</x:v>
+      </x:c>
+      <x:c r="J48" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="205.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A49" s="466" t="str">
+        <x:v>CP034</x:v>
+      </x:c>
+      <x:c r="B49" s="451" t="str">
+        <x:v>investigate historical technologies related to the timber industry</x:v>
+      </x:c>
+      <x:c r="C49" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D49" s="451" t="str">
+        <x:v>Clock Week 6
+Tool Carry-all Week 2
+Tool Carry-all Week 4
+Tool Carry-all Week 5
+Tool Carry-all Week 6</x:v>
+      </x:c>
+      <x:c r="E49" s="451" t="str">
+        <x:v>Clock Week 6: Timber seasoning documentary and exercise. Assemble Carcass.
+Tool Carry-all Week 2: Tools and Techniques used by Aboriginal and/or Torres Strait Islanders.
+Tool Carry-all Week 4: Industry research exercise. Continue with Joint Construction.
+Tool Carry-all Week 5: Industry Research Task. Continue cutting box-pins or dovetails.
+Tool Carry-all Week 6: Industry Research Task. Complete joinery and begin to cut rebate for bottom.</x:v>
+      </x:c>
+      <x:c r="F49" s="451" t="str">
+        <x:v>Clock Week 6: Theory: Discussion: Design of ‘secret’ draw. Workbook/Folio: Research Types of hand planes and their uses Practical: Demonstrate / Observe: Plane Carcass flat and square. Position and glue clock face. | Resource: Google Classroom - Week 6
+Tool Carry-all Week 2: Theory: Discussion: Tools and Techniques used by Aboriginal and/or Torres Strait Islanders. Workbook/Folio: Research types of timbers aboriginal people used for making their tools and equipment. What qualities did these have that made them suitable. | Resource: No resource location stated in source row.
+Tool Carry-all Week 4: Theory: Discussion: Discuss the relationships between classroom techniques and Industry manufacturing processes. Workbook/Folio: Industry Research Task Practical: Demonstrate / Observe: Mark out joints - Box-pin or Dovetail Cut joints Chiseling and fine tuning joint fit | Resource: No resource location stated in source row.
+Tool Carry-all Week 5: Theory: Discussion: Discuss the relationships between classroom techniques and Industry manufacturing processes. Workbook/Folio: Industry Research Task Practical: Demonstrate / Observe: Mark out joints - Box-pin or Dovetail Cut joints Chiseling and fine tuning joint fit | Resource: No resource location stated in source row.
+Tool Carry-all Week 6: Theory: Discussion: Discuss the relationships between classroom techniques and Industry manufacturing processes. Workbook/Folio: Industry Research Task Practical: Demonstrate / Observe: Mark out joints - Box-pin or Dovetail Cut joints Chiseling and fine tuning joint fit Cut rebate for bottom | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G49" s="451" t="str">
+        <x:v>Clock: Project Evidence row 7
+Tool Carry-all: Project Evidence row 8</x:v>
+      </x:c>
+      <x:c r="H49" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I49" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 18, row 6
+stage_5_timber_2021-06-16.docx, table 30, row 2
+stage_5_timber_2021-06-16.docx, table 30, row 4
+stage_5_timber_2021-06-16.docx, table 30, row 5
+stage_5_timber_2021-06-16.docx, table 30, row 6</x:v>
+      </x:c>
+      <x:c r="J49" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A50" s="466" t="str">
+        <x:v>CP035</x:v>
+      </x:c>
+      <x:c r="B50" s="451" t="str">
+        <x:v>investigate issues relating to the sustainability of resources in the timber industry, for example:</x:v>
+      </x:c>
+      <x:c r="C50" s="451" t="str">
+        <x:v>the use of plantation timbers</x:v>
+      </x:c>
+      <x:c r="D50" s="451" t="str">
+        <x:v>Clock Week 7</x:v>
+      </x:c>
+      <x:c r="E50" s="451" t="str">
+        <x:v>Clock Week 7: Mark and cut rebates for drawer. Mark, cut and plane sides.</x:v>
+      </x:c>
+      <x:c r="F50" s="451" t="str">
+        <x:v>Clock Week 7: Theory: Discussion: Possible environmental impact through production of such products. Practical: Demonstrate / Observe: Cut out ‘secret drawer’. Route 6mm chamfer around inside of dial | Resource: Google Classroom - Week 7</x:v>
+      </x:c>
+      <x:c r="G50" s="451" t="str">
+        <x:v>Clock: Project Evidence row 7</x:v>
+      </x:c>
+      <x:c r="H50" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I50" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 18, row 7</x:v>
+      </x:c>
+      <x:c r="J50" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="86.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A51" s="466" t="str">
+        <x:v>CP036</x:v>
+      </x:c>
+      <x:c r="B51" s="451" t="str">
+        <x:v>calculate quantities and costs of materials and components used in the completion of projects, for example:</x:v>
+      </x:c>
+      <x:c r="C51" s="451" t="str">
+        <x:v>use spreadsheets to calculate material quantities and monitor project costs
+determine processes for the efficient use of materials</x:v>
+      </x:c>
+      <x:c r="D51" s="451" t="str">
+        <x:v>Clock Week 8
+Mirror Week 9
+Bedside Table Week 11</x:v>
+      </x:c>
+      <x:c r="E51" s="451" t="str">
+        <x:v>Clock Week 8: Complete cutting and costing list exercise in excel.
+Mirror Week 9: Adding Design Features. Timber Conversion.
+Bedside Table Week 11: Assemble / Gluing. Costing</x:v>
+      </x:c>
+      <x:c r="F51" s="451" t="str">
+        <x:v>Clock Week 8: Theory: Workbook/Folio: Develop cutting list from plans using spreadsheet. Estimate and calculate quantity of materials used. | Resource: Google Classroom - Week 8
+Mirror Week 9: Theory: Discussion: Discuss factors that affect good design - form and function. Workbook/Folio: Spreadsheet costing exercise. Practical: Demonstrate / Observe: Design features. Suitability and techniques | Resource: No resource location stated in source row.
+Bedside Table Week 11: Theory: Discussion: Refresh Gluing and clamping - assembly and clamping times Workbook/Folio: Costing Exercise - Spreadsheet Practical: Demonstrate / Observe: Glueing and clamping processes | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G51" s="451" t="str">
+        <x:v>Clock: Project Evidence row 7
+Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H51" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I51" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 18, row 8
+stage_5_timber_2021-06-16.docx, table 36, row 9
+stage_5_timber_2021-06-16.docx, table 42, row 11</x:v>
+      </x:c>
+      <x:c r="J51" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="21.600000381469727" hidden="0" customHeight="1">
+      <x:c r="A52" s="466" t="str">
+        <x:v>CP037</x:v>
+      </x:c>
+      <x:c r="B52" s="451" t="str">
+        <x:v>contrast the properties and working characteristics of a range of timbers when planning and using timber for specific projects, for example:</x:v>
+      </x:c>
+      <x:c r="C52" s="451" t="str">
+        <x:v>durability
+workability</x:v>
+      </x:c>
+      <x:c r="D52" s="451" t="str">
+        <x:v>Clock Week 9</x:v>
+      </x:c>
+      <x:c r="E52" s="451" t="str">
+        <x:v>Clock Week 9: Assemble drawer - Properties of timber exercise.</x:v>
+      </x:c>
+      <x:c r="F52" s="451" t="str">
+        <x:v>Clock Week 9: Theory: Discussion: Possible ways to improve project. Practical: Demonstrate / Observe: Plane and fit drawer for Carcass. | Resource: Google Classroom - Week 9</x:v>
+      </x:c>
+      <x:c r="G52" s="451" t="str">
+        <x:v>Clock: Project Evidence row 7</x:v>
+      </x:c>
+      <x:c r="H52" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I52" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 18, row 9</x:v>
+      </x:c>
+      <x:c r="J52" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A53" s="477" t="str">
+        <x:v>CP038</x:v>
+      </x:c>
+      <x:c r="B53" s="478" t="str">
+        <x:v>select and prepare timber for the lathe, for example:</x:v>
+      </x:c>
+      <x:c r="C53" s="478" t="str">
+        <x:v>between centres turning</x:v>
+      </x:c>
+      <x:c r="D53" s="478" t="str">
+        <x:v>Pen Week 1
+Pen Week 2</x:v>
+      </x:c>
+      <x:c r="E53" s="478" t="str">
+        <x:v>Pen Week 1: Demonstration of turning. Practice on scrap.
+Pen Week 2: Work on and complete pen.</x:v>
+      </x:c>
+      <x:c r="F53" s="478" t="str">
+        <x:v>Pen Week 1: Theory: Discussion: Types of uses for the Wood Lathe Workbook/Folio: Risk management for using the Lathe Practical: Demonstrate / Observe: Setup and demonstrate turning techniques. Simple scraping and cutting between centres Sanding and finishing on the lathe Turn a timber pen - Start to finish | Resource: No resource location stated in source row.
+Pen Week 2: Demonstrate / Observe: Setup for turning. Simple scraping and cutting between centres - Techniques Sanding and finishing on the lathe Turn a timber pen - Start to finish | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G53" s="478" t="str">
+        <x:v>Pen: SCOPE-01; no Project Evidence row</x:v>
+      </x:c>
+      <x:c r="H53" s="479" t="str">
+        <x:v>Has gaps</x:v>
+      </x:c>
+      <x:c r="I53" s="478" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 24, row 1
+stage_5_timber_2021-06-16.docx, table 24, row 2</x:v>
+      </x:c>
+      <x:c r="J53" s="480" t="str">
+        <x:v>SCOPE-01 — confirm Pen is retained and evidenced, or formally map a replacement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A54" s="477" t="str">
+        <x:v>CP039</x:v>
+      </x:c>
+      <x:c r="B54" s="478" t="str">
+        <x:v>set up and use lathe techniques for basic turning processes, for example:</x:v>
+      </x:c>
+      <x:c r="C54" s="478" t="str">
+        <x:v>between centres turning, eg rolling pin, mallet handle</x:v>
+      </x:c>
+      <x:c r="D54" s="478" t="str">
+        <x:v>Pen Week 1
+Pen Week 2</x:v>
+      </x:c>
+      <x:c r="E54" s="478" t="str">
+        <x:v>Pen Week 1: Demonstration of turning. Practice on scrap.
+Pen Week 2: Work on and complete pen.</x:v>
+      </x:c>
+      <x:c r="F54" s="478" t="str">
+        <x:v>Pen Week 1: Theory: Discussion: Types of uses for the Wood Lathe Workbook/Folio: Risk management for using the Lathe Practical: Demonstrate / Observe: Setup and demonstrate turning techniques. Simple scraping and cutting between centres Sanding and finishing on the lathe Turn a timber pen - Start to finish | Resource: No resource location stated in source row.
+Pen Week 2: Demonstrate / Observe: Setup for turning. Simple scraping and cutting between centres - Techniques Sanding and finishing on the lathe Turn a timber pen - Start to finish | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G54" s="478" t="str">
+        <x:v>Pen: SCOPE-01; no Project Evidence row</x:v>
+      </x:c>
+      <x:c r="H54" s="479" t="str">
+        <x:v>Has gaps</x:v>
+      </x:c>
+      <x:c r="I54" s="478" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 24, row 1
+stage_5_timber_2021-06-16.docx, table 24, row 2</x:v>
+      </x:c>
+      <x:c r="J54" s="480" t="str">
+        <x:v>SCOPE-01 — confirm Pen is retained and evidenced, or formally map a replacement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A55" s="466" t="str">
+        <x:v>CP040</x:v>
+      </x:c>
+      <x:c r="B55" s="451" t="str">
+        <x:v>investigate tools and techniques used by Aboriginal and/or Torres Strait Islander Peoples to manipulate timber and the environment, for example:</x:v>
+      </x:c>
+      <x:c r="C55" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D55" s="451" t="str">
+        <x:v>Tool Carry-all Week 2</x:v>
+      </x:c>
+      <x:c r="E55" s="451" t="str">
+        <x:v>Tool Carry-all Week 2: Tools and Techniques used by Aboriginal and/or Torres Strait Islanders.</x:v>
+      </x:c>
+      <x:c r="F55" s="451" t="str">
+        <x:v>Tool Carry-all Week 2: Theory: Discussion: Tools and Techniques used by Aboriginal and/or Torres Strait Islanders. Workbook/Folio: Research types of timbers aboriginal people used for making their tools and equipment. What qualities did these have that made them suitable. | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G55" s="451" t="str">
+        <x:v>Tool Carry-all: Project Evidence row 8</x:v>
+      </x:c>
+      <x:c r="H55" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I55" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 30, row 2</x:v>
+      </x:c>
+      <x:c r="J55" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="226.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A56" s="466" t="str">
+        <x:v>CP041</x:v>
+      </x:c>
+      <x:c r="B56" s="451" t="str">
+        <x:v>develop and produce practical projects allowing for the characteristics and properties of materials, systems, components, tools and equipment available, for example: (ACTDEK046)</x:v>
+      </x:c>
+      <x:c r="C56" s="451" t="str">
+        <x:v>joining processes
+finishing</x:v>
+      </x:c>
+      <x:c r="D56" s="451" t="str">
+        <x:v>Tool Carry-all Week 4
+Tool Carry-all Week 5
+Tool Carry-all Week 6
+Tool Carry-all Week 13
+Mirror Week 9
+Mirror Week 10</x:v>
+      </x:c>
+      <x:c r="E56" s="451" t="str">
+        <x:v>Tool Carry-all Week 4: Industry research exercise. Continue with Joint Construction.
+Tool Carry-all Week 5: Industry Research Task. Continue cutting box-pins or dovetails.
+Tool Carry-all Week 6: Industry Research Task. Complete joinery and begin to cut rebate for bottom.
+Tool Carry-all Week 13: Sand and Prep project for finishing. Timber finishing and prep research.
+Mirror Week 9: Adding Design Features. Timber Conversion.
+Mirror Week 10: Adding Design Features. Workshop Maintenence.</x:v>
+      </x:c>
+      <x:c r="F56" s="451" t="str">
+        <x:v>Tool Carry-all Week 4: Theory: Discussion: Discuss the relationships between classroom techniques and Industry manufacturing processes. Workbook/Folio: Industry Research Task Practical: Demonstrate / Observe: Mark out joints - Box-pin or Dovetail Cut joints Chiseling and fine tuning joint fit | Resource: No resource location stated in source row.
+Tool Carry-all Week 5: Theory: Discussion: Discuss the relationships between classroom techniques and Industry manufacturing processes. Workbook/Folio: Industry Research Task Practical: Demonstrate / Observe: Mark out joints - Box-pin or Dovetail Cut joints Chiseling and fine tuning joint fit | Resource: No resource location stated in source row.
+Tool Carry-all Week 6: Theory: Discussion: Discuss the relationships between classroom techniques and Industry manufacturing processes. Workbook/Folio: Industry Research Task Practical: Demonstrate / Observe: Mark out joints - Box-pin or Dovetail Cut joints Chiseling and fine tuning joint fit Cut rebate for bottom | Resource: No resource location stated in source row.
+Tool Carry-all Week 13: Theory: Discussion: Sanding and prep' techniques Different types of finishes Workbook/Folio: Finishing methods worksheet Practical: Demonstrate / Observe: Preparing surfaces for finishing Apply finishes | Resource: No resource location stated in source row.
+Mirror Week 9: Theory: Discussion: Discuss factors that affect good design - form and function. Workbook/Folio: Spreadsheet costing exercise. Practical: Demonstrate / Observe: Design features. Suitability and techniques | Resource: No resource location stated in source row.
+Mirror Week 10: Theory: Discussion: The importance of good workshop maintenance Practical: Demonstrate / Observe: Manual handling techniques | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G56" s="451" t="str">
+        <x:v>Tool Carry-all: Project Evidence row 8
+Mirror: Project Evidence row 9</x:v>
+      </x:c>
+      <x:c r="H56" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I56" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 30, row 4
+stage_5_timber_2021-06-16.docx, table 30, row 5
+stage_5_timber_2021-06-16.docx, table 30, row 6
+stage_5_timber_2021-06-16.docx, table 30, row 13
+stage_5_timber_2021-06-16.docx, table 36, row 9
+stage_5_timber_2021-06-16.docx, table 36, row 10</x:v>
+      </x:c>
+      <x:c r="J56" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="162" hidden="0" customHeight="1">
+      <x:c r="A57" s="466" t="str">
+        <x:v>CP042</x:v>
+      </x:c>
+      <x:c r="B57" s="451" t="str">
+        <x:v>investigate advanced manufacturing techniques to assist in the production of projects, for example:</x:v>
+      </x:c>
+      <x:c r="C57" s="451" t="str">
+        <x:v>CNC equipment, eg laser cutters, CNC milling machines
+rapid prototyping</x:v>
+      </x:c>
+      <x:c r="D57" s="451" t="str">
+        <x:v>Tool Carry-all Week 4
+Tool Carry-all Week 5
+Tool Carry-all Week 6
+Mirror Week 10</x:v>
+      </x:c>
+      <x:c r="E57" s="451" t="str">
+        <x:v>Tool Carry-all Week 4: Industry research exercise. Continue with Joint Construction.
+Tool Carry-all Week 5: Industry Research Task. Continue cutting box-pins or dovetails.
+Tool Carry-all Week 6: Industry Research Task. Complete joinery and begin to cut rebate for bottom.
+Mirror Week 10: Adding Design Features. Workshop Maintenence.</x:v>
+      </x:c>
+      <x:c r="F57" s="451" t="str">
+        <x:v>Tool Carry-all Week 4: Theory: Discussion: Discuss the relationships between classroom techniques and Industry manufacturing processes. Workbook/Folio: Industry Research Task Practical: Demonstrate / Observe: Mark out joints - Box-pin or Dovetail Cut joints Chiseling and fine tuning joint fit | Resource: No resource location stated in source row.
+Tool Carry-all Week 5: Theory: Discussion: Discuss the relationships between classroom techniques and Industry manufacturing processes. Workbook/Folio: Industry Research Task Practical: Demonstrate / Observe: Mark out joints - Box-pin or Dovetail Cut joints Chiseling and fine tuning joint fit | Resource: No resource location stated in source row.
+Tool Carry-all Week 6: Theory: Discussion: Discuss the relationships between classroom techniques and Industry manufacturing processes. Workbook/Folio: Industry Research Task Practical: Demonstrate / Observe: Mark out joints - Box-pin or Dovetail Cut joints Chiseling and fine tuning joint fit Cut rebate for bottom | Resource: No resource location stated in source row.
+Mirror Week 10: Theory: Discussion: The importance of good workshop maintenance Practical: Demonstrate / Observe: Manual handling techniques | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G57" s="451" t="str">
+        <x:v>Tool Carry-all: Project Evidence row 8
+Mirror: Project Evidence row 9</x:v>
+      </x:c>
+      <x:c r="H57" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I57" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 30, row 4
+stage_5_timber_2021-06-16.docx, table 30, row 5
+stage_5_timber_2021-06-16.docx, table 30, row 6
+stage_5_timber_2021-06-16.docx, table 36, row 10</x:v>
+      </x:c>
+      <x:c r="J57" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="129.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A58" s="466" t="str">
+        <x:v>CP043</x:v>
+      </x:c>
+      <x:c r="B58" s="451" t="str">
+        <x:v>investigate technologies used in the timber industry to reduce the use of non-renewable resources, for example:</x:v>
+      </x:c>
+      <x:c r="C58" s="451" t="str">
+        <x:v>use of finger jointed timbers</x:v>
+      </x:c>
+      <x:c r="D58" s="451" t="str">
+        <x:v>Tool Carry-all Week 4
+Tool Carry-all Week 5
+Tool Carry-all Week 6</x:v>
+      </x:c>
+      <x:c r="E58" s="451" t="str">
+        <x:v>Tool Carry-all Week 4: Industry research exercise. Continue with Joint Construction.
+Tool Carry-all Week 5: Industry Research Task. Continue cutting box-pins or dovetails.
+Tool Carry-all Week 6: Industry Research Task. Complete joinery and begin to cut rebate for bottom.</x:v>
+      </x:c>
+      <x:c r="F58" s="451" t="str">
+        <x:v>Tool Carry-all Week 4: Theory: Discussion: Discuss the relationships between classroom techniques and Industry manufacturing processes. Workbook/Folio: Industry Research Task Practical: Demonstrate / Observe: Mark out joints - Box-pin or Dovetail Cut joints Chiseling and fine tuning joint fit | Resource: No resource location stated in source row.
+Tool Carry-all Week 5: Theory: Discussion: Discuss the relationships between classroom techniques and Industry manufacturing processes. Workbook/Folio: Industry Research Task Practical: Demonstrate / Observe: Mark out joints - Box-pin or Dovetail Cut joints Chiseling and fine tuning joint fit | Resource: No resource location stated in source row.
+Tool Carry-all Week 6: Theory: Discussion: Discuss the relationships between classroom techniques and Industry manufacturing processes. Workbook/Folio: Industry Research Task Practical: Demonstrate / Observe: Mark out joints - Box-pin or Dovetail Cut joints Chiseling and fine tuning joint fit Cut rebate for bottom | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G58" s="451" t="str">
+        <x:v>Tool Carry-all: Project Evidence row 8</x:v>
+      </x:c>
+      <x:c r="H58" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I58" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 30, row 4
+stage_5_timber_2021-06-16.docx, table 30, row 5
+stage_5_timber_2021-06-16.docx, table 30, row 6</x:v>
+      </x:c>
+      <x:c r="J58" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="129.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A59" s="466" t="str">
+        <x:v>CP044</x:v>
+      </x:c>
+      <x:c r="B59" s="451" t="str">
+        <x:v>compare industrial production processes to those used in the classroom, for example:</x:v>
+      </x:c>
+      <x:c r="C59" s="451" t="str">
+        <x:v>using jigs and templates</x:v>
+      </x:c>
+      <x:c r="D59" s="451" t="str">
+        <x:v>Tool Carry-all Week 4
+Tool Carry-all Week 5
+Tool Carry-all Week 6</x:v>
+      </x:c>
+      <x:c r="E59" s="451" t="str">
+        <x:v>Tool Carry-all Week 4: Industry research exercise. Continue with Joint Construction.
+Tool Carry-all Week 5: Industry Research Task. Continue cutting box-pins or dovetails.
+Tool Carry-all Week 6: Industry Research Task. Complete joinery and begin to cut rebate for bottom.</x:v>
+      </x:c>
+      <x:c r="F59" s="451" t="str">
+        <x:v>Tool Carry-all Week 4: Theory: Discussion: Discuss the relationships between classroom techniques and Industry manufacturing processes. Workbook/Folio: Industry Research Task Practical: Demonstrate / Observe: Mark out joints - Box-pin or Dovetail Cut joints Chiseling and fine tuning joint fit | Resource: No resource location stated in source row.
+Tool Carry-all Week 5: Theory: Discussion: Discuss the relationships between classroom techniques and Industry manufacturing processes. Workbook/Folio: Industry Research Task Practical: Demonstrate / Observe: Mark out joints - Box-pin or Dovetail Cut joints Chiseling and fine tuning joint fit | Resource: No resource location stated in source row.
+Tool Carry-all Week 6: Theory: Discussion: Discuss the relationships between classroom techniques and Industry manufacturing processes. Workbook/Folio: Industry Research Task Practical: Demonstrate / Observe: Mark out joints - Box-pin or Dovetail Cut joints Chiseling and fine tuning joint fit Cut rebate for bottom | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G59" s="451" t="str">
+        <x:v>Tool Carry-all: Project Evidence row 8</x:v>
+      </x:c>
+      <x:c r="H59" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I59" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 30, row 4
+stage_5_timber_2021-06-16.docx, table 30, row 5
+stage_5_timber_2021-06-16.docx, table 30, row 6</x:v>
+      </x:c>
+      <x:c r="J59" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="129.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A60" s="466" t="str">
+        <x:v>CP045</x:v>
+      </x:c>
+      <x:c r="B60" s="451" t="str">
+        <x:v>investigate a range of career paths in the timber and related industries, for example:</x:v>
+      </x:c>
+      <x:c r="C60" s="451" t="str">
+        <x:v>carpenter
+cabinetmaker
+joiner
+wood machinist</x:v>
+      </x:c>
+      <x:c r="D60" s="451" t="str">
+        <x:v>Tool Carry-all Week 4
+Tool Carry-all Week 5
+Tool Carry-all Week 6</x:v>
+      </x:c>
+      <x:c r="E60" s="451" t="str">
+        <x:v>Tool Carry-all Week 4: Industry research exercise. Continue with Joint Construction.
+Tool Carry-all Week 5: Industry Research Task. Continue cutting box-pins or dovetails.
+Tool Carry-all Week 6: Industry Research Task. Complete joinery and begin to cut rebate for bottom.</x:v>
+      </x:c>
+      <x:c r="F60" s="451" t="str">
+        <x:v>Tool Carry-all Week 4: Theory: Discussion: Discuss the relationships between classroom techniques and Industry manufacturing processes. Workbook/Folio: Industry Research Task Practical: Demonstrate / Observe: Mark out joints - Box-pin or Dovetail Cut joints Chiseling and fine tuning joint fit | Resource: No resource location stated in source row.
+Tool Carry-all Week 5: Theory: Discussion: Discuss the relationships between classroom techniques and Industry manufacturing processes. Workbook/Folio: Industry Research Task Practical: Demonstrate / Observe: Mark out joints - Box-pin or Dovetail Cut joints Chiseling and fine tuning joint fit | Resource: No resource location stated in source row.
+Tool Carry-all Week 6: Theory: Discussion: Discuss the relationships between classroom techniques and Industry manufacturing processes. Workbook/Folio: Industry Research Task Practical: Demonstrate / Observe: Mark out joints - Box-pin or Dovetail Cut joints Chiseling and fine tuning joint fit Cut rebate for bottom | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G60" s="451" t="str">
+        <x:v>Tool Carry-all: Project Evidence row 8</x:v>
+      </x:c>
+      <x:c r="H60" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I60" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 30, row 4
+stage_5_timber_2021-06-16.docx, table 30, row 5
+stage_5_timber_2021-06-16.docx, table 30, row 6</x:v>
+      </x:c>
+      <x:c r="J60" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A61" s="466" t="str">
+        <x:v>CP046</x:v>
+      </x:c>
+      <x:c r="B61" s="451" t="str">
+        <x:v>describe elementary first aid procedures, for example:</x:v>
+      </x:c>
+      <x:c r="C61" s="451" t="str">
+        <x:v>outline the procedure to follow after a particular incident, eg burns and cuts</x:v>
+      </x:c>
+      <x:c r="D61" s="451" t="str">
+        <x:v>Tool Carry-all Week 12</x:v>
+      </x:c>
+      <x:c r="E61" s="451" t="str">
+        <x:v>Tool Carry-all Week 12: SWMS for tool carry all.</x:v>
+      </x:c>
+      <x:c r="F61" s="451" t="str">
+        <x:v>Tool Carry-all Week 12: Theory: Workbook/Folio: Sequencing exercise Safe Work Method Statement Practical: Demonstrate / Observe: Dry assembly glue and clamping process checking for square | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G61" s="451" t="str">
+        <x:v>Tool Carry-all: Project Evidence row 8</x:v>
+      </x:c>
+      <x:c r="H61" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I61" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 30, row 12</x:v>
+      </x:c>
+      <x:c r="J61" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="86.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A62" s="466" t="str">
+        <x:v>CP047</x:v>
+      </x:c>
+      <x:c r="B62" s="451" t="str">
+        <x:v>describe the WHS Act and WHS Regulations, and the role of SafeWork NSW in maintaining a safe workplace</x:v>
+      </x:c>
+      <x:c r="C62" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D62" s="451" t="str">
+        <x:v>Mirror Week 1
+Bedside Table Week 1</x:v>
+      </x:c>
+      <x:c r="E62" s="451" t="str">
+        <x:v>Mirror Week 1: Introduction and Workshop Safety. Constraints and limitations.
+Bedside Table Week 1: Introduction. OHS and Risk Management.</x:v>
+      </x:c>
+      <x:c r="F62" s="451" t="str">
+        <x:v>Mirror Week 1: Theory: Discussion: Refresh Onguard Topics and Quiz's Reinforce the safe use of machines. Refresh the importance of PPE Workbook/Folio: Design brief, constraints and considerations General Workshop Safety Sheet Practical: Demonstrate / Observe: Refresh - Measure, mark and cut a rebate and housing joint. | Resource: No resource location stated in source row.
+Bedside Table Week 1: Theory: Discussion: Refresh Onguard Topics and Quiz's Reinforce the safe use of machines. Refresh the importance of PPE Workbook/Folio: General Workshop Safety Sheet - Refresh Purpose of the table and design Input Practical: Demonstrate / Observe: Refresh - Measure, mark and cut a mortice and tenon joint | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G62" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H62" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I62" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 1
+stage_5_timber_2021-06-16.docx, table 42, row 1</x:v>
+      </x:c>
+      <x:c r="J62" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="86.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A63" s="466" t="str">
+        <x:v>CP048</x:v>
+      </x:c>
+      <x:c r="B63" s="451" t="str">
+        <x:v>identify and apply the principles of first aid, for example:</x:v>
+      </x:c>
+      <x:c r="C63" s="451" t="str">
+        <x:v>outline the procedure to follow after a particular incident, eg cuts and lacerations</x:v>
+      </x:c>
+      <x:c r="D63" s="451" t="str">
+        <x:v>Mirror Week 1
+Bedside Table Week 1</x:v>
+      </x:c>
+      <x:c r="E63" s="451" t="str">
+        <x:v>Mirror Week 1: Introduction and Workshop Safety. Constraints and limitations.
+Bedside Table Week 1: Introduction. OHS and Risk Management.</x:v>
+      </x:c>
+      <x:c r="F63" s="451" t="str">
+        <x:v>Mirror Week 1: Theory: Discussion: Refresh Onguard Topics and Quiz's Reinforce the safe use of machines. Refresh the importance of PPE Workbook/Folio: Design brief, constraints and considerations General Workshop Safety Sheet Practical: Demonstrate / Observe: Refresh - Measure, mark and cut a rebate and housing joint. | Resource: No resource location stated in source row.
+Bedside Table Week 1: Theory: Discussion: Refresh Onguard Topics and Quiz's Reinforce the safe use of machines. Refresh the importance of PPE Workbook/Folio: General Workshop Safety Sheet - Refresh Purpose of the table and design Input Practical: Demonstrate / Observe: Refresh - Measure, mark and cut a mortice and tenon joint | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G63" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H63" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I63" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 1
+stage_5_timber_2021-06-16.docx, table 42, row 1</x:v>
+      </x:c>
+      <x:c r="J63" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="172.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A64" s="466" t="str">
+        <x:v>CP049</x:v>
+      </x:c>
+      <x:c r="B64" s="451" t="str">
+        <x:v>identify the functional and aesthetic aspects of design in timber projects, for example:</x:v>
+      </x:c>
+      <x:c r="C64" s="451" t="str">
+        <x:v>suitability of finish for desired appearance
+suitability of species for outdoor applications</x:v>
+      </x:c>
+      <x:c r="D64" s="451" t="str">
+        <x:v>Mirror Week 1
+Mirror Week 2
+Bedside Table Week 1
+Bedside Table Week 2</x:v>
+      </x:c>
+      <x:c r="E64" s="451" t="str">
+        <x:v>Mirror Week 1: Introduction and Workshop Safety. Constraints and limitations.
+Mirror Week 2: Design and sketches. Measure and Mark-out. Safe use of Tools and Equipment.
+Bedside Table Week 1: Introduction. OHS and Risk Management.
+Bedside Table Week 2: Design and sketches. Measure and Mark-out.</x:v>
+      </x:c>
+      <x:c r="F64" s="451" t="str">
+        <x:v>Mirror Week 1: Theory: Discussion: Refresh Onguard Topics and Quiz's Reinforce the safe use of machines. Refresh the importance of PPE Workbook/Folio: Design brief, constraints and considerations General Workshop Safety Sheet Practical: Demonstrate / Observe: Refresh - Measure, mark and cut a rebate and housing joint. | Resource: No resource location stated in source row.
+Mirror Week 2: Theory: Discussion: Look at past projects and discuss design ideas as a group. Workbook/Folio: PMI's on existing designs SOP's Sketch out design ideas Practical: Demonstrate / Observe: Cut timber to lengths for mirror frame | Resource: No resource location stated in source row.
+Bedside Table Week 1: Theory: Discussion: Refresh Onguard Topics and Quiz's Reinforce the safe use of machines. Refresh the importance of PPE Workbook/Folio: General Workshop Safety Sheet - Refresh Purpose of the table and design Input Practical: Demonstrate / Observe: Refresh - Measure, mark and cut a mortice and tenon joint | Resource: No resource location stated in source row.
+Bedside Table Week 2: Theory: Discussion: Look at past projects and discuss design ideas as a group. Workbook/Folio: PMI's on existing designs SOP's Mortise Machine Sketch out design ideas Practical: Demonstrate / Observe: Cut timber to lengths for bedside table | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G64" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H64" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I64" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 1
+stage_5_timber_2021-06-16.docx, table 36, row 2
+stage_5_timber_2021-06-16.docx, table 42, row 1
+stage_5_timber_2021-06-16.docx, table 42, row 2</x:v>
+      </x:c>
+      <x:c r="J64" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="172.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A65" s="466" t="str">
+        <x:v>CP050</x:v>
+      </x:c>
+      <x:c r="B65" s="451" t="str">
+        <x:v>use and/or modify designs when completing projects (ACTDEP049)</x:v>
+      </x:c>
+      <x:c r="C65" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D65" s="451" t="str">
+        <x:v>Mirror Week 1
+Mirror Week 2
+Bedside Table Week 1
+Bedside Table Week 2</x:v>
+      </x:c>
+      <x:c r="E65" s="451" t="str">
+        <x:v>Mirror Week 1: Introduction and Workshop Safety. Constraints and limitations.
+Mirror Week 2: Design and sketches. Measure and Mark-out. Safe use of Tools and Equipment.
+Bedside Table Week 1: Introduction. OHS and Risk Management.
+Bedside Table Week 2: Design and sketches. Measure and Mark-out.</x:v>
+      </x:c>
+      <x:c r="F65" s="451" t="str">
+        <x:v>Mirror Week 1: Theory: Discussion: Refresh Onguard Topics and Quiz's Reinforce the safe use of machines. Refresh the importance of PPE Workbook/Folio: Design brief, constraints and considerations General Workshop Safety Sheet Practical: Demonstrate / Observe: Refresh - Measure, mark and cut a rebate and housing joint. | Resource: No resource location stated in source row.
+Mirror Week 2: Theory: Discussion: Look at past projects and discuss design ideas as a group. Workbook/Folio: PMI's on existing designs SOP's Sketch out design ideas Practical: Demonstrate / Observe: Cut timber to lengths for mirror frame | Resource: No resource location stated in source row.
+Bedside Table Week 1: Theory: Discussion: Refresh Onguard Topics and Quiz's Reinforce the safe use of machines. Refresh the importance of PPE Workbook/Folio: General Workshop Safety Sheet - Refresh Purpose of the table and design Input Practical: Demonstrate / Observe: Refresh - Measure, mark and cut a mortice and tenon joint | Resource: No resource location stated in source row.
+Bedside Table Week 2: Theory: Discussion: Look at past projects and discuss design ideas as a group. Workbook/Folio: PMI's on existing designs SOP's Mortise Machine Sketch out design ideas Practical: Demonstrate / Observe: Cut timber to lengths for bedside table | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G65" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H65" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I65" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 1
+stage_5_timber_2021-06-16.docx, table 36, row 2
+stage_5_timber_2021-06-16.docx, table 42, row 1
+stage_5_timber_2021-06-16.docx, table 42, row 2</x:v>
+      </x:c>
+      <x:c r="J65" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="151.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A66" s="466" t="str">
+        <x:v>CP051</x:v>
+      </x:c>
+      <x:c r="B66" s="451" t="str">
+        <x:v>identify, select and use a range of hand, power and machine tools for preparation, marking out, cutting, shaping and joining timber (ACTDEK046)</x:v>
+      </x:c>
+      <x:c r="C66" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D66" s="451" t="str">
+        <x:v>Mirror Week 2
+Mirror Week 3
+Bedside Table Week 2
+Bedside Table Week 3</x:v>
+      </x:c>
+      <x:c r="E66" s="451" t="str">
+        <x:v>Mirror Week 2: Design and sketches. Measure and Mark-out. Safe use of Tools and Equipment.
+Mirror Week 3: Dress and prepare timber to size. Function of the Plane. Project Management
+Bedside Table Week 2: Design and sketches. Measure and Mark-out.
+Bedside Table Week 3: Dress and prepare timber to size. DAR - FEWTEL</x:v>
+      </x:c>
+      <x:c r="F66" s="451" t="str">
+        <x:v>Mirror Week 2: Theory: Discussion: Look at past projects and discuss design ideas as a group. Workbook/Folio: PMI's on existing designs SOP's Sketch out design ideas Practical: Demonstrate / Observe: Cut timber to lengths for mirror frame | Resource: No resource location stated in source row.
+Mirror Week 3: Theory: Discussion: Refresh FEWTEL. DAR Workbook/Folio: Sketch out design ideas (Cont') Modification of existing plans Practical: Demonstrate / Observe: The use of the handplane / Thicknesser Checking for square face/side | Resource: No resource location stated in source row.
+Bedside Table Week 2: Theory: Discussion: Look at past projects and discuss design ideas as a group. Workbook/Folio: PMI's on existing designs SOP's Mortise Machine Sketch out design ideas Practical: Demonstrate / Observe: Cut timber to lengths for bedside table | Resource: No resource location stated in source row.
+Bedside Table Week 3: Theory: Discussion: Refresh FEWTEL. DAR Workbook/Folio: Sketch out design ideas (Cont') Modification of existing plans Practical: Demonstrate / Observe: Refresh The use of the handplane / Thicknesser | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G66" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H66" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I66" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 2
+stage_5_timber_2021-06-16.docx, table 36, row 3
+stage_5_timber_2021-06-16.docx, table 42, row 2
+stage_5_timber_2021-06-16.docx, table 42, row 3</x:v>
+      </x:c>
+      <x:c r="J66" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="151.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A67" s="466" t="str">
+        <x:v>CP052</x:v>
+      </x:c>
+      <x:c r="B67" s="451" t="str">
+        <x:v>maintain hand tools used to cut and shape timber</x:v>
+      </x:c>
+      <x:c r="C67" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D67" s="451" t="str">
+        <x:v>Mirror Week 2
+Mirror Week 3
+Bedside Table Week 2
+Bedside Table Week 3</x:v>
+      </x:c>
+      <x:c r="E67" s="451" t="str">
+        <x:v>Mirror Week 2: Design and sketches. Measure and Mark-out. Safe use of Tools and Equipment.
+Mirror Week 3: Dress and prepare timber to size. Function of the Plane. Project Management
+Bedside Table Week 2: Design and sketches. Measure and Mark-out.
+Bedside Table Week 3: Dress and prepare timber to size. DAR - FEWTEL</x:v>
+      </x:c>
+      <x:c r="F67" s="451" t="str">
+        <x:v>Mirror Week 2: Theory: Discussion: Look at past projects and discuss design ideas as a group. Workbook/Folio: PMI's on existing designs SOP's Sketch out design ideas Practical: Demonstrate / Observe: Cut timber to lengths for mirror frame | Resource: No resource location stated in source row.
+Mirror Week 3: Theory: Discussion: Refresh FEWTEL. DAR Workbook/Folio: Sketch out design ideas (Cont') Modification of existing plans Practical: Demonstrate / Observe: The use of the handplane / Thicknesser Checking for square face/side | Resource: No resource location stated in source row.
+Bedside Table Week 2: Theory: Discussion: Look at past projects and discuss design ideas as a group. Workbook/Folio: PMI's on existing designs SOP's Mortise Machine Sketch out design ideas Practical: Demonstrate / Observe: Cut timber to lengths for bedside table | Resource: No resource location stated in source row.
+Bedside Table Week 3: Theory: Discussion: Refresh FEWTEL. DAR Workbook/Folio: Sketch out design ideas (Cont') Modification of existing plans Practical: Demonstrate / Observe: Refresh The use of the handplane / Thicknesser | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G67" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H67" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I67" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 2
+stage_5_timber_2021-06-16.docx, table 36, row 3
+stage_5_timber_2021-06-16.docx, table 42, row 2
+stage_5_timber_2021-06-16.docx, table 42, row 3</x:v>
+      </x:c>
+      <x:c r="J67" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A68" s="466" t="str">
+        <x:v>CP053</x:v>
+      </x:c>
+      <x:c r="B68" s="451" t="str">
+        <x:v>identify, select and use suitable processes and techniques for specific projects (ACTDEK047, ACTDEP050)</x:v>
+      </x:c>
+      <x:c r="C68" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D68" s="451" t="str">
+        <x:v>Mirror Week 3</x:v>
+      </x:c>
+      <x:c r="E68" s="451" t="str">
+        <x:v>Mirror Week 3: Dress and prepare timber to size. Function of the Plane. Project Management</x:v>
+      </x:c>
+      <x:c r="F68" s="451" t="str">
+        <x:v>Mirror Week 3: Theory: Discussion: Refresh FEWTEL. DAR Workbook/Folio: Sketch out design ideas (Cont') Modification of existing plans Practical: Demonstrate / Observe: The use of the handplane / Thicknesser Checking for square face/side | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G68" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9</x:v>
+      </x:c>
+      <x:c r="H68" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I68" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 3</x:v>
+      </x:c>
+      <x:c r="J68" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A69" s="466" t="str">
+        <x:v>CP054</x:v>
+      </x:c>
+      <x:c r="B69" s="451" t="str">
+        <x:v>read and interpret plans and/or materials lists to prepare materials for the completion of projects</x:v>
+      </x:c>
+      <x:c r="C69" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D69" s="451" t="str">
+        <x:v>Mirror Week 3
+Bedside Table Week 3</x:v>
+      </x:c>
+      <x:c r="E69" s="451" t="str">
+        <x:v>Mirror Week 3: Dress and prepare timber to size. Function of the Plane. Project Management
+Bedside Table Week 3: Dress and prepare timber to size. DAR - FEWTEL</x:v>
+      </x:c>
+      <x:c r="F69" s="451" t="str">
+        <x:v>Mirror Week 3: Theory: Discussion: Refresh FEWTEL. DAR Workbook/Folio: Sketch out design ideas (Cont') Modification of existing plans Practical: Demonstrate / Observe: The use of the handplane / Thicknesser Checking for square face/side | Resource: No resource location stated in source row.
+Bedside Table Week 3: Theory: Discussion: Refresh FEWTEL. DAR Workbook/Folio: Sketch out design ideas (Cont') Modification of existing plans Practical: Demonstrate / Observe: Refresh The use of the handplane / Thicknesser | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G69" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H69" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I69" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 3
+stage_5_timber_2021-06-16.docx, table 42, row 3</x:v>
+      </x:c>
+      <x:c r="J69" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="226.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A70" s="466" t="str">
+        <x:v>CP055</x:v>
+      </x:c>
+      <x:c r="B70" s="451" t="str">
+        <x:v>select and use a range of framing, corner, joining and widening methods, for example: (ACTDEK046)</x:v>
+      </x:c>
+      <x:c r="C70" s="451" t="str">
+        <x:v>biscuit and dowel widening joints
+through housing joint for a shelf or divider
+mortise and tenon joint for a table</x:v>
+      </x:c>
+      <x:c r="D70" s="451" t="str">
+        <x:v>Mirror Week 4
+Mirror Week 5
+Mirror Week 6
+Bedside Table Week 4
+Bedside Table Week 5
+Bedside Table Week 6</x:v>
+      </x:c>
+      <x:c r="E70" s="451" t="str">
+        <x:v>Mirror Week 4: Dowel, biscuit and Domino Joints. Research and select suitable timbers. Timber properties and suitable joinery
+Mirror Week 5: Dowel, biscuit and Domino Joints, or other suitable Joints.
+Mirror Week 6: Dowel, biscuit and Domino Joints, or other suitable Joints.
+Bedside Table Week 4: On-guard Mortiser
+Bedside Table Week 5: Mortise and Tenon Joints. On guard - Bandsaw
+Bedside Table Week 6: Mortise and Tenon Joints - SOP Bandsaw</x:v>
+      </x:c>
+      <x:c r="F70" s="451" t="str">
+        <x:v>Mirror Week 4: Theory: Discussion: Refresh safety aspects for powertool use Suitability of dowel, biscuits and dominos Workbook/Folio: Joinery Research Practical: Demonstrate / Observe: The use of the dowel, biscuit and domino cutters | Resource: No resource location stated in source row.
+Mirror Week 5: Theory: Discussion: Cont' Refresh safety aspects for powertool use Suitability of dowel, biscuits and dominos Workbook/Folio: Con't Joinery Research Practical: Demonstrate / Observe: Cont' The use of the dowel, biscuit and domino cutters | Resource: No resource location stated in source row.
+Mirror Week 6: Theory: Discussion: Cont' Refresh safety aspects for powertool use Suitability of dowel, biscuits and dominos Workbook/Folio: Con't Joinery Research Practical: Demonstrate / Observe: Cont' The use of the dowel, biscuit and domino cutters | Resource: No resource location stated in source row.
+Bedside Table Week 4: Theory: Discussion: Refresh safety aspects for Machine use Suitability of Mortise and Tenon Joints Workbook/Folio: Tools, machinery and their uses in making the bedside table Onguard - Mortiser Practical: Demonstrate / Observe: The use of the Mortise Machine | Resource: No resource location stated in source row.
+Bedside Table Week 5: Theory: Discussion: Uses of the bandsaw. Tracking and trouble shooting Workbook/Folio: Onguard - Bandsaw Practical: Demonstrate / Observe: Using the mortise machine and Bandsaw to cut mortise and tenon joints | Resource: No resource location stated in source row.
+Bedside Table Week 6: Theory: Discussion: Uses of the bandsaw. Tracking and trouble shooting Workbook/Folio: SOP - Bandsaw Practical: Demonstrate / Observe: Using the mortise machine and Bandsaw to cut mortise and tenon joints | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G70" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H70" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I70" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 4
+stage_5_timber_2021-06-16.docx, table 36, row 5
+stage_5_timber_2021-06-16.docx, table 36, row 6
+stage_5_timber_2021-06-16.docx, table 42, row 4
+stage_5_timber_2021-06-16.docx, table 42, row 5
+stage_5_timber_2021-06-16.docx, table 42, row 6</x:v>
+      </x:c>
+      <x:c r="J70" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A71" s="466" t="str">
+        <x:v>CP056</x:v>
+      </x:c>
+      <x:c r="B71" s="451" t="str">
+        <x:v>research and select appropriate timbers or timber products and allied materials when completing projects (ACTDEK046)</x:v>
+      </x:c>
+      <x:c r="C71" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D71" s="451" t="str">
+        <x:v>Mirror Week 4
+Bedside Table Week 4</x:v>
+      </x:c>
+      <x:c r="E71" s="451" t="str">
+        <x:v>Mirror Week 4: Dowel, biscuit and Domino Joints. Research and select suitable timbers. Timber properties and suitable joinery
+Bedside Table Week 4: On-guard Mortiser</x:v>
+      </x:c>
+      <x:c r="F71" s="451" t="str">
+        <x:v>Mirror Week 4: Theory: Discussion: Refresh safety aspects for powertool use Suitability of dowel, biscuits and dominos Workbook/Folio: Joinery Research Practical: Demonstrate / Observe: The use of the dowel, biscuit and domino cutters | Resource: No resource location stated in source row.
+Bedside Table Week 4: Theory: Discussion: Refresh safety aspects for Machine use Suitability of Mortise and Tenon Joints Workbook/Folio: Tools, machinery and their uses in making the bedside table Onguard - Mortiser Practical: Demonstrate / Observe: The use of the Mortise Machine | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G71" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H71" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I71" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 4
+stage_5_timber_2021-06-16.docx, table 42, row 4</x:v>
+      </x:c>
+      <x:c r="J71" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="140.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A72" s="466" t="str">
+        <x:v>CP057</x:v>
+      </x:c>
+      <x:c r="B72" s="451" t="str">
+        <x:v>identify and check for defects in solid timber and apply techniques to overcome defects in the production of practical projects</x:v>
+      </x:c>
+      <x:c r="C72" s="451" t="str">
+        <x:v>straight grain for ease of planing
+tight grain for improved surface finish when routing</x:v>
+      </x:c>
+      <x:c r="D72" s="451" t="str">
+        <x:v>Mirror Week 4
+Mirror Week 11
+Mirror Week 12
+Bedside Table Week 4</x:v>
+      </x:c>
+      <x:c r="E72" s="451" t="str">
+        <x:v>Mirror Week 4: Dowel, biscuit and Domino Joints. Research and select suitable timbers. Timber properties and suitable joinery
+Mirror Week 11: Assemble / Gluing. Seasoning Timber.
+Mirror Week 12: Assemble / Gluing. Milling
+Bedside Table Week 4: On-guard Mortiser</x:v>
+      </x:c>
+      <x:c r="F72" s="451" t="str">
+        <x:v>Mirror Week 4: Theory: Discussion: Refresh safety aspects for powertool use Suitability of dowel, biscuits and dominos Workbook/Folio: Joinery Research Practical: Demonstrate / Observe: The use of the dowel, biscuit and domino cutters | Resource: No resource location stated in source row.
+Mirror Week 11: Theory: Discussion: Gluing and clamping - assembly and clamping times Workbook/Folio: Seasoning Timber Practical: Demonstrate / Observe: Glueing and clamping processes | Resource: No resource location stated in source row.
+Mirror Week 12: Theory: Discussion: Discuss the effects of plantation forests, carbon pollution and the effects on the earths atmosphere. Workbook/Folio: Milling Timber Practical: Demonstrate / Observe: Glueing and clamping processes | Resource: No resource location stated in source row.
+Bedside Table Week 4: Theory: Discussion: Refresh safety aspects for Machine use Suitability of Mortise and Tenon Joints Workbook/Folio: Tools, machinery and their uses in making the bedside table Onguard - Mortiser Practical: Demonstrate / Observe: The use of the Mortise Machine | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G72" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H72" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I72" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 4
+stage_5_timber_2021-06-16.docx, table 36, row 11
+stage_5_timber_2021-06-16.docx, table 36, row 12
+stage_5_timber_2021-06-16.docx, table 42, row 4</x:v>
+      </x:c>
+      <x:c r="J72" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A73" s="466" t="str">
+        <x:v>CP058</x:v>
+      </x:c>
+      <x:c r="B73" s="451" t="str">
+        <x:v>compare the machining properties of solid timbers and timber products in relation to production, for example: (ACTDEK046)</x:v>
+      </x:c>
+      <x:c r="C73" s="451" t="str">
+        <x:v>straight grain for ease of planing
+tight grain for improved surface finish when routing</x:v>
+      </x:c>
+      <x:c r="D73" s="451" t="str">
+        <x:v>Mirror Week 4</x:v>
+      </x:c>
+      <x:c r="E73" s="451" t="str">
+        <x:v>Mirror Week 4: Dowel, biscuit and Domino Joints. Research and select suitable timbers. Timber properties and suitable joinery</x:v>
+      </x:c>
+      <x:c r="F73" s="451" t="str">
+        <x:v>Mirror Week 4: Theory: Discussion: Refresh safety aspects for powertool use Suitability of dowel, biscuits and dominos Workbook/Folio: Joinery Research Practical: Demonstrate / Observe: The use of the dowel, biscuit and domino cutters | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G73" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9</x:v>
+      </x:c>
+      <x:c r="H73" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I73" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 4</x:v>
+      </x:c>
+      <x:c r="J73" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="86.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A74" s="466" t="str">
+        <x:v>CP059</x:v>
+      </x:c>
+      <x:c r="B74" s="451" t="str">
+        <x:v>apply power and machine tools in the preparing, cutting, shaping and joining of construction of projects, for example:</x:v>
+      </x:c>
+      <x:c r="C74" s="451" t="str">
+        <x:v>moulding an edge using a router</x:v>
+      </x:c>
+      <x:c r="D74" s="451" t="str">
+        <x:v>Mirror Week 7
+Bedside Table Week 7</x:v>
+      </x:c>
+      <x:c r="E74" s="451" t="str">
+        <x:v>Mirror Week 7: On-guard SOP - Router. Timber Types and features.
+Bedside Table Week 7: On-guard SOP - Thicknesser. Orthogonal Drawings</x:v>
+      </x:c>
+      <x:c r="F74" s="451" t="str">
+        <x:v>Mirror Week 7: Theory: Discussion: Types of uses for the Router. Different profile cutters. Safety aspects and cutting direction Workbook/Folio: Research - Timber types and features Practical: Demonstrate / Observe: The use of the router for decorative edges and mirror rebate. | Resource: No resource location stated in source row.
+Bedside Table Week 7: Theory: Discussion: The use of jigs to assist in machining processes Workbook/Folio: CAD orthogonal drawings of the bedside table On-guard - Thicknesser Practical: Demonstrate / Observe: The use of the 'leg jig' to assist with tapering | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G74" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H74" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I74" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 7
+stage_5_timber_2021-06-16.docx, table 42, row 7</x:v>
+      </x:c>
+      <x:c r="J74" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="86.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A75" s="466" t="str">
+        <x:v>CP060</x:v>
+      </x:c>
+      <x:c r="B75" s="451" t="str">
+        <x:v>prepare and use jigs and templates to assist in the construction and assembly of projects</x:v>
+      </x:c>
+      <x:c r="C75" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D75" s="451" t="str">
+        <x:v>Mirror Week 7
+Bedside Table Week 7</x:v>
+      </x:c>
+      <x:c r="E75" s="451" t="str">
+        <x:v>Mirror Week 7: On-guard SOP - Router. Timber Types and features.
+Bedside Table Week 7: On-guard SOP - Thicknesser. Orthogonal Drawings</x:v>
+      </x:c>
+      <x:c r="F75" s="451" t="str">
+        <x:v>Mirror Week 7: Theory: Discussion: Types of uses for the Router. Different profile cutters. Safety aspects and cutting direction Workbook/Folio: Research - Timber types and features Practical: Demonstrate / Observe: The use of the router for decorative edges and mirror rebate. | Resource: No resource location stated in source row.
+Bedside Table Week 7: Theory: Discussion: The use of jigs to assist in machining processes Workbook/Folio: CAD orthogonal drawings of the bedside table On-guard - Thicknesser Practical: Demonstrate / Observe: The use of the 'leg jig' to assist with tapering | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G75" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H75" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I75" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 7
+stage_5_timber_2021-06-16.docx, table 42, row 7</x:v>
+      </x:c>
+      <x:c r="J75" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="194.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A76" s="466" t="str">
+        <x:v>CP061</x:v>
+      </x:c>
+      <x:c r="B76" s="451" t="str">
+        <x:v>select and apply a range of appropriate techniques to check projects for square, for example:</x:v>
+      </x:c>
+      <x:c r="C76" s="451" t="str">
+        <x:v>measuring diagonals
+using a builder's square</x:v>
+      </x:c>
+      <x:c r="D76" s="451" t="str">
+        <x:v>Mirror Week 8
+Mirror Week 11
+Mirror Week 12
+Bedside Table Week 8
+Bedside Table Week 11
+Bedside Table Week 12</x:v>
+      </x:c>
+      <x:c r="E76" s="451" t="str">
+        <x:v>Mirror Week 8: Dry Clamping. Work Method Statements and SOP's.
+Mirror Week 11: Assemble / Gluing. Seasoning Timber.
+Mirror Week 12: Assemble / Gluing. Milling
+Bedside Table Week 8: Dry Clamping. Work Method Statements and SOP's
+Bedside Table Week 11: Assemble / Gluing. Costing
+Bedside Table Week 12: Assemble / Gluing. Sequencing and Time planning</x:v>
+      </x:c>
+      <x:c r="F76" s="451" t="str">
+        <x:v>Mirror Week 8: Theory: Discussion: The importance of dry clamping and checking for square Workbook/Folio: WMS for the mirror Practical: Demonstrate / Observe: Dry clamping and adjusting for square. | Resource: No resource location stated in source row.
+Mirror Week 11: Theory: Discussion: Gluing and clamping - assembly and clamping times Workbook/Folio: Seasoning Timber Practical: Demonstrate / Observe: Glueing and clamping processes | Resource: No resource location stated in source row.
+Mirror Week 12: Theory: Discussion: Discuss the effects of plantation forests, carbon pollution and the effects on the earths atmosphere. Workbook/Folio: Milling Timber Practical: Demonstrate / Observe: Glueing and clamping processes | Resource: No resource location stated in source row.
+Bedside Table Week 8: Theory: Discussion: Refresh The importance of dry clamping and checking for square Workbook/Folio: WMS for the bedside table Practical: Demonstrate / Observe: Dry clamping and adjusting for square. | Resource: No resource location stated in source row.
+Bedside Table Week 11: Theory: Discussion: Refresh Gluing and clamping - assembly and clamping times Workbook/Folio: Costing Exercise - Spreadsheet Practical: Demonstrate / Observe: Glueing and clamping processes | Resource: No resource location stated in source row.
+Bedside Table Week 12: Discussion: Refresh Gluing and clamping - assembly and clamping times Workbook/Folio: Sequencing and time-planning exercise - Gantt Chart Practical: Demonstrate / Observe: Glueing and clamping processes | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G76" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H76" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I76" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 8
+stage_5_timber_2021-06-16.docx, table 36, row 11
+stage_5_timber_2021-06-16.docx, table 36, row 12
+stage_5_timber_2021-06-16.docx, table 42, row 8
+stage_5_timber_2021-06-16.docx, table 42, row 11
+stage_5_timber_2021-06-16.docx, table 42, row 12</x:v>
+      </x:c>
+      <x:c r="J76" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A77" s="466" t="str">
+        <x:v>CP062</x:v>
+      </x:c>
+      <x:c r="B77" s="451" t="str">
+        <x:v>produce annotated freehand sketches of project components and/or projects to visualise, communicate, understand and record ideas</x:v>
+      </x:c>
+      <x:c r="C77" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D77" s="451" t="str">
+        <x:v>Mirror Week 9
+Mirror Week 10</x:v>
+      </x:c>
+      <x:c r="E77" s="451" t="str">
+        <x:v>Mirror Week 9: Adding Design Features. Timber Conversion.
+Mirror Week 10: Adding Design Features. Workshop Maintenence.</x:v>
+      </x:c>
+      <x:c r="F77" s="451" t="str">
+        <x:v>Mirror Week 9: Theory: Discussion: Discuss factors that affect good design - form and function. Workbook/Folio: Spreadsheet costing exercise. Practical: Demonstrate / Observe: Design features. Suitability and techniques | Resource: No resource location stated in source row.
+Mirror Week 10: Theory: Discussion: The importance of good workshop maintenance Practical: Demonstrate / Observe: Manual handling techniques | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G77" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9</x:v>
+      </x:c>
+      <x:c r="H77" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I77" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 9
+stage_5_timber_2021-06-16.docx, table 36, row 10</x:v>
+      </x:c>
+      <x:c r="J77" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="151.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A78" s="466" t="str">
+        <x:v>CP063</x:v>
+      </x:c>
+      <x:c r="B78" s="451" t="str">
+        <x:v>modify and/or apply workshop drawings in the completion of projects, for example:</x:v>
+      </x:c>
+      <x:c r="C78" s="451" t="str">
+        <x:v>use CAD applications in the production of workshop drawings</x:v>
+      </x:c>
+      <x:c r="D78" s="451" t="str">
+        <x:v>Mirror Week 9
+Mirror Week 10
+Bedside Table Week 9
+Bedside Table Week 10</x:v>
+      </x:c>
+      <x:c r="E78" s="451" t="str">
+        <x:v>Mirror Week 9: Adding Design Features. Timber Conversion.
+Mirror Week 10: Adding Design Features. Workshop Maintenence.
+Bedside Table Week 9: Adding Design Features. Orthogonal Drawings
+Bedside Table Week 10: Adding Design Features. Orthogonal Drawings</x:v>
+      </x:c>
+      <x:c r="F78" s="451" t="str">
+        <x:v>Mirror Week 9: Theory: Discussion: Discuss factors that affect good design - form and function. Workbook/Folio: Spreadsheet costing exercise. Practical: Demonstrate / Observe: Design features. Suitability and techniques | Resource: No resource location stated in source row.
+Mirror Week 10: Theory: Discussion: The importance of good workshop maintenance Practical: Demonstrate / Observe: Manual handling techniques | Resource: No resource location stated in source row.
+Bedside Table Week 9: Theory: Discussion: Refresh Discuss factors that affect good design - form and function. Workbook/Folio: Adding design features to CAD orthogonal drawings ie. Inlays, secret drawers, routered mouldings etc. Practical: Demonstrate / Observe: The use of hinges, handles, runners and other suitable hardware | Resource: No resource location stated in source row.
+Bedside Table Week 10: Theory: Discussion: Refresh Discuss factors that affect good design - form and function. Workbook/Folio: Adding design features to CAD orthogonal drawings ie. Inlays, secret drawers, routered mouldings etc. Practical: Demonstrate / Observe: The use of hinges, handles, runners and other suitable hardware | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G78" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H78" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I78" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 9
+stage_5_timber_2021-06-16.docx, table 36, row 10
+stage_5_timber_2021-06-16.docx, table 42, row 9
+stage_5_timber_2021-06-16.docx, table 42, row 10</x:v>
+      </x:c>
+      <x:c r="J78" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A79" s="466" t="str">
+        <x:v>CP064</x:v>
+      </x:c>
+      <x:c r="B79" s="451" t="str">
+        <x:v>select and apply a range of production and detailing techniques, for example:</x:v>
+      </x:c>
+      <x:c r="C79" s="451" t="str">
+        <x:v>inlay
+laser engraving</x:v>
+      </x:c>
+      <x:c r="D79" s="451" t="str">
+        <x:v>Mirror Week 10</x:v>
+      </x:c>
+      <x:c r="E79" s="451" t="str">
+        <x:v>Mirror Week 10: Adding Design Features. Workshop Maintenence.</x:v>
+      </x:c>
+      <x:c r="F79" s="451" t="str">
+        <x:v>Mirror Week 10: Theory: Discussion: The importance of good workshop maintenance Practical: Demonstrate / Observe: Manual handling techniques | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G79" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9</x:v>
+      </x:c>
+      <x:c r="H79" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I79" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 10</x:v>
+      </x:c>
+      <x:c r="J79" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A80" s="466" t="str">
+        <x:v>CP065</x:v>
+      </x:c>
+      <x:c r="B80" s="451" t="str">
+        <x:v>analyse the effects of incorrect seasoning and insect attack on properties and appearance of the timber</x:v>
+      </x:c>
+      <x:c r="C80" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D80" s="451" t="str">
+        <x:v>Mirror Week 11
+Mirror Week 12</x:v>
+      </x:c>
+      <x:c r="E80" s="451" t="str">
+        <x:v>Mirror Week 11: Assemble / Gluing. Seasoning Timber.
+Mirror Week 12: Assemble / Gluing. Milling</x:v>
+      </x:c>
+      <x:c r="F80" s="451" t="str">
+        <x:v>Mirror Week 11: Theory: Discussion: Gluing and clamping - assembly and clamping times Workbook/Folio: Seasoning Timber Practical: Demonstrate / Observe: Glueing and clamping processes | Resource: No resource location stated in source row.
+Mirror Week 12: Theory: Discussion: Discuss the effects of plantation forests, carbon pollution and the effects on the earths atmosphere. Workbook/Folio: Milling Timber Practical: Demonstrate / Observe: Glueing and clamping processes | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G80" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9</x:v>
+      </x:c>
+      <x:c r="H80" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I80" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 11
+stage_5_timber_2021-06-16.docx, table 36, row 12</x:v>
+      </x:c>
+      <x:c r="J80" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A81" s="466" t="str">
+        <x:v>CP066</x:v>
+      </x:c>
+      <x:c r="B81" s="451" t="str">
+        <x:v>select and apply appropriate surface preparation methods and apply a variety of finishes</x:v>
+      </x:c>
+      <x:c r="C81" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D81" s="451" t="str">
+        <x:v>Mirror Week 13
+Bedside Table Week 13
+Bedside Table Week 14</x:v>
+      </x:c>
+      <x:c r="E81" s="451" t="str">
+        <x:v>Mirror Week 13: Finishing Techniques. Environmental sustainability
+Bedside Table Week 13: Finishing Techniques. Logging
+Bedside Table Week 14: Finishing Techniques. Industry Visit / link</x:v>
+      </x:c>
+      <x:c r="F81" s="451" t="str">
+        <x:v>Mirror Week 13: Theory: Discussion: Refresh Sanding and prep' techniques Different types of finishes Discuss deforestation and sustainable logging. Workbook/Folio: Environmental Sustainability Practical: Demonstrate / Observe: Preparing surfaces for finishing Apply finishes | Resource: No resource location stated in source row.
+Bedside Table Week 13: Theory: Discussion: Refresh Sanding and prep' techniques Different types of finishes Workbook/Folio: Logging worksheet Practical: Demonstrate / Observe: Preparing surfaces for finishing Apply finishes | Resource: No resource location stated in source row.
+Bedside Table Week 14: Theory: Discussion: Compare and contrast Industry techniques compared to school. - Joinery / Kitchen Cabinets Workbook/Folio: Industry Link worksheet Practical: Demonstrate / Observe: Preparing surfaces for finishing Apply finishes | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G81" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H81" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I81" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 13
+stage_5_timber_2021-06-16.docx, table 42, row 13
+stage_5_timber_2021-06-16.docx, table 42, row 14</x:v>
+      </x:c>
+      <x:c r="J81" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A82" s="466" t="str">
+        <x:v>CP067</x:v>
+      </x:c>
+      <x:c r="B82" s="451" t="str">
+        <x:v>compare and contrast contemporary industrial manufacturing techniques, materials and equipment with classroom experiences</x:v>
+      </x:c>
+      <x:c r="C82" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D82" s="451" t="str">
+        <x:v>Mirror Week 14</x:v>
+      </x:c>
+      <x:c r="E82" s="451" t="str">
+        <x:v>Mirror Week 14: Fitting Glass. Industry Visit / link</x:v>
+      </x:c>
+      <x:c r="F82" s="451" t="str">
+        <x:v>Mirror Week 14: Theory: Discussion: Compare and contrast Industry techniques compared to school. Workbook/Folio: Industry Links worksheet Practical: Demonstrate / Observe: Cutting glass to suit. | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G82" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9</x:v>
+      </x:c>
+      <x:c r="H82" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I82" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 14</x:v>
+      </x:c>
+      <x:c r="J82" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="108" hidden="0" customHeight="1">
+      <x:c r="A83" s="466" t="str">
+        <x:v>CP068</x:v>
+      </x:c>
+      <x:c r="B83" s="451" t="str">
+        <x:v>research current techniques, materials and equipment used by industry to develop and produce timber products (ACTDEK047)</x:v>
+      </x:c>
+      <x:c r="C83" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D83" s="451" t="str">
+        <x:v>Mirror Week 14
+Bedside Table Week 13
+Bedside Table Week 14</x:v>
+      </x:c>
+      <x:c r="E83" s="451" t="str">
+        <x:v>Mirror Week 14: Fitting Glass. Industry Visit / link
+Bedside Table Week 13: Finishing Techniques. Logging
+Bedside Table Week 14: Finishing Techniques. Industry Visit / link</x:v>
+      </x:c>
+      <x:c r="F83" s="451" t="str">
+        <x:v>Mirror Week 14: Theory: Discussion: Compare and contrast Industry techniques compared to school. Workbook/Folio: Industry Links worksheet Practical: Demonstrate / Observe: Cutting glass to suit. | Resource: No resource location stated in source row.
+Bedside Table Week 13: Theory: Discussion: Refresh Sanding and prep' techniques Different types of finishes Workbook/Folio: Logging worksheet Practical: Demonstrate / Observe: Preparing surfaces for finishing Apply finishes | Resource: No resource location stated in source row.
+Bedside Table Week 14: Theory: Discussion: Compare and contrast Industry techniques compared to school. - Joinery / Kitchen Cabinets Workbook/Folio: Industry Link worksheet Practical: Demonstrate / Observe: Preparing surfaces for finishing Apply finishes | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G83" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H83" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I83" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 14
+stage_5_timber_2021-06-16.docx, table 42, row 13
+stage_5_timber_2021-06-16.docx, table 42, row 14</x:v>
+      </x:c>
+      <x:c r="J83" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A84" s="466" t="str">
+        <x:v>CP069</x:v>
+      </x:c>
+      <x:c r="B84" s="451" t="str">
+        <x:v>describe the impact of new and emerging technologies on careers and professions in the timber industry</x:v>
+      </x:c>
+      <x:c r="C84" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D84" s="451" t="str">
+        <x:v>Mirror Week 14</x:v>
+      </x:c>
+      <x:c r="E84" s="451" t="str">
+        <x:v>Mirror Week 14: Fitting Glass. Industry Visit / link</x:v>
+      </x:c>
+      <x:c r="F84" s="451" t="str">
+        <x:v>Mirror Week 14: Theory: Discussion: Compare and contrast Industry techniques compared to school. Workbook/Folio: Industry Links worksheet Practical: Demonstrate / Observe: Cutting glass to suit. | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G84" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9</x:v>
+      </x:c>
+      <x:c r="H84" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I84" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 14</x:v>
+      </x:c>
+      <x:c r="J84" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A85" s="466" t="str">
+        <x:v>CP070</x:v>
+      </x:c>
+      <x:c r="B85" s="451" t="str">
+        <x:v>compare and contrast careers and professions in the timber and related industries, for example:</x:v>
+      </x:c>
+      <x:c r="C85" s="451" t="str">
+        <x:v>a kitchen manufacturer compared to a builder</x:v>
+      </x:c>
+      <x:c r="D85" s="451" t="str">
+        <x:v>Mirror Week 14</x:v>
+      </x:c>
+      <x:c r="E85" s="451" t="str">
+        <x:v>Mirror Week 14: Fitting Glass. Industry Visit / link</x:v>
+      </x:c>
+      <x:c r="F85" s="451" t="str">
+        <x:v>Mirror Week 14: Theory: Discussion: Compare and contrast Industry techniques compared to school. Workbook/Folio: Industry Links worksheet Practical: Demonstrate / Observe: Cutting glass to suit. | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G85" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9</x:v>
+      </x:c>
+      <x:c r="H85" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I85" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 14</x:v>
+      </x:c>
+      <x:c r="J85" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A86" s="466" t="str">
+        <x:v>CP071</x:v>
+      </x:c>
+      <x:c r="B86" s="451" t="str">
+        <x:v>explore the environmental effect from the production and use of manufactured boards</x:v>
+      </x:c>
+      <x:c r="C86" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D86" s="451" t="str">
+        <x:v>Mirror Week 15
+Bedside Table Week 15</x:v>
+      </x:c>
+      <x:c r="E86" s="451" t="str">
+        <x:v>Mirror Week 15: Safe handling of chemicals and MSDS
+Bedside Table Week 15: Safe handling of chemicals and MSDS</x:v>
+      </x:c>
+      <x:c r="F86" s="451" t="str">
+        <x:v>Mirror Week 15: Theory: Discussion: The importance of safe handling of chemicals and the use of MSDS's. Workbook/Folio: Reading MSDS's Practical: Demonstrate / Observe: Ongoing safe workshop procedures | Resource: No resource location stated in source row.
+Bedside Table Week 15: Theory: Discussion: Refresh The importance of safe handling of chemicals and the use of MSDS's. Workbook/Folio: Reading MSDS's Practical: Demonstrate / Observe: Ongoing safe workshop procedures | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G86" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H86" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I86" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 15
+stage_5_timber_2021-06-16.docx, table 42, row 15</x:v>
+      </x:c>
+      <x:c r="J86" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A87" s="466" t="str">
+        <x:v>CP072</x:v>
+      </x:c>
+      <x:c r="B87" s="451" t="str">
+        <x:v>explain the environmental and societal impact of resources used in the development and production of projects</x:v>
+      </x:c>
+      <x:c r="C87" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D87" s="451" t="str">
+        <x:v>Mirror Week 15
+Bedside Table Week 15</x:v>
+      </x:c>
+      <x:c r="E87" s="451" t="str">
+        <x:v>Mirror Week 15: Safe handling of chemicals and MSDS
+Bedside Table Week 15: Safe handling of chemicals and MSDS</x:v>
+      </x:c>
+      <x:c r="F87" s="451" t="str">
+        <x:v>Mirror Week 15: Theory: Discussion: The importance of safe handling of chemicals and the use of MSDS's. Workbook/Folio: Reading MSDS's Practical: Demonstrate / Observe: Ongoing safe workshop procedures | Resource: No resource location stated in source row.
+Bedside Table Week 15: Theory: Discussion: Refresh The importance of safe handling of chemicals and the use of MSDS's. Workbook/Folio: Reading MSDS's Practical: Demonstrate / Observe: Ongoing safe workshop procedures | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G87" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H87" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I87" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 15
+stage_5_timber_2021-06-16.docx, table 42, row 15</x:v>
+      </x:c>
+      <x:c r="J87" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="54" hidden="0" customHeight="1">
+      <x:c r="A88" s="466" t="str">
+        <x:v>CP073</x:v>
+      </x:c>
+      <x:c r="B88" s="451" t="str">
+        <x:v>investigate the environmental implications of the use of old-growth timbers</x:v>
+      </x:c>
+      <x:c r="C88" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D88" s="451" t="str">
+        <x:v>Mirror Week 16
+Bedside Table Week 16</x:v>
+      </x:c>
+      <x:c r="E88" s="451" t="str">
+        <x:v>Mirror Week 16: Polishing. Sustainability
+Bedside Table Week 16: Polishing. Sustainability and Environmental Impact</x:v>
+      </x:c>
+      <x:c r="F88" s="451" t="str">
+        <x:v>Mirror Week 16: Theory: Discussion: The purposes of Timber polishes Practical: Demonstrate / Observe: Ongoing safe workshop procedures | Resource: No resource location stated in source row.
+Bedside Table Week 16: Theory: Discussion: Refresh The purposes of timber polishes Practical: Demonstrate / Observe: Ongoing safe workshop procedures | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G88" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H88" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I88" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 16
+stage_5_timber_2021-06-16.docx, table 42, row 16</x:v>
+      </x:c>
+      <x:c r="J88" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="54" hidden="0" customHeight="1">
+      <x:c r="A89" s="466" t="str">
+        <x:v>CP074</x:v>
+      </x:c>
+      <x:c r="B89" s="451" t="str">
+        <x:v>describe the effects of the timber and furnishing industries on society and the environment, for example:</x:v>
+      </x:c>
+      <x:c r="C89" s="451" t="str">
+        <x:v>conserving historic furniture</x:v>
+      </x:c>
+      <x:c r="D89" s="451" t="str">
+        <x:v>Mirror Week 16
+Bedside Table Week 16</x:v>
+      </x:c>
+      <x:c r="E89" s="451" t="str">
+        <x:v>Mirror Week 16: Polishing. Sustainability
+Bedside Table Week 16: Polishing. Sustainability and Environmental Impact</x:v>
+      </x:c>
+      <x:c r="F89" s="451" t="str">
+        <x:v>Mirror Week 16: Theory: Discussion: The purposes of Timber polishes Practical: Demonstrate / Observe: Ongoing safe workshop procedures | Resource: No resource location stated in source row.
+Bedside Table Week 16: Theory: Discussion: Refresh The purposes of timber polishes Practical: Demonstrate / Observe: Ongoing safe workshop procedures | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G89" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H89" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I89" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 16
+stage_5_timber_2021-06-16.docx, table 42, row 16</x:v>
+      </x:c>
+      <x:c r="J89" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A90" s="466" t="str">
+        <x:v>CP075</x:v>
+      </x:c>
+      <x:c r="B90" s="451" t="str">
+        <x:v>recognise and comply with WHS signage</x:v>
+      </x:c>
+      <x:c r="C90" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D90" s="451" t="str">
+        <x:v>Mirror Week 18
+Bedside Table Week 18</x:v>
+      </x:c>
+      <x:c r="E90" s="451" t="str">
+        <x:v>Mirror Week 18: Class Test
+Bedside Table Week 18: Class Test</x:v>
+      </x:c>
+      <x:c r="F90" s="451" t="str">
+        <x:v>Mirror Week 18: Theory: Workbook/Folio: Class Test Practical: Demonstrate / Observe: Ongoing safe workshop procedures | Resource: No resource location stated in source row.
+Bedside Table Week 18: Theory: Workbook/Folio: Class Test Practical: Demonstrate / Observe: Ongoing safe workshop procedures | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G90" s="451" t="str">
+        <x:v>Mirror: Project Evidence row 9
+Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H90" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I90" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 36, row 18
+stage_5_timber_2021-06-16.docx, table 42, row 18</x:v>
+      </x:c>
+      <x:c r="J90" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="86.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A91" s="466" t="str">
+        <x:v>CP076</x:v>
+      </x:c>
+      <x:c r="B91" s="451" t="str">
+        <x:v>investigate methods of cutting veneers and their associated characteristics and properties</x:v>
+      </x:c>
+      <x:c r="C91" s="451" t="str">
+        <x:v>Not stated in source.</x:v>
+      </x:c>
+      <x:c r="D91" s="451" t="str">
+        <x:v>Bedside Table Week 9
+Bedside Table Week 10</x:v>
+      </x:c>
+      <x:c r="E91" s="451" t="str">
+        <x:v>Bedside Table Week 9: Adding Design Features. Orthogonal Drawings
+Bedside Table Week 10: Adding Design Features. Orthogonal Drawings</x:v>
+      </x:c>
+      <x:c r="F91" s="451" t="str">
+        <x:v>Bedside Table Week 9: Theory: Discussion: Refresh Discuss factors that affect good design - form and function. Workbook/Folio: Adding design features to CAD orthogonal drawings ie. Inlays, secret drawers, routered mouldings etc. Practical: Demonstrate / Observe: The use of hinges, handles, runners and other suitable hardware | Resource: No resource location stated in source row.
+Bedside Table Week 10: Theory: Discussion: Refresh Discuss factors that affect good design - form and function. Workbook/Folio: Adding design features to CAD orthogonal drawings ie. Inlays, secret drawers, routered mouldings etc. Practical: Demonstrate / Observe: The use of hinges, handles, runners and other suitable hardware | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G91" s="451" t="str">
+        <x:v>Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H91" s="475" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I91" s="451" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 42, row 9
+stage_5_timber_2021-06-16.docx, table 42, row 10</x:v>
+      </x:c>
+      <x:c r="J91" s="452" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="86.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A92" s="467" t="str">
+        <x:v>CP077</x:v>
+      </x:c>
+      <x:c r="B92" s="454" t="str">
+        <x:v>identify, select and use a range of cabinet fittings, hardware and allied materials in the production of projects, for example:</x:v>
+      </x:c>
+      <x:c r="C92" s="454" t="str">
+        <x:v>hinges/handles on a cabinet
+metal runners for smooth-running drawers</x:v>
+      </x:c>
+      <x:c r="D92" s="454" t="str">
+        <x:v>Bedside Table Week 9
+Bedside Table Week 10</x:v>
+      </x:c>
+      <x:c r="E92" s="454" t="str">
+        <x:v>Bedside Table Week 9: Adding Design Features. Orthogonal Drawings
+Bedside Table Week 10: Adding Design Features. Orthogonal Drawings</x:v>
+      </x:c>
+      <x:c r="F92" s="454" t="str">
+        <x:v>Bedside Table Week 9: Theory: Discussion: Refresh Discuss factors that affect good design - form and function. Workbook/Folio: Adding design features to CAD orthogonal drawings ie. Inlays, secret drawers, routered mouldings etc. Practical: Demonstrate / Observe: The use of hinges, handles, runners and other suitable hardware | Resource: No resource location stated in source row.
+Bedside Table Week 10: Theory: Discussion: Refresh Discuss factors that affect good design - form and function. Workbook/Folio: Adding design features to CAD orthogonal drawings ie. Inlays, secret drawers, routered mouldings etc. Practical: Demonstrate / Observe: The use of hinges, handles, runners and other suitable hardware | Resource: No resource location stated in source row.</x:v>
+      </x:c>
+      <x:c r="G92" s="454" t="str">
+        <x:v>Bedside Table: Project Evidence row 10</x:v>
+      </x:c>
+      <x:c r="H92" s="476" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I92" s="454" t="str">
+        <x:v>stage_5_timber_2021-06-16.docx, table 42, row 9
+stage_5_timber_2021-06-16.docx, table 42, row 10</x:v>
+      </x:c>
+      <x:c r="J92" s="455" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J2"/>
+    <x:mergeCell ref="A3:J4"/>
+    <x:mergeCell ref="H6:J6"/>
+    <x:mergeCell ref="H7:J12"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/Timber Course Alignment Audit.xlsx
+++ b/Timber Course Alignment Audit.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview &amp; Legend" sheetId="1" r:id="Rcf448a0dd26a4801"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Syllabus Alignment Matrix" sheetId="2" r:id="R3afeb0cd735b4976"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Evidence" sheetId="3" r:id="R9fa18db5c74d4843"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Register" sheetId="4" r:id="R7ccf8046f0a046cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Register" sheetId="5" r:id="R3ce27269267245d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current Syllabus Summary" sheetId="6" r:id="Rd46bc5f6794a45e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current Program Content Map" sheetId="7" r:id="Ra98e059dbceb4fbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview &amp; Legend" sheetId="1" r:id="R3050c553c5ec4515"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Syllabus Alignment Matrix" sheetId="2" r:id="Rec065f48f56a4759"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Evidence" sheetId="3" r:id="Rcf2d1e2ccf0b4209"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Register" sheetId="4" r:id="R64472fad00504fd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Register" sheetId="5" r:id="R19c9f586a4854577"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current Syllabus Summary" sheetId="6" r:id="R5501f87d503b454e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current Program Content Map" sheetId="7" r:id="R21aa6e97873b4052"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -168,7 +168,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="34">
+  <x:fills count="35">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -328,6 +328,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE6F0EB"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -646,7 +651,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="547">
+  <x:cellXfs count="552">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2096,6 +2101,21 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="24" fillId="33" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="34" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="34" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2538,7 +2558,7 @@
       <x:c r="G15" s="269"/>
       <x:c r="H15" s="269"/>
     </x:row>
-    <x:row r="16" ht="32" customHeight="1">
+    <x:row r="16" ht="112" customHeight="1">
       <x:c r="A16" s="265" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -2548,13 +2568,13 @@
       <x:c r="C16" s="276" t="str">
         <x:v>Year 9 · supplied current program</x:v>
       </x:c>
-      <x:c r="E16" s="507" t="str">
-        <x:f>"All ten current outcomes are addressed across the two-year pathway: "&amp;COUNTIF('Current Syllabus Summary'!B11:B20,"Covered")&amp;" Covered; "&amp;COUNTIF('Current Syllabus Summary'!B11:B20,"Partially covered")&amp;" Partially covered; "&amp;COUNTIF('Current Syllabus Summary'!B11:B20,"Has gaps")&amp;" Has gaps. IND56 is covered across the pathway; Mirror's local evidence repair awaits publication and live re-audit. IND59 is explicitly evidenced at Clock, with other full outcome lists clarified as course context. Of 77 unique current-program content statements, 75 occur in represented formal projects; two Pen-only lathe statements remain pending a course-sequence decision."</x:f>
-        <x:v>All ten current outcomes are addressed across the two-year pathway: 10 Covered; 0 Partially covered; 0 Has gaps. IND56 is covered across the pathway; Mirror's local evidence repair awaits publication and live re-audit. IND59 is explicitly evidenced at Clock, with other full outcome lists clarified as course context. Of 77 unique current-program content statements, 75 occur in represented formal projects; two Pen-only lathe statements remain pending a course-sequence decision.</x:v>
-      </x:c>
-      <x:c r="F16" s="507"/>
-      <x:c r="G16" s="507"/>
-      <x:c r="H16" s="507"/>
+      <x:c r="E16" s="547" t="str">
+        <x:f>"All ten current outcomes are addressed across the two-year pathway: "&amp;COUNTIF('Current Syllabus Summary'!B11:B20,"Covered")&amp;" Covered; "&amp;COUNTIF('Current Syllabus Summary'!B11:B20,"Partially covered")&amp;" Partially covered; "&amp;COUNTIF('Current Syllabus Summary'!B11:B20,"Has gaps")&amp;" Has gaps. IND56 now has live introductory, developed and evidenced collaboration records across Breadboard, Mirror and Bedside Table. IND59 is explicitly evidenced at Clock, with other project outcome lists verified as course context. No current outcome gap remains; the two Pen-only lathe content points remain an open program-scope decision."</x:f>
+        <x:v>All ten current outcomes are addressed across the two-year pathway: 10 Covered; 0 Partially covered; 0 Has gaps. IND56 now has live introductory, developed and evidenced collaboration records across Breadboard, Mirror and Bedside Table. IND59 is explicitly evidenced at Clock, with other project outcome lists verified as course context. No current outcome gap remains; the two Pen-only lathe content points remain an open program-scope decision.</x:v>
+      </x:c>
+      <x:c r="F16" s="547"/>
+      <x:c r="G16" s="547"/>
+      <x:c r="H16" s="547"/>
     </x:row>
     <x:row r="17" ht="32" customHeight="1">
       <x:c r="A17" s="292" t="n">
@@ -3207,7 +3227,7 @@
         <x:v>Weeks 9-10 drawing/CAD communication and Weeks 17-18 folio evidence.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="66" customHeight="1">
+    <x:row r="12" ht="132" customHeight="1">
       <x:c r="A12" s="88" t="str">
         <x:v>Current program</x:v>
       </x:c>
@@ -3244,13 +3264,13 @@
       <x:c r="L12" s="113" t="str">
         <x:v>Weeks 15–16 team-lift and communication practice (CUR-01).</x:v>
       </x:c>
-      <x:c r="M12" s="522" t="str">
+      <x:c r="M12" s="548" t="str">
         <x:v>E</x:v>
       </x:c>
       <x:c r="N12" s="113" t="str">
-        <x:v>Local implementation 2026-08-02 - Mirror Portfolio Workbook, Peer Quality Check and Workshop Handover. Captures roles, criterion/evidence, feedback, justified decision, result check and handover contribution. Local QA complete; publication and live re-audit pending (S19).</x:v>
-      </x:c>
-      <x:c r="O12" s="493" t="str">
+        <x:v>Mirror Portfolio Workbook, Peer Quality Check and Workshop Handover - saved roles, criterion/evidence, feedback, justified decision, result check and handover contribution. Live verified 2026-08-02 at https://stevencowell.github.io/year-10-timber-mirror-project/mirror_portfolio_workbook.html (commit 9668c52; S19).</x:v>
+      </x:c>
+      <x:c r="O12" s="548" t="str">
         <x:v>E</x:v>
       </x:c>
       <x:c r="P12" s="113" t="str">
@@ -3375,7 +3395,7 @@
         <x:v>Weeks 17-18 criterion-based product evaluation and folio evidence.</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="66" customHeight="1">
+    <x:row r="15" ht="118" customHeight="1">
       <x:c r="A15" s="88" t="str">
         <x:v>Current program</x:v>
       </x:c>
@@ -3392,7 +3412,7 @@
         <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="F15" s="113" t="str">
-        <x:v>Breadboard displays the course outcome list as context, not as a separate project-level IND59 assessment claim. Clock Weeks 15-16 remains the formal current-program E evidence for IND59; see Current Syllabus Summary IND59 and S19 local wording clarification.</x:v>
+        <x:v>Breadboard displays the course outcome list as context, not as a separate project-level IND59 assessment claim. Clock Weeks 15-16 remains the formal current-program E evidence for IND59. Course-context wording live verified 2026-08-02 (commit 11f7690; S19).</x:v>
       </x:c>
       <x:c r="G15" s="308" t="str">
         <x:v>Gap</x:v>
@@ -3412,17 +3432,17 @@
       <x:c r="L15" s="113" t="str">
         <x:v>Weeks 3-4 compares traditional and industrial timber production; no emerging-tech task.</x:v>
       </x:c>
-      <x:c r="M15" s="524" t="str">
+      <x:c r="M15" s="549" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="N15" s="113" t="str">
-        <x:v>Mirror displays the course outcome list as context, not as a separate project-level IND59 assessment claim. Clock Weeks 15-16 remains the formal current-program E evidence for IND59; see Current Syllabus Summary IND59 and S19 local wording clarification.</x:v>
-      </x:c>
-      <x:c r="O15" s="524" t="str">
+        <x:v>Mirror displays the course outcome list as context, not as a separate project-level IND59 assessment claim. Clock Weeks 15-16 remains the formal current-program E evidence for IND59. Course-context wording live verified 2026-08-02 (commit 9668c52; S19).</x:v>
+      </x:c>
+      <x:c r="O15" s="549" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="P15" s="113" t="str">
-        <x:v>Bedside Table displays the course outcome list as context, not as a separate project-level IND59 assessment claim. Clock Weeks 15-16 remains the formal current-program E evidence for IND59; see Current Syllabus Summary IND59 and S19 local wording clarification.</x:v>
+        <x:v>Bedside Table displays the course outcome list as context, not as a separate project-level IND59 assessment claim. Clock Weeks 15-16 remains the formal current-program E evidence for IND59. Course-context wording live verified 2026-08-02 (commit 9395842; S19).</x:v>
       </x:c>
       <x:c r="Q15" s="110" t="str">
         <x:v>E</x:v>
@@ -4191,7 +4211,7 @@
         <x:v>Date reviewed</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="142" customHeight="1">
+    <x:row r="5" ht="170" customHeight="1">
       <x:c r="A5" s="47" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -4212,10 +4232,10 @@
 Local implementation 2026-08-02 — Module 05 activity 1 captures peer feedback given/received, one improvement and a result check; it autosaves and is included in Print / Save PDF. Live verified 2026-08-02 (S18).</x:v>
       </x:c>
       <x:c r="G5" s="94" t="str">
-        <x:v>breadboard-folio.html is the selected public assessment-evidence destination: 12 project checkpoints, photo/caption evidence, autosave, backup and Print / Save PDF. It is not a formal task notification or marking rubric.</x:v>
+        <x:v>Live verified assessment-evidence destination: https://stevencowell.github.io/bread-board-guided-course/breadboard-folio.html - 12 project checkpoints, photo/caption evidence, autosave, backup and Print / Save PDF. It is not a formal task notification or marking rubric.</x:v>
       </x:c>
       <x:c r="H5" s="94" t="str">
-        <x:v>Assessment access decision recorded: use the project evidence folio. Formal task notices, dates, marks and Classroom submission remain teacher-controlled.</x:v>
+        <x:v>Assessment access closed and verified 2026-08-02. Formal task notices, dates, marks and Classroom submission remain teacher-controlled.</x:v>
       </x:c>
       <x:c r="I5" s="94" t="str">
         <x:v>Reviewed</x:v>
@@ -4297,7 +4317,7 @@
         <x:v>2026-08-01</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="92" customHeight="1">
+    <x:row r="8" ht="170" customHeight="1">
       <x:c r="A8" s="48" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -4317,10 +4337,10 @@
         <x:v>10 guided modules with saved MCQ/written responses; printable Carry-all folio.</x:v>
       </x:c>
       <x:c r="G8" s="96" t="str">
-        <x:v>carry-all-folio.html is the selected public assessment-evidence destination: 12 project cards, responses/photos, progress, autosave, ZIP backup and Print / Save PDF. It is not a formal task notification or marking rubric.</x:v>
+        <x:v>Live verified assessment-evidence destination: https://stevencowell.github.io/Yr-9-Carry-All/carry-all-folio.html - 12 project cards, responses/photos, progress, autosave, ZIP backup and Print / Save PDF. It is not a formal task notification or marking rubric.</x:v>
       </x:c>
       <x:c r="H8" s="96" t="str">
-        <x:v>IND59 is introductory here. Assessment access decision recorded: use the project evidence folio; formal task notices and Classroom submission remain teacher-controlled.</x:v>
+        <x:v>IND59 is introductory here. Assessment access closed and verified 2026-08-02; formal task notices and Classroom submission remain teacher-controlled.</x:v>
       </x:c>
       <x:c r="I8" s="96" t="str">
         <x:v>Reviewed</x:v>
@@ -4332,7 +4352,7 @@
         <x:v>2026-08-01</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="92" customHeight="1">
+    <x:row r="9" ht="170" customHeight="1">
       <x:c r="A9" s="48" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -4349,25 +4369,25 @@
         <x:v>Mirror-Project-Plans.pdf is linked from the live site.</x:v>
       </x:c>
       <x:c r="F9" s="96" t="str">
-        <x:v>9 live theory/activity pages, quizzes and editable portfolio workbook; separate folio; 20 repaired support-week routes. Local implementation 2026-08-02 - Portfolio Workbook Peer Quality Check and Workshop Handover captures a reviewer role, observable criterion/evidence, feedback, justified decision, result check and workshop handover; publication pending.</x:v>
+        <x:v>9 live theory/activity pages, quizzes and editable portfolio workbook; separate folio; 20 repaired support-week routes. The live Portfolio Workbook Peer Quality Check and Workshop Handover captures reviewer roles, observable criterion/evidence, feedback, a justified decision, result check and workshop handover.</x:v>
       </x:c>
       <x:c r="G9" s="96" t="str">
-        <x:v>mirror_assessment.html identifies practical, folio and class-test evidence. Local assessment-guide update adds the peer quality-check and handover record to portfolio evidence and rubric; publication pending.</x:v>
+        <x:v>mirror_assessment.html identifies practical, folio and class-test evidence and now includes the peer quality-check and handover record in the portfolio evidence checklist and rubric. Live verified 2026-08-02.</x:v>
       </x:c>
       <x:c r="H9" s="96" t="str">
-        <x:v>IND56 local repair awaits publication and live re-audit (CUR-01). IND59 is a course-context outcome here, not a separate Mirror evidence claim; Clock is the designated pathway E point (CUR-02).</x:v>
+        <x:v>IND56 project evidence is closed and verified. IND59 is course context here, not a separate Mirror assessment claim; Clock is the designated pathway E point.</x:v>
       </x:c>
       <x:c r="I9" s="96" t="str">
-        <x:v>Reviewed - local evidence repair pending publication</x:v>
+        <x:v>Reviewed - live evidence verified</x:v>
       </x:c>
       <x:c r="J9" s="33" t="str">
-        <x:v>Current-program project. Repaired support routes remain complete. Local collaboration record and assessment-rubric traceability were QA checked 2026-08-02; this does not assert individual student achievement.</x:v>
+        <x:v>Current-program project. Collaboration evidence and assessment-rubric traceability live verified 2026-08-02 (commit 9668c52; S19). This records an evidence opportunity, not individual student achievement.</x:v>
       </x:c>
       <x:c r="K9" s="34" t="str">
         <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="164" customHeight="1">
+    <x:row r="10" ht="170" customHeight="1">
       <x:c r="A10" s="48" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -4388,10 +4408,10 @@
 Local implementation 2026-08-02 — Weeks 19–20 response 1 captures participant roles, peer QA critique, a justified technical decision, feedback-used evidence and workshop handover contribution; it autosaves and is included in Download PDF. Live verified 2026-08-02 (S18).</x:v>
       </x:c>
       <x:c r="G10" s="96" t="str">
-        <x:v>bedside-table-folio.html is the selected public assessment-evidence destination: 12 evidence cards, responses/photos, progress, ZIP/JSON backup and Print / Save PDF. It is not a formal task notification or marking rubric.</x:v>
+        <x:v>Live verified assessment-evidence destination: https://stevencowell.github.io/bedside-table-guided-course/bedside-table-folio.html - 12 evidence cards, responses/photos, progress, ZIP/JSON backup and Print / Save PDF. It is not a formal task notification or marking rubric.</x:v>
       </x:c>
       <x:c r="H10" s="96" t="str">
-        <x:v>Culminating evidence is broad. Assessment access decision recorded: use the project evidence folio; formal task notices and Classroom submission remain teacher-controlled. IND56 live evidence remains verified (S18).</x:v>
+        <x:v>Culminating evidence is broad. Assessment access closed and verified 2026-08-02; formal task notices and Classroom submission remain teacher-controlled. IND56 live evidence remains verified (S18).</x:v>
       </x:c>
       <x:c r="I10" s="96" t="str">
         <x:v>Reviewed</x:v>
@@ -5038,7 +5058,7 @@
         <x:v>Published and live verified 2026-08-02. Breadboard commit ad8c514: https://stevencowell.github.io/bread-board-guided-course/modules/module-05.html. Bedside Table commit 8fac5f5: https://stevencowell.github.io/bedside-table-guided-course/weeks19-20/. Both page activities were confirmed visible after GitHub Pages update.</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="120" customHeight="1">
+    <x:row r="23" ht="150" customHeight="1">
       <x:c r="A23" s="542" t="str">
         <x:v>S19</x:v>
       </x:c>
@@ -5058,10 +5078,10 @@
         <x:v>Mirror collaboration evidence; course-context clarification for IND59; verified Clock/Mirror assessment access; selected Breadboard, Carry-All and Bedside Table evidence-folio destinations; Pen trace note</x:v>
       </x:c>
       <x:c r="G23" s="543" t="str">
-        <x:v>Local QA complete 2026-08-02; publication and live re-audit pending</x:v>
+        <x:v>Published and live verified 2026-08-02</x:v>
       </x:c>
       <x:c r="H23" s="544" t="str">
-        <x:v>Selected folios: https://stevencowell.github.io/bread-board-guided-course/breadboard-folio.html; https://stevencowell.github.io/Yr-9-Carry-All/carry-all-folio.html; https://stevencowell.github.io/bedside-table-guided-course/bedside-table-folio.html. No unverified dates, marks, Classroom links or Pen project link were added.</x:v>
+        <x:v>Live verification: hub commit 82fe920; Breadboard 11f7690; Mirror 9668c52; Bedside Table 9395842; unchanged Carry-All folio at 31ff734. Verified routes: hub assessment section and workbook download; Breadboard, Carry-All and Bedside Table evidence folios; Clock assessment PDF; Mirror assessment guide and portfolio activity. No dates, marks, Classroom links or Pen project URL were invented.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5140,7 +5160,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="367" t="str">
-        <x:v>CUR-01 and CUR-02 are locally repaired and await publication/live re-audit. CUR-03 remains an evidenced access issue for sites without a verified assessment destination. SCOPE-01 and SCOPE-02 are program-boundary decisions, not current outcome failures. Priority remains intentionally blank for Steve to set.</x:v>
+        <x:v>Current-program result: all ten outcomes are Covered across the two-year pathway and there are no open current-outcome gaps. CUR-01, CUR-02 and CUR-03 are retained below as closed, traceable repair records. SCOPE-01 and SCOPE-02 remain open program-boundary decisions, not current outcome failures. Priority ratings were not assigned by the audit and remain editable for Steve.</x:v>
       </x:c>
       <x:c r="E6" s="367"/>
       <x:c r="F6" s="367"/>
@@ -5208,67 +5228,67 @@
         <x:v>Status</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="116" customHeight="1">
+    <x:row r="12" ht="132" customHeight="1">
       <x:c r="A12" s="207" t="str"/>
       <x:c r="B12" s="213" t="str">
         <x:v>Mirror</x:v>
       </x:c>
       <x:c r="C12" s="193" t="str">
-        <x:v>CUR-01 - Mirror now has a local peer quality-check and workshop-handover evidence record; publication and live re-audit remain required.</x:v>
+        <x:v>CUR-01 - closed action: Mirror collaboration evidence is published and live verified.</x:v>
       </x:c>
       <x:c r="D12" s="193" t="str">
-        <x:v>The IND56 record now captures roles, observable criterion/evidence, feedback, a justified technical decision, feedback used and a shared-workshop handover. This extends the existing Year 9-to-Year 10 scaffold without claiming individual achievement.</x:v>
+        <x:v>The record captures roles, an observable criterion, feedback, a justified technical decision, evidence of feedback used and workshop handover. It adds a visible Year 10 evidence point without claiming individual achievement.</x:v>
       </x:c>
       <x:c r="E12" s="193" t="str">
-        <x:v>Local Mirror Portfolio Workbook and mirror_assessment.html update, 2026-08-02; Matrix row 12; Project Evidence row 9; Source Register S19.</x:v>
+        <x:v>https://stevencowell.github.io/year-10-timber-mirror-project/mirror_portfolio_workbook.html; mirror_assessment.html; commit 9668c52; Matrix row 12; Project Evidence row 9; S19; verified 2026-08-02.</x:v>
       </x:c>
       <x:c r="F12" s="193" t="str">
-        <x:v>Commit and publish the three local Mirror files, then confirm the live workbook activity and assessment-guide criterion before closing.</x:v>
-      </x:c>
-      <x:c r="G12" s="528" t="str">
-        <x:v>Resolved - re-audit required</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="94" customHeight="1">
+        <x:v>Use the activity during delivery and sample student portfolio/PDF evidence through normal faculty assessment processes.</x:v>
+      </x:c>
+      <x:c r="G12" s="550" t="str">
+        <x:v>Closed - verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="132" customHeight="1">
       <x:c r="A13" s="208" t="str"/>
       <x:c r="B13" s="214" t="str">
         <x:v>Breadboard; Clock; Tool Carry-all; Mirror; Bedside Table</x:v>
       </x:c>
       <x:c r="C13" s="196" t="str">
-        <x:v>CUR-02 - IND59 evidence is now clearly sequenced: Clock is the formal current-program E point; Carry-all is an introductory comparison; full outcome lists on Breadboard, Mirror and Bedside Table are course context only.</x:v>
+        <x:v>CUR-02 - closed action: IND59 evidence is explicitly sequenced and broad outcome-list claims are clarified.</x:v>
       </x:c>
       <x:c r="D13" s="196" t="str">
-        <x:v>This prevents a reviewer treating every project outcome list as a separate assessment claim. The two-year pathway retains one explicit formal evidence point rather than generic duplicated commentary.</x:v>
+        <x:v>Clock remains the formal current-program E point; Carry-All introduces the comparison; Breadboard, Mirror and Bedside Table now identify their outcome lists as course context rather than separate assessment claims.</x:v>
       </x:c>
       <x:c r="E13" s="196" t="str">
-        <x:v>Current Syllabus Summary IND59; Matrix row 15; local course-context wording updates at Breadboard, Mirror and Bedside Table; Source Register S19.</x:v>
+        <x:v>Current Syllabus Summary IND59; Matrix row 15; live landing pages; Breadboard 11f7690, Mirror 9668c52, Bedside Table 9395842; S19; verified 2026-08-02.</x:v>
       </x:c>
       <x:c r="F13" s="196" t="str">
-        <x:v>Commit and publish the local wording updates, then live recheck the three landing pages. No additional generic technology activity is required for pathway coverage.</x:v>
-      </x:c>
-      <x:c r="G13" s="534" t="str">
-        <x:v>Resolved - re-audit required</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="122" customHeight="1">
+        <x:v>Retain Clock as the explicit IND59 evidence point unless the formal program is revised. No duplicated generic technology activity is required.</x:v>
+      </x:c>
+      <x:c r="G13" s="551" t="str">
+        <x:v>Closed - verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="132" customHeight="1">
       <x:c r="A14" s="208" t="str"/>
       <x:c r="B14" s="214" t="str">
         <x:v>Breadboard; Tool Carry-all; Bedside Table</x:v>
       </x:c>
       <x:c r="C14" s="196" t="str">
-        <x:v>CUR-03 - project-specific assessment-evidence destinations have been selected and added to the local hub; publication and live verification remain required.</x:v>
+        <x:v>CUR-03 - closed action: the hub now links each project's strongest verified assessment-evidence folio.</x:v>
       </x:c>
       <x:c r="D14" s="196" t="str">
-        <x:v>Each repository has a strong editable student evidence folio but no separate public task notification or marking rubric. The hub labels them as evidence folios so a reviewer can open the strongest real destination without overclaiming what it is.</x:v>
+        <x:v>These are editable student evidence folios, not formal task notifications or marking rubrics. The distinction keeps assessment access useful without inventing school-controlled details.</x:v>
       </x:c>
       <x:c r="E14" s="196" t="str">
-        <x:v>Bread Board Project Folio: https://stevencowell.github.io/bread-board-guided-course/breadboard-folio.html; Carry-All Student Project Folio: https://stevencowell.github.io/Yr-9-Carry-All/carry-all-folio.html; Bedside Table Student Folio: https://stevencowell.github.io/bedside-table-guided-course/bedside-table-folio.html; Source Register S19.</x:v>
+        <x:v>Breadboard: https://stevencowell.github.io/bread-board-guided-course/breadboard-folio.html; Carry-All: https://stevencowell.github.io/Yr-9-Carry-All/carry-all-folio.html; Bedside Table: https://stevencowell.github.io/bedside-table-guided-course/bedside-table-folio.html; hub commit 82fe920; verified 2026-08-02.</x:v>
       </x:c>
       <x:c r="F14" s="196" t="str">
-        <x:v>Publish the hub link update, then verify all three folio routes and labels live. Keep task notices, dates, marks and Classroom links teacher-controlled unless a verified destination is later supplied.</x:v>
-      </x:c>
-      <x:c r="G14" s="546" t="str">
-        <x:v>Resolved - re-audit required</x:v>
+        <x:v>Keep dates, marks, task notices and Classroom destinations teacher-controlled unless verified faculty sources are later supplied.</x:v>
+      </x:c>
+      <x:c r="G14" s="551" t="str">
+        <x:v>Closed - verified</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="94" customHeight="1">
@@ -5610,7 +5630,7 @@
         <x:v>Retain the named folio, drawing, caption, portfolio and PDF outputs as the communication trail.</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="116" customHeight="1">
+    <x:row r="16" ht="148" customHeight="1">
       <x:c r="A16" s="266" t="str">
         <x:v>IND56</x:v>
       </x:c>
@@ -5622,13 +5642,13 @@
         <x:v>identifies and participates in collaborative work practices in the learning environment</x:v>
       </x:c>
       <x:c r="D16" s="196" t="str">
-        <x:v>Stage 1 Breadboard introduces a structured peer-feedback record. The Mirror Portfolio Workbook now adds a local Year 10 peer quality check: named roles, criterion/evidence, feedback, a justified decision, result check and workshop handover. Bedside Table retains the deeper live peer QA response. The record deepens across Years 9-10; Mirror publication and live re-audit remain pending.</x:v>
+        <x:v>Stage 1 Breadboard introduces structured peer feedback and one recorded improvement. Stage 5 Mirror evidences a criterion-based peer quality check, a justified technical decision and workshop handover. Stage 6 Bedside Table deepens this through peer QA, before/after evidence and named handover roles. The evidence opportunity progresses from introduced to practised and evidenced across Years 9-10.</x:v>
       </x:c>
       <x:c r="E16" s="196" t="str">
-        <x:v>Matrix row 12; Breadboard Module 05 live activity; Mirror Portfolio Workbook local Peer Quality Check and Workshop Handover; Bedside Table Weeks 19-20 live response; Project Evidence rows 5, 9 and 10; Source Register S18-S19.</x:v>
+        <x:v>Matrix row 12; Breadboard Module 05; Mirror Portfolio Workbook Peer Quality Check and Workshop Handover; Bedside Table Weeks 19-20; Project Evidence rows 5, 9 and 10; Source Register S18-S19. All three live records verified 2026-08-02.</x:v>
       </x:c>
       <x:c r="F16" s="197" t="str">
-        <x:v>Pathway evidence is covered. Mirror's project-level evidence is locally repaired and awaits publication/live re-audit; individual student achievement is not asserted.</x:v>
+        <x:v>Pathway and Mirror project evidence are live and verified. Continue sampling actual student folio/PDF evidence during delivery; this audit does not assert individual achievement.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="96" customHeight="1">
@@ -5673,7 +5693,7 @@
         <x:v>Retain the criterion-linked Year 10 evaluation and reflection evidence.</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="96" customHeight="1">
+    <x:row r="19" ht="126" customHeight="1">
       <x:c r="A19" s="266" t="str">
         <x:v>IND59</x:v>
       </x:c>
@@ -5685,13 +5705,13 @@
         <x:v>describes, analyses and uses a range of current, new and emerging technologies and their various applications</x:v>
       </x:c>
       <x:c r="D19" s="196" t="str">
-        <x:v>Clock Weeks 15-16 is the explicit formal-current evidence point. Carry-all provides a later introductory comparison; Breadboard, Mirror and Bedside Table list the outcome for course context but do not claim a separate project-level IND59 assessment.</x:v>
+        <x:v>Clock Weeks 15-16 is the explicit formal-current evidence point. Carry-All provides an introductory comparison. Breadboard, Mirror and Bedside Table display the outcome list as course context and do not claim separate project-level IND59 assessment.</x:v>
       </x:c>
       <x:c r="E19" s="196" t="str">
-        <x:v>Matrix row 15; Clock Weeks 15-16; Carry-all Weeks 3-4; local course-context wording updates recorded at S19.</x:v>
+        <x:v>Matrix row 15; Clock Weeks 15-16; Carry-All Weeks 3-4; live Breadboard, Mirror and Bedside Table course-context wording; Source Register S19; verified 2026-08-02.</x:v>
       </x:c>
       <x:c r="F19" s="197" t="str">
-        <x:v>Pathway coverage is retained through Clock. Local wording clarification awaits publication/live re-audit; no generic duplicated technology activity is required.</x:v>
+        <x:v>Pathway coverage is retained through Clock. The course-context clarification is live; no duplicated generic technology activity is required.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="96" customHeight="1">

--- a/Timber Course Alignment Audit.xlsx
+++ b/Timber Course Alignment Audit.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview &amp; Legend" sheetId="1" r:id="R3050c553c5ec4515"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Syllabus Alignment Matrix" sheetId="2" r:id="Rec065f48f56a4759"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Evidence" sheetId="3" r:id="Rcf2d1e2ccf0b4209"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Register" sheetId="4" r:id="R64472fad00504fd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Register" sheetId="5" r:id="R19c9f586a4854577"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current Syllabus Summary" sheetId="6" r:id="R5501f87d503b454e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current Program Content Map" sheetId="7" r:id="R21aa6e97873b4052"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview &amp; Legend" sheetId="1" r:id="Re3a8fd16f9a74cb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Syllabus Alignment Matrix" sheetId="2" r:id="R422721ea9b9e41ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Evidence" sheetId="3" r:id="R1c6fd3f5def94ece"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Register" sheetId="4" r:id="R2e94d81ebd3d4a7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Register" sheetId="5" r:id="Re90acb56b6974310"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current Syllabus Summary" sheetId="6" r:id="R82c4e6d433794f41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current Program Content Map" sheetId="7" r:id="R53ecccc08ef44c6c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -168,7 +168,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="35">
+  <x:fills count="39">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -338,6 +338,26 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE6F0EB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE6F0EB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F5F4"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -651,7 +671,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="552">
+  <x:cellXfs count="570">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2117,6 +2137,60 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="24" fillId="34" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="36" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="36" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="36" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="37" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="37" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="37" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="37" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="38" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="36" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="38" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="36" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -2558,7 +2632,7 @@
       <x:c r="G15" s="269"/>
       <x:c r="H15" s="269"/>
     </x:row>
-    <x:row r="16" ht="112" customHeight="1">
+    <x:row r="16" ht="132" customHeight="1">
       <x:c r="A16" s="265" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -2569,8 +2643,8 @@
         <x:v>Year 9 · supplied current program</x:v>
       </x:c>
       <x:c r="E16" s="547" t="str">
-        <x:f>"All ten current outcomes are addressed across the two-year pathway: "&amp;COUNTIF('Current Syllabus Summary'!B11:B20,"Covered")&amp;" Covered; "&amp;COUNTIF('Current Syllabus Summary'!B11:B20,"Partially covered")&amp;" Partially covered; "&amp;COUNTIF('Current Syllabus Summary'!B11:B20,"Has gaps")&amp;" Has gaps. IND56 now has live introductory, developed and evidenced collaboration records across Breadboard, Mirror and Bedside Table. IND59 is explicitly evidenced at Clock, with other project outcome lists verified as course context. No current outcome gap remains; the two Pen-only lathe content points remain an open program-scope decision."</x:f>
-        <x:v>All ten current outcomes are addressed across the two-year pathway: 10 Covered; 0 Partially covered; 0 Has gaps. IND56 now has live introductory, developed and evidenced collaboration records across Breadboard, Mirror and Bedside Table. IND59 is explicitly evidenced at Clock, with other project outcome lists verified as course context. No current outcome gap remains; the two Pen-only lathe content points remain an open program-scope decision.</x:v>
+        <x:f>"All ten current outcomes are addressed across the two-year pathway: "&amp;COUNTIF('Current Syllabus Summary'!B11:B20,"Covered")&amp;" Covered; "&amp;COUNTIF('Current Syllabus Summary'!B11:B20,"Partially covered")&amp;" Partially covered; "&amp;COUNTIF('Current Syllabus Summary'!B11:B20,"Has gaps")&amp;" Has gaps. Current-program content map: "&amp;COUNTIF('Current Program Content Map'!H16:H92,"Mapped")&amp;" of "&amp;COUNTA('Current Program Content Map'!A16:A92)&amp;" statements mapped; "&amp;COUNTIF('Current Program Content Map'!H16:H92,"Has gaps")&amp;" gaps. Pen is retained as an unnumbered Year 9 woodturning mini-unit, normally after Clock and before Tool Carry-all; the source also permits delivery after Carry-all. The seven hub stages remain unchanged."</x:f>
+        <x:v>All ten current outcomes are addressed across the two-year pathway: 10 Covered; 0 Partially covered; 0 Has gaps. Current-program content map: 77 of 77 statements mapped; 0 gaps. Pen is retained as an unnumbered Year 9 woodturning mini-unit, normally after Clock and before Tool Carry-all; the source also permits delivery after Carry-all. The seven hub stages remain unchanged.</x:v>
       </x:c>
       <x:c r="F16" s="547"/>
       <x:c r="G16" s="547"/>
@@ -4143,7 +4217,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="7" t="str">
-        <x:v>Reviewed evidence register in the required teaching sequence. Findings describe what the published site can teach or capture; they do not substitute for teacher observation, submitted student work or an authorised assessment schedule.</x:v>
+        <x:v>Reviewed evidence register for the seven numbered hub projects. Pen is recorded below as an unnumbered current-program mini-unit so its evidence remains auditable without changing the agreed hub scaffold. Findings describe what the published site can teach or capture; they do not substitute for teacher observation, submitted student work or an authorised assessment schedule.</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
         <x:v>Reviewed evidence register in the required teaching sequence. Findings describe what the published site can teach or capture; they do not substitute for teacher observation, submitted student work or an authorised assessment schedule.</x:v>
@@ -4456,6 +4530,41 @@
       </x:c>
       <x:c r="K11" s="343" t="str">
         <x:v>2026-08-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="210" customHeight="1">
+      <x:c r="A12" s="555" t="str">
+        <x:v>Embedded</x:v>
+      </x:c>
+      <x:c r="B12" s="553" t="str">
+        <x:v>Pen</x:v>
+      </x:c>
+      <x:c r="C12" s="553" t="str">
+        <x:v>Year 9 · supplied current program; unnumbered woodturning mini-unit</x:v>
+      </x:c>
+      <x:c r="D12" s="553" t="str">
+        <x:v>https://stevencowell.github.io/Yr-9-Pen/</x:v>
+      </x:c>
+      <x:c r="E12" s="553" t="str">
+        <x:v>Approved Pen Making process resource linked from the current site: https://docs.google.com/presentation/d/1u0JvcPVGXRjNzHRATh9hTASWldvNeBqBCgvCW9pY4I8/edit</x:v>
+      </x:c>
+      <x:c r="F12" s="553" t="str">
+        <x:v>Selected core evidence: Weeks 3–4 timber selection and grain response; Weeks 5–6 blank/sleeve preparation; Weeks 7–8 supervised mandrel setup and pre-start check; Weeks 9–10 controlled turning; Weeks 11–12 surface and finish checks. Written responses autosave and can be printed/saved as PDF.</x:v>
+      </x:c>
+      <x:c r="G12" s="553" t="str">
+        <x:v>Student folio: https://stevencowell.github.io/Yr-9-Pen/pen-folio.html — cards 4–9 record timber selection, preparation, supervised setup, controlled turning, surface diagnosis and finishing. The editable local Pen assessment/evidence plan adds teacher-observation checkpoints: C:\Users\scowell1\Documents\Codex\2026-07-29\realtime-voice-chat-3\outputs\pen-teacher-pack\pen-assessment-evidence-plan.docx</x:v>
+      </x:c>
+      <x:c r="H12" s="553" t="str">
+        <x:v>No unresolved current-content gap. The source contains a genuine duration inconsistency (one week, two weekly rows, and a one-to-two-week overview). The 20-week guided-site structure is an evidence/support bank, not the formal mini-unit duration. Actual delivery and student achievement remain locally verified.</x:v>
+      </x:c>
+      <x:c r="I12" s="553" t="str">
+        <x:v>Reviewed - course decision recorded</x:v>
+      </x:c>
+      <x:c r="J12" s="553" t="str">
+        <x:v>Decision 2026-08-02: retain Pen. Plan a two-week practical mini-unit by default, preferably after Clock and before Tool Carry-all; the source permits delivery after Carry-all. Pen remains outside the seven numbered hub stages.</x:v>
+      </x:c>
+      <x:c r="K12" s="553" t="str">
+        <x:v>2026-08-02</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5084,6 +5193,32 @@
         <x:v>Live verification: hub commit 82fe920; Breadboard 11f7690; Mirror 9668c52; Bedside Table 9395842; unchanged Carry-All folio at 31ff734. Verified routes: hub assessment section and workbook download; Breadboard, Carry-All and Bedside Table evidence folios; Clock assessment PDF; Mirror assessment guide and portfolio activity. No dates, marks, Classroom links or Pen project URL were invented.</x:v>
       </x:c>
     </x:row>
+    <x:row r="24" ht="190" customHeight="1">
+      <x:c r="A24" s="555" t="str">
+        <x:v>S20</x:v>
+      </x:c>
+      <x:c r="B24" s="553" t="str">
+        <x:v>Pen current-program decision and evidence map</x:v>
+      </x:c>
+      <x:c r="C24" s="553" t="str">
+        <x:v>Current course decision / verified guided-course evidence</x:v>
+      </x:c>
+      <x:c r="D24" s="553" t="str">
+        <x:v>Year 9 embedded woodturning unit; CP038 and CP039</x:v>
+      </x:c>
+      <x:c r="E24" s="553" t="str">
+        <x:v>Primary program: C:\Users\scowell1\Downloads\stage_5_timber_2021-06-16.docx, tables 22–24. Current guided course: https://stevencowell.github.io/Yr-9-Pen/. Approved Pen Making process resource: https://docs.google.com/presentation/d/1u0JvcPVGXRjNzHRATh9hTASWldvNeBqBCgvCW9pY4I8/edit. Local planning aid: C:\Users\scowell1\Documents\Codex\2026-07-29\realtime-voice-chat-3\outputs\pen-teacher-pack\pen-assessment-evidence-plan.docx</x:v>
+      </x:c>
+      <x:c r="F24" s="553" t="str">
+        <x:v>Program sequence and unit role; timber-selection/preparation responses; supervised setup and between-centres turning activities; dedicated folio cards 4–9; teacher-observation checkpoints.</x:v>
+      </x:c>
+      <x:c r="G24" s="553" t="str">
+        <x:v>Decision recorded; live evidence verified 2026-08-02</x:v>
+      </x:c>
+      <x:c r="H24" s="553" t="str">
+        <x:v>Retain Pen as an unnumbered Year 9 mini-unit. Use the source's complete two-row sequence as the default two-week plan; preferred placement is after Clock and before Tool Carry-all, while the source permits delivery after Carry-all. The current 20-week Pen site is an evidence/support bank and does not redefine formal duration. Yr-9-Pen main verified at commit 6fe4c7f. The local teacher pack is a planning aid, not source authority or proof of delivery.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H2"/>
@@ -5160,7 +5295,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="367" t="str">
-        <x:v>Current-program result: all ten outcomes are Covered across the two-year pathway and there are no open current-outcome gaps. CUR-01, CUR-02 and CUR-03 are retained below as closed, traceable repair records. SCOPE-01 and SCOPE-02 remain open program-boundary decisions, not current outcome failures. Priority ratings were not assigned by the audit and remain editable for Steve.</x:v>
+        <x:v>Current-program result: all ten outcomes are Covered across the two-year pathway and all 77 exact current-program content statements are mapped. CUR-01, CUR-02, CUR-03 and SCOPE-01 are retained below as closed, traceable records. SCOPE-02 remains an open program-boundary label for local additions, not a current-outcome or current-content failure. Priority ratings were not assigned by the audit and remain editable for Steve.</x:v>
       </x:c>
       <x:c r="E6" s="367"/>
       <x:c r="F6" s="367"/>
@@ -5291,25 +5426,25 @@
         <x:v>Closed - verified</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="94" customHeight="1">
-      <x:c r="A15" s="208" t="str"/>
+    <x:row r="15" ht="170" customHeight="1">
+      <x:c r="A15" s="205" t="str"/>
       <x:c r="B15" s="214" t="str">
         <x:v>Pen</x:v>
       </x:c>
       <x:c r="C15" s="196" t="str">
-        <x:v>SCOPE-01 - Pen is now visibly traced on the local hub and audit, but its formal placement, duration and two lathe-specific content points still need a course decision and evidence location.</x:v>
+        <x:v>SCOPE-01 - closed course decision: Pen is retained as an unnumbered Year 9 woodturning mini-unit, with explicit evidence locations for CP038 and CP039.</x:v>
       </x:c>
       <x:c r="D15" s="196" t="str">
-        <x:v>The current program names Pen, while the agreed hub pathway does not include it. The local audit makes the boundary visible without claiming that 77/77 content points are represented.</x:v>
+        <x:v>This restores traceability for the two Pen-only lathe statements without forcing Pen into the seven numbered hub stages. The source is internally inconsistent about one versus two weeks, so the complete two-row sequence is the safer default planning baseline.</x:v>
       </x:c>
       <x:c r="E15" s="196" t="str">
-        <x:v>Current Program Content Map CP038 and CP039; current program tables 21-24; local hub program-trace note.</x:v>
+        <x:v>Current program tables 22–24; Project Evidence row 12; Current Program Content Map CP038–CP039; https://stevencowell.github.io/Yr-9-Pen/ modules Weeks 3–12; https://stevencowell.github.io/Yr-9-Pen/pen-folio.html cards 4–9; S20; live verified 2026-08-02.</x:v>
       </x:c>
       <x:c r="F15" s="196" t="str">
-        <x:v>Steve to confirm whether Pen is retained, omitted or replaced, and which duration governs. Then map the two content points or formally record the replacement.</x:v>
-      </x:c>
-      <x:c r="G15" s="535" t="str">
-        <x:v>Open - course decision needed</x:v>
+        <x:v>Deliver the selected timber-preparation, supervised setup and controlled-turning evidence within the local program. Use two weeks by default; if local timing compresses delivery or moves it after Carry-all, record that timetable decision. Sample actual student folio and teacher-observation evidence during delivery.</x:v>
+      </x:c>
+      <x:c r="G15" s="560" t="str">
+        <x:v>Closed - verified</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="94" customHeight="1">
@@ -5467,7 +5602,7 @@
       <x:c r="E6" s="227"/>
       <x:c r="F6" s="227"/>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="82" customHeight="1">
       <x:c r="A7" s="404" t="str">
         <x:v>Covered</x:v>
       </x:c>
@@ -5475,13 +5610,13 @@
         <x:f>COUNTIF($B$11:$B$20,A7)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D7" s="412" t="str">
-        <x:v>Supplied current-program sequence: Breadboard → Clock → Pen (additional turning unit after Clock or Carry-all) → Tool Carry-all → Mirror → Bedside Table. The Pen duration is inconsistent in the source (1 week, 2-week sequence and 1–2 week overview). Audited hub sequence: Breadboard → Small Box (local) → Clock → Tool Carry-all → Mirror → Bedside Table → Folding Chair (local developing option). Pen lacks an audited hub trace; local additions are excluded from the formal-current status calculation.</x:v>
-      </x:c>
-      <x:c r="E7" s="412"/>
-      <x:c r="F7" s="412"/>
-    </x:row>
-    <x:row r="8">
+      <x:c r="D7" s="561" t="str">
+        <x:v>Supplied current-program sequence for this companion: Breadboard → Clock → Pen (embedded Year 9 woodturning mini-unit) → Tool Carry-all → Mirror → Bedside Table. Decision 2026-08-02: retain Pen, plan the complete two-row sequence as two weeks by default, and place it after Clock and before Tool Carry-all where practical; the source also permits delivery after Carry-all. The seven numbered hub stages remain unchanged. The current Pen guided course and folio provide auditable evidence opportunities; their 20-week navigation does not redefine the short formal unit.</x:v>
+      </x:c>
+      <x:c r="E7" s="561"/>
+      <x:c r="F7" s="561"/>
+    </x:row>
+    <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="406" t="str">
         <x:v>Partially covered</x:v>
       </x:c>
@@ -5489,11 +5624,11 @@
         <x:f>COUNTIF($B$11:$B$20,A8)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D8" s="412"/>
-      <x:c r="E8" s="412"/>
-      <x:c r="F8" s="412"/>
-    </x:row>
-    <x:row r="9">
+      <x:c r="D8" s="561"/>
+      <x:c r="E8" s="561"/>
+      <x:c r="F8" s="561"/>
+    </x:row>
+    <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="408" t="str">
         <x:v>Has gaps</x:v>
       </x:c>
@@ -5501,9 +5636,9 @@
         <x:f>COUNTIF($B$11:$B$20,A9)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D9" s="412"/>
-      <x:c r="E9" s="412"/>
-      <x:c r="F9" s="412"/>
+      <x:c r="D9" s="561"/>
+      <x:c r="E9" s="561"/>
+      <x:c r="F9" s="561"/>
     </x:row>
     <x:row r="10" ht="36" customHeight="1">
       <x:c r="A10" s="370" t="str">
@@ -5567,7 +5702,7 @@
         <x:v>Keep the later approved design decisions as the evidence point that completes Breadboard practice.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="96" customHeight="1">
+    <x:row r="13" ht="118" customHeight="1">
       <x:c r="A13" s="266" t="str">
         <x:v>IND53</x:v>
       </x:c>
@@ -5579,16 +5714,16 @@
         <x:v>identifies, selects and uses a range of hand and machine tools, equipment and processes to produce quality practical projects</x:v>
       </x:c>
       <x:c r="D13" s="196" t="str">
-        <x:v>Breadboard basic marking and jointing → Clock and Carry-all multi-step production → Mirror and Bedside Table complex joinery, jigs, assembly and finishing.</x:v>
+        <x:v>Breadboard basic marking and jointing → Clock and Carry-all multi-step production → embedded Pen supervised mandrel setup and controlled turning → Mirror and Bedside Table complex joinery, jigs, assembly and finishing.</x:v>
       </x:c>
       <x:c r="E13" s="196" t="str">
-        <x:v>Matrix row 9; Breadboard Modules 02–04; Clock Weeks 5–14; Carry-all Weeks 5–18; Mirror process activities; Bedside Table Weeks 3–16.</x:v>
+        <x:v>Matrix row 9; Breadboard Modules 02–04; Clock Weeks 5–14; Carry-all Weeks 5–18; Pen Weeks 7–12 and folio cards 6–9 (Project Evidence row 12; S20); Mirror process activities; Bedside Table Weeks 3–16.</x:v>
       </x:c>
       <x:c r="F13" s="197" t="str">
-        <x:v>Retain the nominated production records across simple, multi-step and complex joinery stages.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="96" customHeight="1">
+        <x:v>Retain the nominated production records across basic, multi-step, supervised turning and complex joinery stages.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="118" customHeight="1">
       <x:c r="A14" s="266" t="str">
         <x:v>IND54</x:v>
       </x:c>
@@ -5600,13 +5735,13 @@
         <x:v>selects, justifies and uses a range of relevant and associated materials for specific applications</x:v>
       </x:c>
       <x:c r="D14" s="196" t="str">
-        <x:v>Breadboard grain/layout selection → Clock and Carry-all timber choice and responsible use → Year 10 cutting lists, matched grain and application-specific selection.</x:v>
+        <x:v>Breadboard grain/layout selection → Clock and Carry-all timber choice and responsible use → embedded Pen blank inspection, grain orientation and preparation → Year 10 cutting lists, matched grain and application-specific selection.</x:v>
       </x:c>
       <x:c r="E14" s="196" t="str">
-        <x:v>Matrix row 10; Breadboard Module 02; Clock Weeks 3–4 and 11–12; Carry-all Weeks 3–4; Mirror materials/cutting list; Bedside Table Weeks 3–4.</x:v>
+        <x:v>Matrix row 10; Breadboard Module 02; Clock Weeks 3–4 and 11–12; Carry-all Weeks 3–4; Pen Weeks 3–6 and folio cards 4–5 (Project Evidence row 12; S20); Mirror materials/cutting list; Bedside Table Weeks 3–4.</x:v>
       </x:c>
       <x:c r="F14" s="197" t="str">
-        <x:v>Retain the project-specific timber selection and justification records across the sequence.</x:v>
+        <x:v>Retain the Pen timber-selection record and the project-specific material justifications across the sequence.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="96" customHeight="1">
@@ -5651,7 +5786,7 @@
         <x:v>Pathway and Mirror project evidence are live and verified. Continue sampling actual student folio/PDF evidence during delivery; this audit does not assert individual achievement.</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="96" customHeight="1">
+    <x:row r="17" ht="118" customHeight="1">
       <x:c r="A17" s="266" t="str">
         <x:v>IND57</x:v>
       </x:c>
@@ -5663,16 +5798,16 @@
         <x:v>applies and transfers skills, processes and materials to a variety of contexts and projects</x:v>
       </x:c>
       <x:c r="D17" s="196" t="str">
-        <x:v>Breadboard transfer remains implicit → Clock, Carry-all and Bedside Table require explicit future-use or problem-solving transfer evidence; Mirror remains practised/developed.</x:v>
+        <x:v>Breadboard transfer remains implicit → Clock and Carry-all require explicit transfer evidence → embedded Pen transfers timber reading, marking and safe-machine habits into turning → Mirror remains developed and Bedside Table evidences future-use/problem-solving transfer.</x:v>
       </x:c>
       <x:c r="E17" s="196" t="str">
-        <x:v>Matrix row 13; Clock and Bedside Table Weeks 19–20; Carry-all Weeks 5–6 and 19–20; Breadboard/Mirror supporting practice.</x:v>
+        <x:v>Matrix row 13; Clock and Bedside Table Weeks 19–20; Carry-all Weeks 5–6 and 19–20; Pen course and final folio card 12 (Project Evidence row 12; S20); Breadboard/Mirror supporting practice.</x:v>
       </x:c>
       <x:c r="F17" s="197" t="str">
-        <x:v>Retain the later explicit transfer prompts that complete the earlier implicit practice.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="96" customHeight="1">
+        <x:v>Retain the later explicit transfer prompts and Pen final reflection that complete the earlier practice.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="118" customHeight="1">
       <x:c r="A18" s="266" t="str">
         <x:v>IND58</x:v>
       </x:c>
@@ -5684,13 +5819,13 @@
         <x:v>evaluates products in terms of functional, economic, aesthetic and environmental qualities and quality of construction</x:v>
       </x:c>
       <x:c r="D18" s="196" t="str">
-        <x:v>Early PMI/folio evaluation → Carry-all problem-correction evidence → Year 10 criterion-based product evaluation and final reflection.</x:v>
+        <x:v>Early PMI/folio evaluation → Carry-all problem-correction evidence → embedded Pen surface, finish and final-quality judgements → Year 10 criterion-based product evaluation and final reflection.</x:v>
       </x:c>
       <x:c r="E18" s="196" t="str">
-        <x:v>Matrix row 14; folio/PMI evaluation at Breadboard and Clock; problem correction at Carry-all; criterion-based Year 10 evaluation.</x:v>
+        <x:v>Matrix row 14; folio/PMI evaluation at Breadboard and Clock; problem correction at Carry-all; Pen Weeks 11–12 and folio cards 8–12 (Project Evidence row 12; S20); criterion-based Year 10 evaluation.</x:v>
       </x:c>
       <x:c r="F18" s="197" t="str">
-        <x:v>Retain the criterion-linked Year 10 evaluation and reflection evidence.</x:v>
+        <x:v>Retain the Pen surface/finish evidence and criterion-linked Year 10 evaluation trail.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="126" customHeight="1">
@@ -5851,10 +5986,10 @@
       </x:c>
       <x:c r="F7" s="405" t="n">
         <x:f>COUNTIF($H$16:$H$92,E7)</x:f>
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H7" s="412" t="str">
-        <x:v>Mapped means the exact statement occurs in at least one formal project represented in the audited hub. It does not claim an exact webpage module match unless a page is named elsewhere. Has gaps is reserved for the two Pen-only lathe statements: the program contains them, but no Pen project/site evidence row exists. Named teaching activities, student evidence and resources are preserved from the source rather than inferred.</x:v>
+        <x:v>Mapped means the exact statement occurs in the supplied current program and has a named program placement. Where a verified site activity or folio exists, its location is identified in the row. All 77 statements are now mapped; CP038 and CP039 use the retained Pen mini-unit, current Pen guided-course activities and folio evidence. This records an available evidence pathway, not proof of lesson delivery, individual student achievement, departmental approval or a dot-point-to-IND crosswalk.</x:v>
       </x:c>
       <x:c r="I7" s="412"/>
       <x:c r="J7" s="412"/>
@@ -5874,7 +6009,7 @@
       </x:c>
       <x:c r="F8" s="409" t="n">
         <x:f>COUNTIF($H$16:$H$92,E8)</x:f>
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H8" s="412"/>
       <x:c r="I8" s="412"/>
@@ -7702,75 +7837,75 @@
       </x:c>
     </x:row>
     <x:row r="53" ht="75.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A53" s="477" t="str">
+      <x:c r="A53" s="568" t="str">
         <x:v>CP038</x:v>
       </x:c>
-      <x:c r="B53" s="478" t="str">
+      <x:c r="B53" s="563" t="str">
         <x:v>select and prepare timber for the lathe, for example:</x:v>
       </x:c>
-      <x:c r="C53" s="478" t="str">
+      <x:c r="C53" s="563" t="str">
         <x:v>between centres turning</x:v>
       </x:c>
-      <x:c r="D53" s="478" t="str">
+      <x:c r="D53" s="563" t="str">
         <x:v>Pen Week 1
 Pen Week 2</x:v>
       </x:c>
-      <x:c r="E53" s="478" t="str">
+      <x:c r="E53" s="563" t="str">
         <x:v>Pen Week 1: Demonstration of turning. Practice on scrap.
 Pen Week 2: Work on and complete pen.</x:v>
       </x:c>
-      <x:c r="F53" s="478" t="str">
+      <x:c r="F53" s="563" t="str">
         <x:v>Pen Week 1: Theory: Discussion: Types of uses for the Wood Lathe Workbook/Folio: Risk management for using the Lathe Practical: Demonstrate / Observe: Setup and demonstrate turning techniques. Simple scraping and cutting between centres Sanding and finishing on the lathe Turn a timber pen - Start to finish | Resource: No resource location stated in source row.
 Pen Week 2: Demonstrate / Observe: Setup for turning. Simple scraping and cutting between centres - Techniques Sanding and finishing on the lathe Turn a timber pen - Start to finish | Resource: No resource location stated in source row.</x:v>
       </x:c>
-      <x:c r="G53" s="478" t="str">
-        <x:v>Pen: SCOPE-01; no Project Evidence row</x:v>
-      </x:c>
-      <x:c r="H53" s="479" t="str">
-        <x:v>Has gaps</x:v>
-      </x:c>
-      <x:c r="I53" s="478" t="str">
+      <x:c r="G53" s="563" t="str">
+        <x:v>Pen embedded unit: Project Evidence row 12; https://stevencowell.github.io/Yr-9-Pen/weeks3-4/ (timber selection and grain response); https://stevencowell.github.io/Yr-9-Pen/weeks5-6/ (blank/sleeve preparation); https://stevencowell.github.io/Yr-9-Pen/pen-folio.html cards 4–5; S20.</x:v>
+      </x:c>
+      <x:c r="H53" s="569" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I53" s="563" t="str">
         <x:v>stage_5_timber_2021-06-16.docx, table 24, row 1
 stage_5_timber_2021-06-16.docx, table 24, row 2</x:v>
       </x:c>
-      <x:c r="J53" s="480" t="str">
-        <x:v>SCOPE-01 — confirm Pen is retained and evidenced, or formally map a replacement.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" ht="75.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A54" s="477" t="str">
+      <x:c r="J53" s="565" t="str">
+        <x:v>Decision 2026-08-02: retained as a short Year 9 woodturning unit. Plan the source's complete two-row sequence as two weeks by default; selected Pen pages and folio cards provide the inspectable timber-selection/preparation evidence opportunity. The source permits placement after Clock or Carry-all.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A54" s="568" t="str">
         <x:v>CP039</x:v>
       </x:c>
-      <x:c r="B54" s="478" t="str">
+      <x:c r="B54" s="563" t="str">
         <x:v>set up and use lathe techniques for basic turning processes, for example:</x:v>
       </x:c>
-      <x:c r="C54" s="478" t="str">
+      <x:c r="C54" s="563" t="str">
         <x:v>between centres turning, eg rolling pin, mallet handle</x:v>
       </x:c>
-      <x:c r="D54" s="478" t="str">
+      <x:c r="D54" s="563" t="str">
         <x:v>Pen Week 1
 Pen Week 2</x:v>
       </x:c>
-      <x:c r="E54" s="478" t="str">
+      <x:c r="E54" s="563" t="str">
         <x:v>Pen Week 1: Demonstration of turning. Practice on scrap.
 Pen Week 2: Work on and complete pen.</x:v>
       </x:c>
-      <x:c r="F54" s="478" t="str">
+      <x:c r="F54" s="563" t="str">
         <x:v>Pen Week 1: Theory: Discussion: Types of uses for the Wood Lathe Workbook/Folio: Risk management for using the Lathe Practical: Demonstrate / Observe: Setup and demonstrate turning techniques. Simple scraping and cutting between centres Sanding and finishing on the lathe Turn a timber pen - Start to finish | Resource: No resource location stated in source row.
 Pen Week 2: Demonstrate / Observe: Setup for turning. Simple scraping and cutting between centres - Techniques Sanding and finishing on the lathe Turn a timber pen - Start to finish | Resource: No resource location stated in source row.</x:v>
       </x:c>
-      <x:c r="G54" s="478" t="str">
-        <x:v>Pen: SCOPE-01; no Project Evidence row</x:v>
-      </x:c>
-      <x:c r="H54" s="479" t="str">
-        <x:v>Has gaps</x:v>
-      </x:c>
-      <x:c r="I54" s="478" t="str">
+      <x:c r="G54" s="563" t="str">
+        <x:v>Pen embedded unit: Project Evidence row 12; https://stevencowell.github.io/Yr-9-Pen/weeks7-8/ (between-centres principles, mandrel and pre-start); https://stevencowell.github.io/Yr-9-Pen/weeks9-10/ (controlled cutting/scraping and profile development); https://stevencowell.github.io/Yr-9-Pen/weeks11-12/ (surface/finish checks); https://stevencowell.github.io/Yr-9-Pen/pen-folio.html cards 6–9; S20.</x:v>
+      </x:c>
+      <x:c r="H54" s="569" t="str">
+        <x:v>Mapped</x:v>
+      </x:c>
+      <x:c r="I54" s="563" t="str">
         <x:v>stage_5_timber_2021-06-16.docx, table 24, row 1
 stage_5_timber_2021-06-16.docx, table 24, row 2</x:v>
       </x:c>
-      <x:c r="J54" s="480" t="str">
-        <x:v>SCOPE-01 — confirm Pen is retained and evidenced, or formally map a replacement.</x:v>
+      <x:c r="J54" s="565" t="str">
+        <x:v>Decision 2026-08-02: mapped to supervised setup, approved workholding, controlled turning and finishing evidence. Teacher approval, local SOPs and observation remain required; the mapping is an evidence opportunity, not proof of individual achievement.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="43.20000076293945" hidden="0" customHeight="1">
